--- a/tk_review/db/binding_major_sources.xlsx
+++ b/tk_review/db/binding_major_sources.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Binding'!$A$1:$M$576</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Binding'!$A$1:$M$579</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M576"/>
+  <dimension ref="A1:M579"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -30136,634 +30136,590 @@
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>PFBS</t>
+          <t>HFPO-DA</t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>bovine</t>
+          <t>human</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>bovine serum albumin (BSA)</t>
+          <t>human serum albumin (HSA)</t>
         </is>
       </c>
       <c r="D556" t="inlineStr">
         <is>
-          <t>log D</t>
+          <t>Kd</t>
         </is>
       </c>
       <c r="E556" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>1156</t>
         </is>
       </c>
       <c r="F556" t="inlineStr">
         <is>
-          <t>log10 (L_water/L_protein)</t>
-        </is>
-      </c>
-      <c r="G556" t="inlineStr"/>
-      <c r="H556" t="n">
-        <v>3.725</v>
-      </c>
+          <t>uM</t>
+        </is>
+      </c>
+      <c r="G556" t="n">
+        <v>1156</v>
+      </c>
+      <c r="H556" t="inlineStr"/>
       <c r="I556" t="inlineStr">
         <is>
-          <t>Bischel 2011</t>
-        </is>
-      </c>
-      <c r="J556" t="n">
-        <v>0.57</v>
-      </c>
+          <t>Jia 2022</t>
+        </is>
+      </c>
+      <c r="J556" t="inlineStr"/>
       <c r="K556" t="inlineStr">
         <is>
-          <t>0.010 to 0.57 uM</t>
-        </is>
-      </c>
-      <c r="L556" t="n">
-        <v>200</v>
-      </c>
+          <t>MST titration series</t>
+        </is>
+      </c>
+      <c r="L556" t="inlineStr"/>
       <c r="M556" t="inlineStr">
         <is>
-          <t>200 uM</t>
+          <t>see Text S7</t>
         </is>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>PFDA</t>
+          <t>HFPO-TA</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>bovine</t>
+          <t>human</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>bovine serum albumin (BSA)</t>
+          <t>human serum albumin (HSA)</t>
         </is>
       </c>
       <c r="D557" t="inlineStr">
         <is>
-          <t>log D</t>
+          <t>Kd</t>
         </is>
       </c>
       <c r="E557" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>84</t>
         </is>
       </c>
       <c r="F557" t="inlineStr">
         <is>
-          <t>log10 (L_water/L_protein)</t>
-        </is>
-      </c>
-      <c r="G557" t="inlineStr"/>
-      <c r="H557" t="n">
-        <v>3.725</v>
-      </c>
+          <t>uM</t>
+        </is>
+      </c>
+      <c r="G557" t="n">
+        <v>84</v>
+      </c>
+      <c r="H557" t="inlineStr"/>
       <c r="I557" t="inlineStr">
         <is>
-          <t>Bischel 2011</t>
-        </is>
-      </c>
-      <c r="J557" t="n">
-        <v>0.47</v>
-      </c>
+          <t>Jia 2022</t>
+        </is>
+      </c>
+      <c r="J557" t="inlineStr"/>
       <c r="K557" t="inlineStr">
         <is>
-          <t>0.016 to 0.47 uM</t>
-        </is>
-      </c>
-      <c r="L557" t="n">
-        <v>200</v>
-      </c>
+          <t>MST titration series</t>
+        </is>
+      </c>
+      <c r="L557" t="inlineStr"/>
       <c r="M557" t="inlineStr">
         <is>
-          <t>200 uM</t>
+          <t>see Text S7</t>
         </is>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>PFDoDA</t>
+          <t>HFPO-TeA</t>
         </is>
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>bovine</t>
+          <t>human</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>bovine serum albumin (BSA)</t>
+          <t>human serum albumin (HSA)</t>
         </is>
       </c>
       <c r="D558" t="inlineStr">
         <is>
-          <t>log D</t>
+          <t>Kd</t>
         </is>
       </c>
       <c r="E558" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>179</t>
         </is>
       </c>
       <c r="F558" t="inlineStr">
         <is>
-          <t>log10 (L_water/L_protein)</t>
-        </is>
-      </c>
-      <c r="G558" t="inlineStr"/>
-      <c r="H558" t="n">
-        <v>3.165</v>
-      </c>
+          <t>uM</t>
+        </is>
+      </c>
+      <c r="G558" t="n">
+        <v>179</v>
+      </c>
+      <c r="H558" t="inlineStr"/>
       <c r="I558" t="inlineStr">
         <is>
-          <t>Bischel 2011</t>
-        </is>
-      </c>
-      <c r="J558" t="n">
-        <v>0.68</v>
-      </c>
+          <t>Jia 2022</t>
+        </is>
+      </c>
+      <c r="J558" t="inlineStr"/>
       <c r="K558" t="inlineStr">
         <is>
-          <t>0.031 to 0.68 uM</t>
-        </is>
-      </c>
-      <c r="L558" t="n">
-        <v>200</v>
-      </c>
+          <t>MST titration series</t>
+        </is>
+      </c>
+      <c r="L558" t="inlineStr"/>
       <c r="M558" t="inlineStr">
         <is>
-          <t>200 uM</t>
+          <t>see Text S7</t>
         </is>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>PFHpA</t>
+          <t>PFEESA</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>bovine</t>
+          <t>human</t>
         </is>
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>bovine serum albumin (BSA)</t>
+          <t>human serum albumin (HSA)</t>
         </is>
       </c>
       <c r="D559" t="inlineStr">
         <is>
-          <t>log D</t>
+          <t>Kd</t>
         </is>
       </c>
       <c r="E559" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>874</t>
         </is>
       </c>
       <c r="F559" t="inlineStr">
         <is>
-          <t>log10 (L_water/L_protein)</t>
-        </is>
-      </c>
-      <c r="G559" t="inlineStr"/>
-      <c r="H559" t="n">
-        <v>4.095</v>
-      </c>
+          <t>uM</t>
+        </is>
+      </c>
+      <c r="G559" t="n">
+        <v>874</v>
+      </c>
+      <c r="H559" t="inlineStr"/>
       <c r="I559" t="inlineStr">
         <is>
-          <t>Bischel 2011</t>
-        </is>
-      </c>
-      <c r="J559" t="n">
-        <v>0.3</v>
-      </c>
+          <t>Jia 2022</t>
+        </is>
+      </c>
+      <c r="J559" t="inlineStr"/>
       <c r="K559" t="inlineStr">
         <is>
-          <t>0.054 to 0.30 uM</t>
-        </is>
-      </c>
-      <c r="L559" t="n">
-        <v>200</v>
-      </c>
+          <t>MST titration series</t>
+        </is>
+      </c>
+      <c r="L559" t="inlineStr"/>
       <c r="M559" t="inlineStr">
         <is>
-          <t>200 uM</t>
+          <t>see Text S7</t>
         </is>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>PFHxA</t>
+          <t>HFPO-DA</t>
         </is>
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>bovine</t>
+          <t>human</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
         <is>
-          <t>bovine serum albumin (BSA)</t>
+          <t>liver fatty acid-binding protein (hL-FABP)</t>
         </is>
       </c>
       <c r="D560" t="inlineStr">
         <is>
-          <t>log D</t>
+          <t>Kd</t>
         </is>
       </c>
       <c r="E560" t="inlineStr">
         <is>
-          <t>4.05</t>
+          <t>267.78</t>
         </is>
       </c>
       <c r="F560" t="inlineStr">
         <is>
-          <t>log10 (L_water/L_protein)</t>
-        </is>
-      </c>
-      <c r="G560" t="inlineStr"/>
-      <c r="H560" t="n">
-        <v>3.915</v>
-      </c>
+          <t>uM</t>
+        </is>
+      </c>
+      <c r="G560" t="n">
+        <v>267.8</v>
+      </c>
+      <c r="H560" t="inlineStr"/>
       <c r="I560" t="inlineStr">
         <is>
-          <t>Bischel 2011</t>
-        </is>
-      </c>
-      <c r="J560" t="n">
-        <v>0.43</v>
-      </c>
+          <t>Jia 2022</t>
+        </is>
+      </c>
+      <c r="J560" t="inlineStr"/>
       <c r="K560" t="inlineStr">
         <is>
-          <t>0.009 to 0.43 uM</t>
-        </is>
-      </c>
-      <c r="L560" t="n">
-        <v>200</v>
-      </c>
+          <t>MST titration series</t>
+        </is>
+      </c>
+      <c r="L560" t="inlineStr"/>
       <c r="M560" t="inlineStr">
         <is>
-          <t>200 uM</t>
+          <t>see Text S7</t>
         </is>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>PFHxS</t>
+          <t>HFPO-TA</t>
         </is>
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>bovine</t>
+          <t>human</t>
         </is>
       </c>
       <c r="C561" t="inlineStr">
         <is>
-          <t>bovine serum albumin (BSA)</t>
+          <t>liver fatty acid-binding protein (hL-FABP)</t>
         </is>
       </c>
       <c r="D561" t="inlineStr">
         <is>
-          <t>log D</t>
+          <t>Kd</t>
         </is>
       </c>
       <c r="E561" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>19.94</t>
         </is>
       </c>
       <c r="F561" t="inlineStr">
         <is>
-          <t>log10 (L_water/L_protein)</t>
-        </is>
-      </c>
-      <c r="G561" t="inlineStr"/>
-      <c r="H561" t="n">
-        <v>4.165</v>
-      </c>
+          <t>uM</t>
+        </is>
+      </c>
+      <c r="G561" t="n">
+        <v>19.94</v>
+      </c>
+      <c r="H561" t="inlineStr"/>
       <c r="I561" t="inlineStr">
         <is>
-          <t>Bischel 2011</t>
-        </is>
-      </c>
-      <c r="J561" t="n">
-        <v>0.27</v>
-      </c>
+          <t>Jia 2022</t>
+        </is>
+      </c>
+      <c r="J561" t="inlineStr"/>
       <c r="K561" t="inlineStr">
         <is>
-          <t>0.012 to 0.27 uM</t>
-        </is>
-      </c>
-      <c r="L561" t="n">
-        <v>200</v>
-      </c>
+          <t>MST titration series</t>
+        </is>
+      </c>
+      <c r="L561" t="inlineStr"/>
       <c r="M561" t="inlineStr">
         <is>
-          <t>200 uM</t>
+          <t>see Text S7</t>
         </is>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>PFNA</t>
+          <t>HFPO-TeA</t>
         </is>
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>bovine</t>
+          <t>human</t>
         </is>
       </c>
       <c r="C562" t="inlineStr">
         <is>
-          <t>bovine serum albumin (BSA)</t>
+          <t>liver fatty acid-binding protein (hL-FABP)</t>
         </is>
       </c>
       <c r="D562" t="inlineStr">
         <is>
-          <t>log D</t>
+          <t>Kd</t>
         </is>
       </c>
       <c r="E562" t="inlineStr">
         <is>
-          <t>4.05</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="F562" t="inlineStr">
         <is>
-          <t>log10 (L_water/L_protein)</t>
-        </is>
-      </c>
-      <c r="G562" t="inlineStr"/>
-      <c r="H562" t="n">
-        <v>3.915</v>
-      </c>
+          <t>uM</t>
+        </is>
+      </c>
+      <c r="G562" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="H562" t="inlineStr"/>
       <c r="I562" t="inlineStr">
         <is>
-          <t>Bischel 2011</t>
-        </is>
-      </c>
-      <c r="J562" t="n">
-        <v>0.46</v>
-      </c>
+          <t>Jia 2022</t>
+        </is>
+      </c>
+      <c r="J562" t="inlineStr"/>
       <c r="K562" t="inlineStr">
         <is>
-          <t>0.064 to 0.46 uM</t>
-        </is>
-      </c>
-      <c r="L562" t="n">
-        <v>200</v>
-      </c>
+          <t>MST titration series</t>
+        </is>
+      </c>
+      <c r="L562" t="inlineStr"/>
       <c r="M562" t="inlineStr">
         <is>
-          <t>200 uM</t>
+          <t>see Text S7</t>
         </is>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>PFOA</t>
+          <t>PFDoA</t>
         </is>
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>bovine</t>
+          <t>human</t>
         </is>
       </c>
       <c r="C563" t="inlineStr">
         <is>
-          <t>bovine serum albumin (BSA)</t>
+          <t>liver fatty acid-binding protein (hL-FABP)</t>
         </is>
       </c>
       <c r="D563" t="inlineStr">
         <is>
-          <t>log D</t>
+          <t>Kd</t>
         </is>
       </c>
       <c r="E563" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="F563" t="inlineStr">
         <is>
-          <t>log10 (L_water/L_protein)</t>
-        </is>
-      </c>
-      <c r="G563" t="inlineStr"/>
-      <c r="H563" t="n">
-        <v>4.005</v>
-      </c>
+          <t>uM</t>
+        </is>
+      </c>
+      <c r="G563" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="H563" t="inlineStr"/>
       <c r="I563" t="inlineStr">
         <is>
-          <t>Bischel 2011</t>
-        </is>
-      </c>
-      <c r="J563" t="n">
-        <v>0.32</v>
-      </c>
+          <t>Jia 2022</t>
+        </is>
+      </c>
+      <c r="J563" t="inlineStr"/>
       <c r="K563" t="inlineStr">
         <is>
-          <t>0.023 to 0.32 uM</t>
-        </is>
-      </c>
-      <c r="L563" t="n">
-        <v>200</v>
-      </c>
+          <t>MST titration series</t>
+        </is>
+      </c>
+      <c r="L563" t="inlineStr"/>
       <c r="M563" t="inlineStr">
         <is>
-          <t>200 uM</t>
+          <t>see Text S7</t>
         </is>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>PFOS</t>
+          <t>PFEESA</t>
         </is>
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>bovine</t>
+          <t>human</t>
         </is>
       </c>
       <c r="C564" t="inlineStr">
         <is>
-          <t>bovine serum albumin (BSA)</t>
+          <t>liver fatty acid-binding protein (hL-FABP)</t>
         </is>
       </c>
       <c r="D564" t="inlineStr">
         <is>
-          <t>log D</t>
+          <t>Kd</t>
         </is>
       </c>
       <c r="E564" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>3138.2</t>
         </is>
       </c>
       <c r="F564" t="inlineStr">
         <is>
-          <t>log10 (L_water/L_protein)</t>
-        </is>
-      </c>
-      <c r="G564" t="inlineStr"/>
-      <c r="H564" t="n">
-        <v>3.965</v>
-      </c>
+          <t>uM</t>
+        </is>
+      </c>
+      <c r="G564" t="n">
+        <v>3138</v>
+      </c>
+      <c r="H564" t="inlineStr"/>
       <c r="I564" t="inlineStr">
         <is>
-          <t>Bischel 2011</t>
-        </is>
-      </c>
-      <c r="J564" t="n">
-        <v>0.26</v>
-      </c>
+          <t>Jia 2022</t>
+        </is>
+      </c>
+      <c r="J564" t="inlineStr"/>
       <c r="K564" t="inlineStr">
         <is>
-          <t>0.013 to 0.26 uM</t>
-        </is>
-      </c>
-      <c r="L564" t="n">
-        <v>200</v>
-      </c>
+          <t>MST titration series</t>
+        </is>
+      </c>
+      <c r="L564" t="inlineStr"/>
       <c r="M564" t="inlineStr">
         <is>
-          <t>200 uM</t>
+          <t>see Text S7</t>
         </is>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>PFPeA</t>
+          <t>PFHxA</t>
         </is>
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>bovine</t>
+          <t>human</t>
         </is>
       </c>
       <c r="C565" t="inlineStr">
         <is>
-          <t>bovine serum albumin (BSA)</t>
+          <t>liver fatty acid-binding protein (hL-FABP)</t>
         </is>
       </c>
       <c r="D565" t="inlineStr">
         <is>
-          <t>log D</t>
+          <t>Kd</t>
         </is>
       </c>
       <c r="E565" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>538.07</t>
         </is>
       </c>
       <c r="F565" t="inlineStr">
         <is>
-          <t>log10 (L_water/L_protein)</t>
-        </is>
-      </c>
-      <c r="G565" t="inlineStr"/>
-      <c r="H565" t="n">
-        <v>3.265</v>
-      </c>
+          <t>uM</t>
+        </is>
+      </c>
+      <c r="G565" t="n">
+        <v>538.1</v>
+      </c>
+      <c r="H565" t="inlineStr"/>
       <c r="I565" t="inlineStr">
         <is>
-          <t>Bischel 2011</t>
-        </is>
-      </c>
-      <c r="J565" t="n">
-        <v>0.5600000000000001</v>
-      </c>
+          <t>Jia 2022</t>
+        </is>
+      </c>
+      <c r="J565" t="inlineStr"/>
       <c r="K565" t="inlineStr">
         <is>
-          <t>0.024 to 0.56 uM</t>
-        </is>
-      </c>
-      <c r="L565" t="n">
-        <v>200</v>
-      </c>
+          <t>MST titration series</t>
+        </is>
+      </c>
+      <c r="L565" t="inlineStr"/>
       <c r="M565" t="inlineStr">
         <is>
-          <t>200 uM</t>
+          <t>see Text S7</t>
         </is>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>PFUnDA</t>
+          <t>PFNA</t>
         </is>
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>bovine</t>
+          <t>human</t>
         </is>
       </c>
       <c r="C566" t="inlineStr">
         <is>
-          <t>bovine serum albumin (BSA)</t>
+          <t>liver fatty acid-binding protein (hL-FABP)</t>
         </is>
       </c>
       <c r="D566" t="inlineStr">
         <is>
-          <t>log D</t>
+          <t>Kd</t>
         </is>
       </c>
       <c r="E566" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>6.62</t>
         </is>
       </c>
       <c r="F566" t="inlineStr">
         <is>
-          <t>log10 (L_water/L_protein)</t>
-        </is>
-      </c>
-      <c r="G566" t="inlineStr"/>
-      <c r="H566" t="n">
-        <v>3.565</v>
-      </c>
+          <t>uM</t>
+        </is>
+      </c>
+      <c r="G566" t="n">
+        <v>6.62</v>
+      </c>
+      <c r="H566" t="inlineStr"/>
       <c r="I566" t="inlineStr">
         <is>
-          <t>Bischel 2011</t>
-        </is>
-      </c>
-      <c r="J566" t="n">
-        <v>0.38</v>
-      </c>
+          <t>Jia 2022</t>
+        </is>
+      </c>
+      <c r="J566" t="inlineStr"/>
       <c r="K566" t="inlineStr">
         <is>
-          <t>0.026 to 0.38 uM</t>
-        </is>
-      </c>
-      <c r="L566" t="n">
-        <v>200</v>
-      </c>
+          <t>MST titration series</t>
+        </is>
+      </c>
+      <c r="L566" t="inlineStr"/>
       <c r="M566" t="inlineStr">
         <is>
-          <t>200 uM</t>
+          <t>see Text S7</t>
         </is>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>11Cl-PF3OUdS (8:2 Cl-PFESA)</t>
+          <t>PFOA</t>
         </is>
       </c>
       <c r="B567" t="inlineStr">
@@ -30773,56 +30729,50 @@
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>human serum albumin (HSA)</t>
+          <t>liver fatty acid-binding protein (hL-FABP)</t>
         </is>
       </c>
       <c r="D567" t="inlineStr">
         <is>
-          <t>Ka</t>
+          <t>Kd</t>
         </is>
       </c>
       <c r="E567" t="inlineStr">
         <is>
-          <t>127.6</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="F567" t="inlineStr">
         <is>
-          <t>M^-1</t>
+          <t>uM</t>
         </is>
       </c>
       <c r="G567" t="n">
-        <v>7837</v>
-      </c>
-      <c r="H567" t="n">
-        <v>0.134</v>
-      </c>
+        <v>17.95</v>
+      </c>
+      <c r="H567" t="inlineStr"/>
       <c r="I567" t="inlineStr">
         <is>
-          <t>Wu 2024</t>
-        </is>
-      </c>
-      <c r="J567" t="n">
-        <v>500</v>
-      </c>
+          <t>Jia 2022</t>
+        </is>
+      </c>
+      <c r="J567" t="inlineStr"/>
       <c r="K567" t="inlineStr">
         <is>
-          <t>0.17-0.50 mM</t>
-        </is>
-      </c>
-      <c r="L567" t="n">
-        <v>830</v>
-      </c>
+          <t>MST titration series</t>
+        </is>
+      </c>
+      <c r="L567" t="inlineStr"/>
       <c r="M567" t="inlineStr">
         <is>
-          <t>0.50-0.83 mM</t>
+          <t>see Text S7</t>
         </is>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>9Cl-PF3ONS (F-53B, 6:2 Cl-PFESA)</t>
+          <t>PFOS</t>
         </is>
       </c>
       <c r="B568" t="inlineStr">
@@ -30832,526 +30782,675 @@
       </c>
       <c r="C568" t="inlineStr">
         <is>
-          <t>human serum albumin (HSA)</t>
+          <t>liver fatty acid-binding protein (hL-FABP)</t>
         </is>
       </c>
       <c r="D568" t="inlineStr">
         <is>
-          <t>Ka</t>
+          <t>Kd</t>
         </is>
       </c>
       <c r="E568" t="inlineStr">
         <is>
-          <t>117.1</t>
+          <t>16.45</t>
         </is>
       </c>
       <c r="F568" t="inlineStr">
         <is>
-          <t>M^-1</t>
+          <t>uM</t>
         </is>
       </c>
       <c r="G568" t="n">
-        <v>8540</v>
-      </c>
-      <c r="H568" t="n">
-        <v>0.105</v>
-      </c>
+        <v>16.45</v>
+      </c>
+      <c r="H568" t="inlineStr"/>
       <c r="I568" t="inlineStr">
         <is>
-          <t>Wu 2024</t>
-        </is>
-      </c>
-      <c r="J568" t="n">
-        <v>500</v>
-      </c>
+          <t>Jia 2022</t>
+        </is>
+      </c>
+      <c r="J568" t="inlineStr"/>
       <c r="K568" t="inlineStr">
         <is>
-          <t>0.17-0.50 mM</t>
-        </is>
-      </c>
-      <c r="L568" t="n">
-        <v>830</v>
-      </c>
+          <t>MST titration series</t>
+        </is>
+      </c>
+      <c r="L568" t="inlineStr"/>
       <c r="M568" t="inlineStr">
         <is>
-          <t>0.50-0.83 mM</t>
+          <t>see Text S7</t>
         </is>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>HFPO-DA (GenX)</t>
+          <t>PFBS</t>
         </is>
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>human</t>
+          <t>bovine</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
         <is>
-          <t>human serum albumin (HSA)</t>
+          <t>bovine serum albumin (BSA)</t>
         </is>
       </c>
       <c r="D569" t="inlineStr">
         <is>
-          <t>Ka</t>
+          <t>log D</t>
         </is>
       </c>
       <c r="E569" t="inlineStr">
         <is>
-          <t>58.99</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="F569" t="inlineStr">
         <is>
-          <t>M^-1</t>
-        </is>
-      </c>
-      <c r="G569" t="n">
-        <v>16950</v>
-      </c>
+          <t>log10 (L_water/L_protein)</t>
+        </is>
+      </c>
+      <c r="G569" t="inlineStr"/>
       <c r="H569" t="n">
-        <v>-0.259</v>
+        <v>3.725</v>
       </c>
       <c r="I569" t="inlineStr">
         <is>
-          <t>Wu 2024</t>
+          <t>Bischel 2011</t>
         </is>
       </c>
       <c r="J569" t="n">
-        <v>500</v>
+        <v>0.57</v>
       </c>
       <c r="K569" t="inlineStr">
         <is>
-          <t>0.17-0.50 mM</t>
+          <t>0.010 to 0.57 uM</t>
         </is>
       </c>
       <c r="L569" t="n">
-        <v>830</v>
+        <v>200</v>
       </c>
       <c r="M569" t="inlineStr">
         <is>
-          <t>0.50-0.83 mM</t>
+          <t>200 uM</t>
         </is>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>NaDONA (ADONA)</t>
+          <t>PFDA</t>
         </is>
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>human</t>
+          <t>bovine</t>
         </is>
       </c>
       <c r="C570" t="inlineStr">
         <is>
-          <t>human serum albumin (HSA)</t>
+          <t>bovine serum albumin (BSA)</t>
         </is>
       </c>
       <c r="D570" t="inlineStr">
         <is>
-          <t>Ka</t>
+          <t>log D</t>
         </is>
       </c>
       <c r="E570" t="inlineStr">
         <is>
-          <t>93.09</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="F570" t="inlineStr">
         <is>
-          <t>M^-1</t>
-        </is>
-      </c>
-      <c r="G570" t="n">
-        <v>10740</v>
-      </c>
+          <t>log10 (L_water/L_protein)</t>
+        </is>
+      </c>
+      <c r="G570" t="inlineStr"/>
       <c r="H570" t="n">
-        <v>-0.026</v>
+        <v>3.725</v>
       </c>
       <c r="I570" t="inlineStr">
         <is>
-          <t>Wu 2024</t>
+          <t>Bischel 2011</t>
         </is>
       </c>
       <c r="J570" t="n">
-        <v>500</v>
+        <v>0.47</v>
       </c>
       <c r="K570" t="inlineStr">
         <is>
-          <t>0.17-0.50 mM</t>
+          <t>0.016 to 0.47 uM</t>
         </is>
       </c>
       <c r="L570" t="n">
-        <v>830</v>
+        <v>200</v>
       </c>
       <c r="M570" t="inlineStr">
         <is>
-          <t>0.50-0.83 mM</t>
+          <t>200 uM</t>
         </is>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>PFBA</t>
+          <t>PFDoDA</t>
         </is>
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>human</t>
+          <t>bovine</t>
         </is>
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>human serum albumin (HSA)</t>
+          <t>bovine serum albumin (BSA)</t>
         </is>
       </c>
       <c r="D571" t="inlineStr">
         <is>
-          <t>Ka</t>
+          <t>log D</t>
         </is>
       </c>
       <c r="E571" t="inlineStr">
         <is>
-          <t>20.37</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="F571" t="inlineStr">
         <is>
-          <t>M^-1</t>
-        </is>
-      </c>
-      <c r="G571" t="n">
-        <v>49090</v>
-      </c>
+          <t>log10 (L_water/L_protein)</t>
+        </is>
+      </c>
+      <c r="G571" t="inlineStr"/>
       <c r="H571" t="n">
-        <v>-0.843</v>
+        <v>3.165</v>
       </c>
       <c r="I571" t="inlineStr">
         <is>
-          <t>Wu 2024</t>
+          <t>Bischel 2011</t>
         </is>
       </c>
       <c r="J571" t="n">
-        <v>500</v>
+        <v>0.68</v>
       </c>
       <c r="K571" t="inlineStr">
         <is>
-          <t>0.17-0.50 mM</t>
+          <t>0.031 to 0.68 uM</t>
         </is>
       </c>
       <c r="L571" t="n">
-        <v>830</v>
+        <v>200</v>
       </c>
       <c r="M571" t="inlineStr">
         <is>
-          <t>0.50-0.83 mM</t>
+          <t>200 uM</t>
         </is>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>PFBS</t>
+          <t>PFHpA</t>
         </is>
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>human</t>
+          <t>bovine</t>
         </is>
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>human serum albumin (HSA)</t>
+          <t>bovine serum albumin (BSA)</t>
         </is>
       </c>
       <c r="D572" t="inlineStr">
         <is>
-          <t>Ka</t>
+          <t>log D</t>
         </is>
       </c>
       <c r="E572" t="inlineStr">
         <is>
-          <t>116.5</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="F572" t="inlineStr">
         <is>
-          <t>M^-1</t>
-        </is>
-      </c>
-      <c r="G572" t="n">
-        <v>8584</v>
-      </c>
+          <t>log10 (L_water/L_protein)</t>
+        </is>
+      </c>
+      <c r="G572" t="inlineStr"/>
       <c r="H572" t="n">
-        <v>0.08799999999999999</v>
+        <v>4.095</v>
       </c>
       <c r="I572" t="inlineStr">
         <is>
-          <t>Wu 2024</t>
+          <t>Bischel 2011</t>
         </is>
       </c>
       <c r="J572" t="n">
-        <v>500</v>
+        <v>0.3</v>
       </c>
       <c r="K572" t="inlineStr">
         <is>
-          <t>0.17-0.50 mM</t>
+          <t>0.054 to 0.30 uM</t>
         </is>
       </c>
       <c r="L572" t="n">
-        <v>830</v>
+        <v>200</v>
       </c>
       <c r="M572" t="inlineStr">
         <is>
-          <t>0.50-0.83 mM</t>
+          <t>200 uM</t>
         </is>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>PFHxS</t>
+          <t>PFHxA</t>
         </is>
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>human</t>
+          <t>bovine</t>
         </is>
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>human serum albumin (HSA)</t>
+          <t>bovine serum albumin (BSA)</t>
         </is>
       </c>
       <c r="D573" t="inlineStr">
         <is>
-          <t>Ka</t>
+          <t>log D</t>
         </is>
       </c>
       <c r="E573" t="inlineStr">
         <is>
-          <t>157.9</t>
+          <t>4.05</t>
         </is>
       </c>
       <c r="F573" t="inlineStr">
         <is>
-          <t>M^-1</t>
-        </is>
-      </c>
-      <c r="G573" t="n">
-        <v>6333</v>
-      </c>
+          <t>log10 (L_water/L_protein)</t>
+        </is>
+      </c>
+      <c r="G573" t="inlineStr"/>
       <c r="H573" t="n">
-        <v>0.241</v>
+        <v>3.915</v>
       </c>
       <c r="I573" t="inlineStr">
         <is>
-          <t>Wu 2024</t>
+          <t>Bischel 2011</t>
         </is>
       </c>
       <c r="J573" t="n">
-        <v>500</v>
+        <v>0.43</v>
       </c>
       <c r="K573" t="inlineStr">
         <is>
-          <t>0.17-0.50 mM</t>
+          <t>0.009 to 0.43 uM</t>
         </is>
       </c>
       <c r="L573" t="n">
-        <v>830</v>
+        <v>200</v>
       </c>
       <c r="M573" t="inlineStr">
         <is>
-          <t>0.50-0.83 mM</t>
+          <t>200 uM</t>
         </is>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>PFOA</t>
+          <t>PFHxS</t>
         </is>
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>human</t>
+          <t>bovine</t>
         </is>
       </c>
       <c r="C574" t="inlineStr">
         <is>
-          <t>human serum albumin (HSA)</t>
+          <t>bovine serum albumin (BSA)</t>
         </is>
       </c>
       <c r="D574" t="inlineStr">
         <is>
-          <t>Ka</t>
+          <t>log D</t>
         </is>
       </c>
       <c r="E574" t="inlineStr">
         <is>
-          <t>103.3</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="F574" t="inlineStr">
         <is>
-          <t>M^-1</t>
-        </is>
-      </c>
-      <c r="G574" t="n">
-        <v>9681</v>
-      </c>
+          <t>log10 (L_water/L_protein)</t>
+        </is>
+      </c>
+      <c r="G574" t="inlineStr"/>
       <c r="H574" t="n">
-        <v>0.024</v>
+        <v>4.165</v>
       </c>
       <c r="I574" t="inlineStr">
         <is>
-          <t>Wu 2024</t>
+          <t>Bischel 2011</t>
         </is>
       </c>
       <c r="J574" t="n">
-        <v>500</v>
+        <v>0.27</v>
       </c>
       <c r="K574" t="inlineStr">
         <is>
-          <t>0.17-0.50 mM</t>
+          <t>0.012 to 0.27 uM</t>
         </is>
       </c>
       <c r="L574" t="n">
-        <v>830</v>
+        <v>200</v>
       </c>
       <c r="M574" t="inlineStr">
         <is>
-          <t>0.50-0.83 mM</t>
+          <t>200 uM</t>
         </is>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>PFOS</t>
+          <t>PFNA</t>
         </is>
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>human</t>
+          <t>bovine</t>
         </is>
       </c>
       <c r="C575" t="inlineStr">
         <is>
-          <t>human serum albumin (HSA)</t>
+          <t>bovine serum albumin (BSA)</t>
         </is>
       </c>
       <c r="D575" t="inlineStr">
         <is>
-          <t>Ka</t>
+          <t>log D</t>
         </is>
       </c>
       <c r="E575" t="inlineStr">
         <is>
-          <t>394.6</t>
+          <t>4.05</t>
         </is>
       </c>
       <c r="F575" t="inlineStr">
         <is>
-          <t>M^-1</t>
-        </is>
-      </c>
-      <c r="G575" t="n">
-        <v>2534</v>
-      </c>
+          <t>log10 (L_water/L_protein)</t>
+        </is>
+      </c>
+      <c r="G575" t="inlineStr"/>
       <c r="H575" t="n">
-        <v>0.712</v>
+        <v>3.915</v>
       </c>
       <c r="I575" t="inlineStr">
         <is>
-          <t>Wu 2024</t>
+          <t>Bischel 2011</t>
         </is>
       </c>
       <c r="J575" t="n">
-        <v>500</v>
+        <v>0.46</v>
       </c>
       <c r="K575" t="inlineStr">
         <is>
-          <t>0.17-0.50 mM</t>
+          <t>0.064 to 0.46 uM</t>
         </is>
       </c>
       <c r="L575" t="n">
-        <v>830</v>
+        <v>200</v>
       </c>
       <c r="M575" t="inlineStr">
         <is>
-          <t>0.50-0.83 mM</t>
+          <t>200 uM</t>
         </is>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>PFPrS</t>
+          <t>PFOA</t>
         </is>
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>human</t>
+          <t>bovine</t>
         </is>
       </c>
       <c r="C576" t="inlineStr">
         <is>
-          <t>human serum albumin (HSA)</t>
+          <t>bovine serum albumin (BSA)</t>
         </is>
       </c>
       <c r="D576" t="inlineStr">
         <is>
-          <t>Ka</t>
+          <t>log D</t>
         </is>
       </c>
       <c r="E576" t="inlineStr">
         <is>
-          <t>79.45</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="F576" t="inlineStr">
         <is>
-          <t>M^-1</t>
-        </is>
-      </c>
-      <c r="G576" t="n">
-        <v>12590</v>
-      </c>
+          <t>log10 (L_water/L_protein)</t>
+        </is>
+      </c>
+      <c r="G576" t="inlineStr"/>
       <c r="H576" t="n">
-        <v>-0.111</v>
+        <v>4.005</v>
       </c>
       <c r="I576" t="inlineStr">
         <is>
-          <t>Wu 2024</t>
+          <t>Bischel 2011</t>
         </is>
       </c>
       <c r="J576" t="n">
-        <v>500</v>
+        <v>0.32</v>
       </c>
       <c r="K576" t="inlineStr">
         <is>
-          <t>0.17-0.50 mM</t>
+          <t>0.023 to 0.32 uM</t>
         </is>
       </c>
       <c r="L576" t="n">
-        <v>830</v>
+        <v>200</v>
       </c>
       <c r="M576" t="inlineStr">
         <is>
-          <t>0.50-0.83 mM</t>
+          <t>200 uM</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>PFOS</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>bovine</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>bovine serum albumin (BSA)</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>log D</t>
+        </is>
+      </c>
+      <c r="E577" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
+      <c r="F577" t="inlineStr">
+        <is>
+          <t>log10 (L_water/L_protein)</t>
+        </is>
+      </c>
+      <c r="G577" t="inlineStr"/>
+      <c r="H577" t="n">
+        <v>3.965</v>
+      </c>
+      <c r="I577" t="inlineStr">
+        <is>
+          <t>Bischel 2011</t>
+        </is>
+      </c>
+      <c r="J577" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="K577" t="inlineStr">
+        <is>
+          <t>0.013 to 0.26 uM</t>
+        </is>
+      </c>
+      <c r="L577" t="n">
+        <v>200</v>
+      </c>
+      <c r="M577" t="inlineStr">
+        <is>
+          <t>200 uM</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>PFPeA</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>bovine</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>bovine serum albumin (BSA)</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>log D</t>
+        </is>
+      </c>
+      <c r="E578" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="F578" t="inlineStr">
+        <is>
+          <t>log10 (L_water/L_protein)</t>
+        </is>
+      </c>
+      <c r="G578" t="inlineStr"/>
+      <c r="H578" t="n">
+        <v>3.265</v>
+      </c>
+      <c r="I578" t="inlineStr">
+        <is>
+          <t>Bischel 2011</t>
+        </is>
+      </c>
+      <c r="J578" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="K578" t="inlineStr">
+        <is>
+          <t>0.024 to 0.56 uM</t>
+        </is>
+      </c>
+      <c r="L578" t="n">
+        <v>200</v>
+      </c>
+      <c r="M578" t="inlineStr">
+        <is>
+          <t>200 uM</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>PFUnDA</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>bovine</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>bovine serum albumin (BSA)</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>log D</t>
+        </is>
+      </c>
+      <c r="E579" t="inlineStr">
+        <is>
+          <t>3.7</t>
+        </is>
+      </c>
+      <c r="F579" t="inlineStr">
+        <is>
+          <t>log10 (L_water/L_protein)</t>
+        </is>
+      </c>
+      <c r="G579" t="inlineStr"/>
+      <c r="H579" t="n">
+        <v>3.565</v>
+      </c>
+      <c r="I579" t="inlineStr">
+        <is>
+          <t>Bischel 2011</t>
+        </is>
+      </c>
+      <c r="J579" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="K579" t="inlineStr">
+        <is>
+          <t>0.026 to 0.38 uM</t>
+        </is>
+      </c>
+      <c r="L579" t="n">
+        <v>200</v>
+      </c>
+      <c r="M579" t="inlineStr">
+        <is>
+          <t>200 uM</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M576"/>
+  <autoFilter ref="A1:M579"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -31570,42 +31669,42 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bischel 2011</t>
+          <t>Jia 2022</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C10" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D10" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>log D 11</t>
+          <t>Kd 13</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Wu 2024</t>
+          <t>Bischel 2011</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ka 10</t>
+          <t>log D 11</t>
         </is>
       </c>
     </row>
@@ -31620,7 +31719,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -31654,237 +31753,249 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>The top TOP_N sources (currently 10), plus any source tied with the last of them. A rank boundary that splits two sources with identical counts is an arbitrary decision dressed as a ranking. At 10 nothing ties at the boundary, so the rule does not bind here.</t>
+          <t>The top TOP_N sources (currently 10), plus any source tied with the last of them. A rank boundary that splits two sources with identical counts is an arbitrary decision dressed as a ranking. At 10 nothing ties AT the boundary, so the rule does not bind here -- but Wu 2024 and Khazaee 2021 tie with each other at 10 rows, one row below the cut of 11. A one-row margin is not a judgement about quality.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Ties inside the list</t>
+          <t>Missing by one row</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Broken on distinct compounds. Starnes 2024 and Qin 2024 (plasma) both supply 32 rows; Qin covers 16 compounds against 8 and so is listed first. Both are kept either way.</t>
+          <t>Khazaee 2021 is the only source in the database measuring PFAS against PPAR-alpha, -gamma and -delta and against intestinal FABP, and its rank understates it: 7 of its 17 reported pairs are non-detections, which carry no number and so are filed as qualitative rows. Read those from db/protein_binding.csv.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Why not Ryu 2024</t>
+          <t>Ties inside the list</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>It is the largest contributor to the full database (320 rows) and reports unbound fractions in whole tissue homogenate -- total protein plus phospholipid, no protein resolved. A row count is not a ranking of usefulness for this question.</t>
+          <t>Broken on distinct compounds. Starnes 2024 and Qin 2024 (plasma) both supply 32 rows; Qin covers 16 compounds against 8 and so is listed first. Both are kept either way.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Row selection</t>
+          <t>Why not Ryu 2024</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>By source, not by matrix: once a source is in, its rows come with it and the `protein` column says what each was measured in. But only EXPERIMENTAL Kd, Ka, log D and log K_membrane rows are here. Docking scores and predicted values are excluded as not measurements; unbound fractions are excluded as neither a Kd nor a K, and not convertible to either without a binding-site molarity almost no paper reports. Both remain in db/binding_affinity.xlsx.</t>
+          <t>It is the largest contributor to the full database (320 rows) and reports unbound fractions in whole tissue homogenate -- total protein plus phospholipid, no protein resolved. A row count is not a ranking of usefulness for this question.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
+          <t>Row selection</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>By source, not by matrix: once a source is in, its rows come with it and the `protein` column says what each was measured in. But only EXPERIMENTAL Kd, Ka, log D and log K_membrane rows are here. Docking scores and predicted values are excluded as not measurements; unbound fractions are excluded as neither a Kd nor a K, and not convertible to either without a binding-site molarity almost no paper reports. Both remain in db/binding_affinity.xlsx.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
           <t>Treat with care</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>Wu 2024's affinities sit three to four orders below every other measurement of the same compound on albumin (its PFOA value is 103 M-1); its docking scores are excluded here. Starnes 2025 measures by differential scanning fluorimetry at the protein's melting transition, about three orders off the dialysis values -- a documented offset, not a disagreement to average over. Muensterman 2026 is biomimetic chromatography calibrated against pharmaceuticals, a surrogate rather than an equilibrium measurement, and the paper does not state its basis.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr"/>
-      <c r="B9" s="5" t="inlineStr"/>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Wu 2024's affinities sit three to four orders below every other measurement of the same compound on albumin (its PFOA value is 103 M-1); its docking scores are excluded here. Starnes 2025 measures by differential scanning fluorimetry at the protein's melting transition, about three orders off the dialysis values -- a documented offset, not a disagreement to average over. Muensterman 2026 is biomimetic chromatography calibrated against pharmaceuticals, a surrogate rather than an equilibrium measurement, and the paper does not state its basis. Jia 2022 measures by microscale thermophoresis; on hL-FABP its PFOA Kd is 181x the equilibrium-dialysis value of Khazaee 2021 and the fluorescence value is 509x it, so a liver-FABP affinity is only comparable within one method.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr"/>
       <c r="B10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>pfas</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>Chemical as the paper names it.</t>
-        </is>
-      </c>
+      <c r="A11" s="4" t="inlineStr"/>
+      <c r="B11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>species</t>
+          <t>pfas</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Species the protein came from.</t>
+          <t>Chemical as the paper names it.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>protein</t>
+          <t>species</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Protein or matrix, as the paper describes it.</t>
+          <t>Species the protein came from.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>measure</t>
+          <t>protein</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Kd, Ka, log D (protein-water), log K_membrane, f_unbound. A '(computed)' suffix means the source reports the value as predicted rather than measured.</t>
+          <t>Protein or matrix, as the paper describes it.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>measure</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>The number as printed, including ranges and bounds.</t>
+          <t>Kd, Ka, log D (protein-water), log K_membrane, f_unbound. A '(computed)' suffix means the source reports the value as predicted rather than measured.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>units</t>
+          <t>value</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Canonicalised unit for that value.</t>
+          <t>The number as printed, including ranges and bounds.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>kd_uM</t>
+          <t>units</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Everything that converts EXACTLY to a dissociation constant in micromolar. Blank is a deliberate state, never a gap: log D is not converted to Kd, and a Kd is not derived from an affinity without a stoichiometry the paper reports.</t>
+          <t>Canonicalised unit for that value.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>logK</t>
+          <t>kd_uM</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>log10 of the protein-water partition coefficient, L_water per kg protein. Two exact routes only: the paper measured it, or reported BOTH an affinity and a stoichiometry.</t>
+          <t>Everything that converts EXACTLY to a dissociation constant in micromolar. Blank is a deliberate state, never a gap: log D is not converted to Kd, and a Kd is not derived from an affinity without a stoichiometry the paper reports.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
+          <t>logK</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>log10 of the protein-water partition coefficient, L_water per kg protein. Two exact routes only: the paper measured it, or reported BOTH an affinity and a stoichiometry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
           <t>source</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>First author and year. 'Qin 2024 (plasma)' is doi 10.1021/acs.est.3c10824; the other Qin 2024 paper, the baseline-toxicity one, is a different study and is labelled separately.</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr"/>
-      <c r="B20" s="5" t="inlineStr"/>
-    </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>pfas_conc_uM</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>Dosed PFAS concentration in micromolar where unit arithmetic alone reaches one. A range is carried as its midpoint only where the source states a range in molar units.</t>
-        </is>
-      </c>
+      <c r="A21" s="4" t="inlineStr"/>
+      <c r="B21" s="5" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>pfas_conc_as_stated</t>
+          <t>pfas_conc_uM</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>The paper's own wording, verbatim.</t>
+          <t>Dosed PFAS concentration in micromolar where unit arithmetic alone reaches one. A range is carried as its midpoint only where the source states a range in molar units.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>protein_conc_uM</t>
+          <t>pfas_conc_as_stated</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Protein concentration in micromolar, same rule.</t>
+          <t>The paper's own wording, verbatim.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
+          <t>protein_conc_uM</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Protein concentration in micromolar, same rule.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
           <t>protein_conc_as_stated</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>The paper's own wording, verbatim. Blank numbers beside a populated cell here are the cases that cannot be converted without assuming a molecular weight, a volume or a dilution -- a mass concentration (mg/mL), a stationary phase, or a molar ratio. None is inferred.</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr"/>
-      <c r="B25" s="5" t="inlineStr"/>
-    </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+      <c r="A26" s="4" t="inlineStr"/>
+      <c r="B26" s="5" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>Why concentration matters</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>PFAS binding to albumin is not linear. The apparent affinity falls about 2x per decade of free concentration (Qin 2024 Table 1), so two constants measured at different ligand:protein ratios are not comparable even for the same compound and protein. These columns are what makes that check possible.</t>
         </is>

--- a/tk_review/db/binding_major_sources.xlsx
+++ b/tk_review/db/binding_major_sources.xlsx
@@ -6388,7 +6388,9 @@
       <c r="G113" t="n">
         <v>9.06</v>
       </c>
-      <c r="H113" t="inlineStr"/>
+      <c r="H113" t="n">
+        <v>3.22</v>
+      </c>
       <c r="I113" t="inlineStr">
         <is>
           <t>Chen 2025</t>
@@ -6445,7 +6447,9 @@
       <c r="G114" t="n">
         <v>2.31</v>
       </c>
-      <c r="H114" t="inlineStr"/>
+      <c r="H114" t="n">
+        <v>3.814</v>
+      </c>
       <c r="I114" t="inlineStr">
         <is>
           <t>Chen 2025</t>
@@ -6502,7 +6506,9 @@
       <c r="G115" t="n">
         <v>3.52</v>
       </c>
-      <c r="H115" t="inlineStr"/>
+      <c r="H115" t="n">
+        <v>3.631</v>
+      </c>
       <c r="I115" t="inlineStr">
         <is>
           <t>Chen 2025</t>
@@ -6559,7 +6565,9 @@
       <c r="G116" t="n">
         <v>70.56999999999999</v>
       </c>
-      <c r="H116" t="inlineStr"/>
+      <c r="H116" t="n">
+        <v>2.329</v>
+      </c>
       <c r="I116" t="inlineStr">
         <is>
           <t>Chen 2025</t>
@@ -6616,7 +6624,9 @@
       <c r="G117" t="n">
         <v>18.96</v>
       </c>
-      <c r="H117" t="inlineStr"/>
+      <c r="H117" t="n">
+        <v>2.9</v>
+      </c>
       <c r="I117" t="inlineStr">
         <is>
           <t>Chen 2025</t>
@@ -6673,7 +6683,9 @@
       <c r="G118" t="n">
         <v>49.32</v>
       </c>
-      <c r="H118" t="inlineStr"/>
+      <c r="H118" t="n">
+        <v>2.484</v>
+      </c>
       <c r="I118" t="inlineStr">
         <is>
           <t>Chen 2025</t>
@@ -6730,7 +6742,9 @@
       <c r="G119" t="n">
         <v>30.44</v>
       </c>
-      <c r="H119" t="inlineStr"/>
+      <c r="H119" t="n">
+        <v>2.694</v>
+      </c>
       <c r="I119" t="inlineStr">
         <is>
           <t>Chen 2025</t>
@@ -6787,7 +6801,9 @@
       <c r="G120" t="n">
         <v>10.75</v>
       </c>
-      <c r="H120" t="inlineStr"/>
+      <c r="H120" t="n">
+        <v>3.146</v>
+      </c>
       <c r="I120" t="inlineStr">
         <is>
           <t>Chen 2025</t>
@@ -6844,7 +6860,9 @@
       <c r="G121" t="n">
         <v>3.64</v>
       </c>
-      <c r="H121" t="inlineStr"/>
+      <c r="H121" t="n">
+        <v>3.616</v>
+      </c>
       <c r="I121" t="inlineStr">
         <is>
           <t>Chen 2025</t>
@@ -6901,7 +6919,9 @@
       <c r="G122" t="n">
         <v>2.42</v>
       </c>
-      <c r="H122" t="inlineStr"/>
+      <c r="H122" t="n">
+        <v>3.794</v>
+      </c>
       <c r="I122" t="inlineStr">
         <is>
           <t>Chen 2025</t>
@@ -6958,7 +6978,9 @@
       <c r="G123" t="n">
         <v>4.23</v>
       </c>
-      <c r="H123" t="inlineStr"/>
+      <c r="H123" t="n">
+        <v>3.551</v>
+      </c>
       <c r="I123" t="inlineStr">
         <is>
           <t>Chen 2025</t>
@@ -7015,7 +7037,9 @@
       <c r="G124" t="n">
         <v>16.97</v>
       </c>
-      <c r="H124" t="inlineStr"/>
+      <c r="H124" t="n">
+        <v>2.948</v>
+      </c>
       <c r="I124" t="inlineStr">
         <is>
           <t>Chen 2025</t>
@@ -7072,7 +7096,9 @@
       <c r="G125" t="n">
         <v>2.71</v>
       </c>
-      <c r="H125" t="inlineStr"/>
+      <c r="H125" t="n">
+        <v>3.744</v>
+      </c>
       <c r="I125" t="inlineStr">
         <is>
           <t>Chen 2025</t>
@@ -7129,7 +7155,9 @@
       <c r="G126" t="n">
         <v>1.82</v>
       </c>
-      <c r="H126" t="inlineStr"/>
+      <c r="H126" t="n">
+        <v>3.917</v>
+      </c>
       <c r="I126" t="inlineStr">
         <is>
           <t>Chen 2025</t>
@@ -7186,7 +7214,9 @@
       <c r="G127" t="n">
         <v>1.99</v>
       </c>
-      <c r="H127" t="inlineStr"/>
+      <c r="H127" t="n">
+        <v>3.879</v>
+      </c>
       <c r="I127" t="inlineStr">
         <is>
           <t>Chen 2025</t>
@@ -7243,7 +7273,9 @@
       <c r="G128" t="n">
         <v>4.49</v>
       </c>
-      <c r="H128" t="inlineStr"/>
+      <c r="H128" t="n">
+        <v>3.525</v>
+      </c>
       <c r="I128" t="inlineStr">
         <is>
           <t>Chen 2025</t>
@@ -7300,7 +7332,9 @@
       <c r="G129" t="n">
         <v>2.26</v>
       </c>
-      <c r="H129" t="inlineStr"/>
+      <c r="H129" t="n">
+        <v>3.823</v>
+      </c>
       <c r="I129" t="inlineStr">
         <is>
           <t>Chen 2025</t>
@@ -7357,7 +7391,9 @@
       <c r="G130" t="n">
         <v>14.4</v>
       </c>
-      <c r="H130" t="inlineStr"/>
+      <c r="H130" t="n">
+        <v>3.019</v>
+      </c>
       <c r="I130" t="inlineStr">
         <is>
           <t>Chen 2025</t>
@@ -7414,7 +7450,9 @@
       <c r="G131" t="n">
         <v>0.87</v>
       </c>
-      <c r="H131" t="inlineStr"/>
+      <c r="H131" t="n">
+        <v>4.238</v>
+      </c>
       <c r="I131" t="inlineStr">
         <is>
           <t>Chen 2025</t>
@@ -7471,7 +7509,9 @@
       <c r="G132" t="n">
         <v>1.58</v>
       </c>
-      <c r="H132" t="inlineStr"/>
+      <c r="H132" t="n">
+        <v>3.979</v>
+      </c>
       <c r="I132" t="inlineStr">
         <is>
           <t>Chen 2025</t>
@@ -7528,7 +7568,9 @@
       <c r="G133" t="n">
         <v>5.68</v>
       </c>
-      <c r="H133" t="inlineStr"/>
+      <c r="H133" t="n">
+        <v>3.423</v>
+      </c>
       <c r="I133" t="inlineStr">
         <is>
           <t>Chen 2025</t>
@@ -7585,7 +7627,9 @@
       <c r="G134" t="n">
         <v>5.58</v>
       </c>
-      <c r="H134" t="inlineStr"/>
+      <c r="H134" t="n">
+        <v>3.431</v>
+      </c>
       <c r="I134" t="inlineStr">
         <is>
           <t>Chen 2025</t>
@@ -7642,7 +7686,9 @@
       <c r="G135" t="n">
         <v>3.07</v>
       </c>
-      <c r="H135" t="inlineStr"/>
+      <c r="H135" t="n">
+        <v>3.69</v>
+      </c>
       <c r="I135" t="inlineStr">
         <is>
           <t>Chen 2025</t>
@@ -7699,7 +7745,9 @@
       <c r="G136" t="n">
         <v>7.4</v>
       </c>
-      <c r="H136" t="inlineStr"/>
+      <c r="H136" t="n">
+        <v>3.308</v>
+      </c>
       <c r="I136" t="inlineStr">
         <is>
           <t>Chen 2025</t>
@@ -7756,7 +7804,9 @@
       <c r="G137" t="n">
         <v>6.57</v>
       </c>
-      <c r="H137" t="inlineStr"/>
+      <c r="H137" t="n">
+        <v>3.36</v>
+      </c>
       <c r="I137" t="inlineStr">
         <is>
           <t>Chen 2025</t>
@@ -7813,7 +7863,9 @@
       <c r="G138" t="n">
         <v>5.44</v>
       </c>
-      <c r="H138" t="inlineStr"/>
+      <c r="H138" t="n">
+        <v>3.442</v>
+      </c>
       <c r="I138" t="inlineStr">
         <is>
           <t>Chen 2025</t>
@@ -7870,7 +7922,9 @@
       <c r="G139" t="n">
         <v>6.63</v>
       </c>
-      <c r="H139" t="inlineStr"/>
+      <c r="H139" t="n">
+        <v>3.356</v>
+      </c>
       <c r="I139" t="inlineStr">
         <is>
           <t>Chen 2025</t>
@@ -7927,7 +7981,9 @@
       <c r="G140" t="n">
         <v>33.68</v>
       </c>
-      <c r="H140" t="inlineStr"/>
+      <c r="H140" t="n">
+        <v>2.65</v>
+      </c>
       <c r="I140" t="inlineStr">
         <is>
           <t>Chen 2025</t>
@@ -7984,7 +8040,9 @@
       <c r="G141" t="n">
         <v>12.98</v>
       </c>
-      <c r="H141" t="inlineStr"/>
+      <c r="H141" t="n">
+        <v>3.064</v>
+      </c>
       <c r="I141" t="inlineStr">
         <is>
           <t>Chen 2025</t>
@@ -8041,7 +8099,9 @@
       <c r="G142" t="n">
         <v>12.22</v>
       </c>
-      <c r="H142" t="inlineStr"/>
+      <c r="H142" t="n">
+        <v>3.09</v>
+      </c>
       <c r="I142" t="inlineStr">
         <is>
           <t>Chen 2025</t>
@@ -8098,7 +8158,9 @@
       <c r="G143" t="n">
         <v>84.90000000000001</v>
       </c>
-      <c r="H143" t="inlineStr"/>
+      <c r="H143" t="n">
+        <v>2.249</v>
+      </c>
       <c r="I143" t="inlineStr">
         <is>
           <t>Chen 2025</t>
@@ -8155,7 +8217,9 @@
       <c r="G144" t="n">
         <v>15.6</v>
       </c>
-      <c r="H144" t="inlineStr"/>
+      <c r="H144" t="n">
+        <v>2.984</v>
+      </c>
       <c r="I144" t="inlineStr">
         <is>
           <t>Chen 2025</t>
@@ -8212,7 +8276,9 @@
       <c r="G145" t="n">
         <v>3.64</v>
       </c>
-      <c r="H145" t="inlineStr"/>
+      <c r="H145" t="n">
+        <v>3.616</v>
+      </c>
       <c r="I145" t="inlineStr">
         <is>
           <t>Chen 2025</t>
@@ -8269,7 +8335,9 @@
       <c r="G146" t="n">
         <v>1.88</v>
       </c>
-      <c r="H146" t="inlineStr"/>
+      <c r="H146" t="n">
+        <v>3.903</v>
+      </c>
       <c r="I146" t="inlineStr">
         <is>
           <t>Chen 2025</t>
@@ -8326,7 +8394,9 @@
       <c r="G147" t="n">
         <v>15.76</v>
       </c>
-      <c r="H147" t="inlineStr"/>
+      <c r="H147" t="n">
+        <v>2.98</v>
+      </c>
       <c r="I147" t="inlineStr">
         <is>
           <t>Chen 2025</t>
@@ -8383,7 +8453,9 @@
       <c r="G148" t="n">
         <v>1.29</v>
       </c>
-      <c r="H148" t="inlineStr"/>
+      <c r="H148" t="n">
+        <v>4.067</v>
+      </c>
       <c r="I148" t="inlineStr">
         <is>
           <t>Chen 2025</t>
@@ -8440,7 +8512,9 @@
       <c r="G149" t="n">
         <v>5.15</v>
       </c>
-      <c r="H149" t="inlineStr"/>
+      <c r="H149" t="n">
+        <v>3.466</v>
+      </c>
       <c r="I149" t="inlineStr">
         <is>
           <t>Chen 2025</t>
@@ -8497,7 +8571,9 @@
       <c r="G150" t="n">
         <v>1.62</v>
       </c>
-      <c r="H150" t="inlineStr"/>
+      <c r="H150" t="n">
+        <v>3.968</v>
+      </c>
       <c r="I150" t="inlineStr">
         <is>
           <t>Chen 2025</t>
@@ -8554,7 +8630,9 @@
       <c r="G151" t="n">
         <v>6.2</v>
       </c>
-      <c r="H151" t="inlineStr"/>
+      <c r="H151" t="n">
+        <v>3.385</v>
+      </c>
       <c r="I151" t="inlineStr">
         <is>
           <t>Chen 2025</t>
@@ -8611,7 +8689,9 @@
       <c r="G152" t="n">
         <v>1.68</v>
       </c>
-      <c r="H152" t="inlineStr"/>
+      <c r="H152" t="n">
+        <v>3.952</v>
+      </c>
       <c r="I152" t="inlineStr">
         <is>
           <t>Chen 2025</t>
@@ -8668,7 +8748,9 @@
       <c r="G153" t="n">
         <v>13.98</v>
       </c>
-      <c r="H153" t="inlineStr"/>
+      <c r="H153" t="n">
+        <v>3.032</v>
+      </c>
       <c r="I153" t="inlineStr">
         <is>
           <t>Chen 2025</t>
@@ -8725,7 +8807,9 @@
       <c r="G154" t="n">
         <v>10.45</v>
       </c>
-      <c r="H154" t="inlineStr"/>
+      <c r="H154" t="n">
+        <v>3.158</v>
+      </c>
       <c r="I154" t="inlineStr">
         <is>
           <t>Chen 2025</t>
@@ -8782,7 +8866,9 @@
       <c r="G155" t="n">
         <v>1.31</v>
       </c>
-      <c r="H155" t="inlineStr"/>
+      <c r="H155" t="n">
+        <v>4.06</v>
+      </c>
       <c r="I155" t="inlineStr">
         <is>
           <t>Chen 2025</t>
@@ -8839,7 +8925,9 @@
       <c r="G156" t="n">
         <v>6.19</v>
       </c>
-      <c r="H156" t="inlineStr"/>
+      <c r="H156" t="n">
+        <v>3.386</v>
+      </c>
       <c r="I156" t="inlineStr">
         <is>
           <t>Chen 2025</t>
@@ -8896,7 +8984,9 @@
       <c r="G157" t="n">
         <v>0.22</v>
       </c>
-      <c r="H157" t="inlineStr"/>
+      <c r="H157" t="n">
+        <v>4.835</v>
+      </c>
       <c r="I157" t="inlineStr">
         <is>
           <t>Chen 2025</t>
@@ -8953,7 +9043,9 @@
       <c r="G158" t="n">
         <v>47.55</v>
       </c>
-      <c r="H158" t="inlineStr"/>
+      <c r="H158" t="n">
+        <v>2.5</v>
+      </c>
       <c r="I158" t="inlineStr">
         <is>
           <t>Chen 2025</t>
@@ -9010,7 +9102,9 @@
       <c r="G159" t="n">
         <v>3.75</v>
       </c>
-      <c r="H159" t="inlineStr"/>
+      <c r="H159" t="n">
+        <v>3.603</v>
+      </c>
       <c r="I159" t="inlineStr">
         <is>
           <t>Chen 2025</t>
@@ -9067,7 +9161,9 @@
       <c r="G160" t="n">
         <v>6.56</v>
       </c>
-      <c r="H160" t="inlineStr"/>
+      <c r="H160" t="n">
+        <v>3.361</v>
+      </c>
       <c r="I160" t="inlineStr">
         <is>
           <t>Chen 2025</t>
@@ -9124,7 +9220,9 @@
       <c r="G161" t="n">
         <v>2.57</v>
       </c>
-      <c r="H161" t="inlineStr"/>
+      <c r="H161" t="n">
+        <v>3.767</v>
+      </c>
       <c r="I161" t="inlineStr">
         <is>
           <t>Chen 2025</t>
@@ -9181,7 +9279,9 @@
       <c r="G162" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="H162" t="inlineStr"/>
+      <c r="H162" t="n">
+        <v>4.204</v>
+      </c>
       <c r="I162" t="inlineStr">
         <is>
           <t>Chen 2025</t>
@@ -9238,7 +9338,9 @@
       <c r="G163" t="n">
         <v>11.18</v>
       </c>
-      <c r="H163" t="inlineStr"/>
+      <c r="H163" t="n">
+        <v>3.129</v>
+      </c>
       <c r="I163" t="inlineStr">
         <is>
           <t>Chen 2025</t>
@@ -9295,7 +9397,9 @@
       <c r="G164" t="n">
         <v>16.27</v>
       </c>
-      <c r="H164" t="inlineStr"/>
+      <c r="H164" t="n">
+        <v>2.966</v>
+      </c>
       <c r="I164" t="inlineStr">
         <is>
           <t>Chen 2025</t>
@@ -9352,7 +9456,9 @@
       <c r="G165" t="n">
         <v>17.15</v>
       </c>
-      <c r="H165" t="inlineStr"/>
+      <c r="H165" t="n">
+        <v>2.943</v>
+      </c>
       <c r="I165" t="inlineStr">
         <is>
           <t>Chen 2025</t>
@@ -9409,7 +9515,9 @@
       <c r="G166" t="n">
         <v>13.09</v>
       </c>
-      <c r="H166" t="inlineStr"/>
+      <c r="H166" t="n">
+        <v>3.06</v>
+      </c>
       <c r="I166" t="inlineStr">
         <is>
           <t>Chen 2025</t>
@@ -9466,7 +9574,9 @@
       <c r="G167" t="n">
         <v>31.44</v>
       </c>
-      <c r="H167" t="inlineStr"/>
+      <c r="H167" t="n">
+        <v>2.68</v>
+      </c>
       <c r="I167" t="inlineStr">
         <is>
           <t>Chen 2025</t>
@@ -9523,7 +9633,9 @@
       <c r="G168" t="n">
         <v>4.73</v>
       </c>
-      <c r="H168" t="inlineStr"/>
+      <c r="H168" t="n">
+        <v>3.503</v>
+      </c>
       <c r="I168" t="inlineStr">
         <is>
           <t>Chen 2025</t>
@@ -9580,7 +9692,9 @@
       <c r="G169" t="n">
         <v>5.94</v>
       </c>
-      <c r="H169" t="inlineStr"/>
+      <c r="H169" t="n">
+        <v>3.404</v>
+      </c>
       <c r="I169" t="inlineStr">
         <is>
           <t>Chen 2025</t>

--- a/tk_review/db/binding_major_sources.xlsx
+++ b/tk_review/db/binding_major_sources.xlsx
@@ -456,7 +456,7 @@
     <col width="44" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="44" customWidth="1" min="10" max="10"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
     <col width="19" customWidth="1" min="12" max="12"/>
   </cols>
@@ -509,7 +509,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>binding_site</t>
+          <t>ligand_protein_ratio_max</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -563,7 +563,9 @@
       <c r="I2" t="n">
         <v>4.88</v>
       </c>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="n">
+        <v>0.004</v>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>C078</t>
@@ -615,7 +617,9 @@
       <c r="I3" t="n">
         <v>2.9</v>
       </c>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="n">
+        <v>0.004</v>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>C078</t>
@@ -667,7 +671,9 @@
       <c r="I4" t="n">
         <v>3.44</v>
       </c>
-      <c r="J4" t="inlineStr"/>
+      <c r="J4" t="n">
+        <v>0.004</v>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>C078</t>
@@ -719,7 +725,9 @@
       <c r="I5" t="n">
         <v>3.79</v>
       </c>
-      <c r="J5" t="inlineStr"/>
+      <c r="J5" t="n">
+        <v>0.004</v>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>C078</t>
@@ -771,7 +779,9 @@
       <c r="I6" t="n">
         <v>4.49</v>
       </c>
-      <c r="J6" t="inlineStr"/>
+      <c r="J6" t="n">
+        <v>0.004</v>
+      </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>C078</t>
@@ -823,7 +833,9 @@
       <c r="I7" t="n">
         <v>3.84</v>
       </c>
-      <c r="J7" t="inlineStr"/>
+      <c r="J7" t="n">
+        <v>0.004</v>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>C078</t>
@@ -875,7 +887,9 @@
       <c r="I8" t="n">
         <v>4.69</v>
       </c>
-      <c r="J8" t="inlineStr"/>
+      <c r="J8" t="n">
+        <v>0.004</v>
+      </c>
       <c r="K8" t="inlineStr">
         <is>
           <t>C078</t>
@@ -927,7 +941,9 @@
       <c r="I9" t="n">
         <v>4.33</v>
       </c>
-      <c r="J9" t="inlineStr"/>
+      <c r="J9" t="n">
+        <v>0.004</v>
+      </c>
       <c r="K9" t="inlineStr">
         <is>
           <t>C078</t>
@@ -979,7 +995,9 @@
       <c r="I10" t="n">
         <v>4.3</v>
       </c>
-      <c r="J10" t="inlineStr"/>
+      <c r="J10" t="n">
+        <v>0.004</v>
+      </c>
       <c r="K10" t="inlineStr">
         <is>
           <t>C078</t>
@@ -1031,7 +1049,9 @@
       <c r="I11" t="n">
         <v>4.29</v>
       </c>
-      <c r="J11" t="inlineStr"/>
+      <c r="J11" t="n">
+        <v>0.004</v>
+      </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>C078</t>
@@ -1083,7 +1103,9 @@
       <c r="I12" t="n">
         <v>4.29</v>
       </c>
-      <c r="J12" t="inlineStr"/>
+      <c r="J12" t="n">
+        <v>0.004</v>
+      </c>
       <c r="K12" t="inlineStr">
         <is>
           <t>C078</t>
@@ -1135,7 +1157,9 @@
       <c r="I13" t="n">
         <v>2.28</v>
       </c>
-      <c r="J13" t="inlineStr"/>
+      <c r="J13" t="n">
+        <v>0.004</v>
+      </c>
       <c r="K13" t="inlineStr">
         <is>
           <t>C078</t>
@@ -1187,7 +1211,9 @@
       <c r="I14" t="n">
         <v>4.81</v>
       </c>
-      <c r="J14" t="inlineStr"/>
+      <c r="J14" t="n">
+        <v>0.004</v>
+      </c>
       <c r="K14" t="inlineStr">
         <is>
           <t>C078</t>
@@ -1239,7 +1265,9 @@
       <c r="I15" t="n">
         <v>5.13</v>
       </c>
-      <c r="J15" t="inlineStr"/>
+      <c r="J15" t="n">
+        <v>0.004</v>
+      </c>
       <c r="K15" t="inlineStr">
         <is>
           <t>C078</t>
@@ -1291,7 +1319,9 @@
       <c r="I16" t="n">
         <v>5.12</v>
       </c>
-      <c r="J16" t="inlineStr"/>
+      <c r="J16" t="n">
+        <v>0.004</v>
+      </c>
       <c r="K16" t="inlineStr">
         <is>
           <t>C078</t>
@@ -1343,7 +1373,9 @@
       <c r="I17" t="n">
         <v>3.93</v>
       </c>
-      <c r="J17" t="inlineStr"/>
+      <c r="J17" t="n">
+        <v>0.004</v>
+      </c>
       <c r="K17" t="inlineStr">
         <is>
           <t>C078</t>
@@ -1395,7 +1427,9 @@
       <c r="I18" t="n">
         <v>4.88</v>
       </c>
-      <c r="J18" t="inlineStr"/>
+      <c r="J18" t="n">
+        <v>0.004</v>
+      </c>
       <c r="K18" t="inlineStr">
         <is>
           <t>C078</t>
@@ -1447,7 +1481,9 @@
       <c r="I19" t="n">
         <v>2.83</v>
       </c>
-      <c r="J19" t="inlineStr"/>
+      <c r="J19" t="n">
+        <v>0.004</v>
+      </c>
       <c r="K19" t="inlineStr">
         <is>
           <t>C078</t>
@@ -1499,7 +1535,9 @@
       <c r="I20" t="n">
         <v>4.61</v>
       </c>
-      <c r="J20" t="inlineStr"/>
+      <c r="J20" t="n">
+        <v>0.004</v>
+      </c>
       <c r="K20" t="inlineStr">
         <is>
           <t>C078</t>
@@ -1551,7 +1589,9 @@
       <c r="I21" t="n">
         <v>4.54</v>
       </c>
-      <c r="J21" t="inlineStr"/>
+      <c r="J21" t="n">
+        <v>0.004</v>
+      </c>
       <c r="K21" t="inlineStr">
         <is>
           <t>C078</t>
@@ -1603,7 +1643,9 @@
       <c r="I22" t="n">
         <v>5.14</v>
       </c>
-      <c r="J22" t="inlineStr"/>
+      <c r="J22" t="n">
+        <v>0.004</v>
+      </c>
       <c r="K22" t="inlineStr">
         <is>
           <t>C078</t>
@@ -1655,7 +1697,9 @@
       <c r="I23" t="n">
         <v>4.2</v>
       </c>
-      <c r="J23" t="inlineStr"/>
+      <c r="J23" t="n">
+        <v>0.004</v>
+      </c>
       <c r="K23" t="inlineStr">
         <is>
           <t>C078</t>
@@ -1707,7 +1751,9 @@
       <c r="I24" t="n">
         <v>4.76</v>
       </c>
-      <c r="J24" t="inlineStr"/>
+      <c r="J24" t="n">
+        <v>0.004</v>
+      </c>
       <c r="K24" t="inlineStr">
         <is>
           <t>C078</t>
@@ -1759,7 +1805,9 @@
       <c r="I25" t="n">
         <v>4</v>
       </c>
-      <c r="J25" t="inlineStr"/>
+      <c r="J25" t="n">
+        <v>0.004</v>
+      </c>
       <c r="K25" t="inlineStr">
         <is>
           <t>C078</t>
@@ -1811,7 +1859,9 @@
       <c r="I26" t="n">
         <v>3.87</v>
       </c>
-      <c r="J26" t="inlineStr"/>
+      <c r="J26" t="n">
+        <v>0.004</v>
+      </c>
       <c r="K26" t="inlineStr">
         <is>
           <t>C078</t>
@@ -1863,7 +1913,9 @@
       <c r="I27" t="n">
         <v>4.47</v>
       </c>
-      <c r="J27" t="inlineStr"/>
+      <c r="J27" t="n">
+        <v>0.004</v>
+      </c>
       <c r="K27" t="inlineStr">
         <is>
           <t>C078</t>
@@ -1915,7 +1967,9 @@
       <c r="I28" t="n">
         <v>5.17</v>
       </c>
-      <c r="J28" t="inlineStr"/>
+      <c r="J28" t="n">
+        <v>0.004</v>
+      </c>
       <c r="K28" t="inlineStr">
         <is>
           <t>C078</t>
@@ -1967,7 +2021,9 @@
       <c r="I29" t="n">
         <v>4.56</v>
       </c>
-      <c r="J29" t="inlineStr"/>
+      <c r="J29" t="n">
+        <v>0.008999999999999999</v>
+      </c>
       <c r="K29" t="inlineStr">
         <is>
           <t>C079</t>
@@ -2019,7 +2075,9 @@
       <c r="I30" t="n">
         <v>2.3</v>
       </c>
-      <c r="J30" t="inlineStr"/>
+      <c r="J30" t="n">
+        <v>0.008999999999999999</v>
+      </c>
       <c r="K30" t="inlineStr">
         <is>
           <t>C079</t>
@@ -2071,7 +2129,9 @@
       <c r="I31" t="n">
         <v>2.43</v>
       </c>
-      <c r="J31" t="inlineStr"/>
+      <c r="J31" t="n">
+        <v>0.008999999999999999</v>
+      </c>
       <c r="K31" t="inlineStr">
         <is>
           <t>C079</t>
@@ -2123,7 +2183,9 @@
       <c r="I32" t="n">
         <v>2.49</v>
       </c>
-      <c r="J32" t="inlineStr"/>
+      <c r="J32" t="n">
+        <v>0.008999999999999999</v>
+      </c>
       <c r="K32" t="inlineStr">
         <is>
           <t>C079</t>
@@ -2175,7 +2237,9 @@
       <c r="I33" t="n">
         <v>3.52</v>
       </c>
-      <c r="J33" t="inlineStr"/>
+      <c r="J33" t="n">
+        <v>0.008999999999999999</v>
+      </c>
       <c r="K33" t="inlineStr">
         <is>
           <t>C079</t>
@@ -2227,7 +2291,9 @@
       <c r="I34" t="n">
         <v>2.34</v>
       </c>
-      <c r="J34" t="inlineStr"/>
+      <c r="J34" t="n">
+        <v>0.008999999999999999</v>
+      </c>
       <c r="K34" t="inlineStr">
         <is>
           <t>C079</t>
@@ -2279,7 +2345,9 @@
       <c r="I35" t="n">
         <v>4.95</v>
       </c>
-      <c r="J35" t="inlineStr"/>
+      <c r="J35" t="n">
+        <v>0.008999999999999999</v>
+      </c>
       <c r="K35" t="inlineStr">
         <is>
           <t>C079</t>
@@ -2331,7 +2399,9 @@
       <c r="I36" t="n">
         <v>2.21</v>
       </c>
-      <c r="J36" t="inlineStr"/>
+      <c r="J36" t="n">
+        <v>0.008999999999999999</v>
+      </c>
       <c r="K36" t="inlineStr">
         <is>
           <t>C079</t>
@@ -2383,7 +2453,9 @@
       <c r="I37" t="n">
         <v>3.03</v>
       </c>
-      <c r="J37" t="inlineStr"/>
+      <c r="J37" t="n">
+        <v>0.008999999999999999</v>
+      </c>
       <c r="K37" t="inlineStr">
         <is>
           <t>C079</t>
@@ -2435,7 +2507,9 @@
       <c r="I38" t="n">
         <v>2.96</v>
       </c>
-      <c r="J38" t="inlineStr"/>
+      <c r="J38" t="n">
+        <v>0.008999999999999999</v>
+      </c>
       <c r="K38" t="inlineStr">
         <is>
           <t>C079</t>
@@ -2487,7 +2561,9 @@
       <c r="I39" t="n">
         <v>3.76</v>
       </c>
-      <c r="J39" t="inlineStr"/>
+      <c r="J39" t="n">
+        <v>0.008999999999999999</v>
+      </c>
       <c r="K39" t="inlineStr">
         <is>
           <t>C079</t>
@@ -2539,7 +2615,9 @@
       <c r="I40" t="n">
         <v>3.45</v>
       </c>
-      <c r="J40" t="inlineStr"/>
+      <c r="J40" t="n">
+        <v>0.008999999999999999</v>
+      </c>
       <c r="K40" t="inlineStr">
         <is>
           <t>C079</t>
@@ -2591,7 +2669,9 @@
       <c r="I41" t="n">
         <v>2.03</v>
       </c>
-      <c r="J41" t="inlineStr"/>
+      <c r="J41" t="n">
+        <v>0.008999999999999999</v>
+      </c>
       <c r="K41" t="inlineStr">
         <is>
           <t>C079</t>
@@ -2643,7 +2723,9 @@
       <c r="I42" t="n">
         <v>3.67</v>
       </c>
-      <c r="J42" t="inlineStr"/>
+      <c r="J42" t="n">
+        <v>0.008999999999999999</v>
+      </c>
       <c r="K42" t="inlineStr">
         <is>
           <t>C079</t>
@@ -2695,7 +2777,9 @@
       <c r="I43" t="n">
         <v>4.96</v>
       </c>
-      <c r="J43" t="inlineStr"/>
+      <c r="J43" t="n">
+        <v>0.008999999999999999</v>
+      </c>
       <c r="K43" t="inlineStr">
         <is>
           <t>C079</t>
@@ -2747,7 +2831,9 @@
       <c r="I44" t="n">
         <v>4.81</v>
       </c>
-      <c r="J44" t="inlineStr"/>
+      <c r="J44" t="n">
+        <v>0.008999999999999999</v>
+      </c>
       <c r="K44" t="inlineStr">
         <is>
           <t>C079</t>
@@ -2799,7 +2885,9 @@
       <c r="I45" t="n">
         <v>1.81</v>
       </c>
-      <c r="J45" t="inlineStr"/>
+      <c r="J45" t="n">
+        <v>0.008999999999999999</v>
+      </c>
       <c r="K45" t="inlineStr">
         <is>
           <t>C079</t>
@@ -2851,7 +2939,9 @@
       <c r="I46" t="n">
         <v>2.47</v>
       </c>
-      <c r="J46" t="inlineStr"/>
+      <c r="J46" t="n">
+        <v>0.008999999999999999</v>
+      </c>
       <c r="K46" t="inlineStr">
         <is>
           <t>C079</t>
@@ -2903,7 +2993,9 @@
       <c r="I47" t="n">
         <v>1.73</v>
       </c>
-      <c r="J47" t="inlineStr"/>
+      <c r="J47" t="n">
+        <v>0.008999999999999999</v>
+      </c>
       <c r="K47" t="inlineStr">
         <is>
           <t>C079</t>
@@ -2955,7 +3047,9 @@
       <c r="I48" t="n">
         <v>1.95</v>
       </c>
-      <c r="J48" t="inlineStr"/>
+      <c r="J48" t="n">
+        <v>0.008999999999999999</v>
+      </c>
       <c r="K48" t="inlineStr">
         <is>
           <t>C079</t>
@@ -3007,7 +3101,9 @@
       <c r="I49" t="n">
         <v>2.81</v>
       </c>
-      <c r="J49" t="inlineStr"/>
+      <c r="J49" t="n">
+        <v>0.008999999999999999</v>
+      </c>
       <c r="K49" t="inlineStr">
         <is>
           <t>C079</t>
@@ -3059,7 +3155,9 @@
       <c r="I50" t="n">
         <v>4.49</v>
       </c>
-      <c r="J50" t="inlineStr"/>
+      <c r="J50" t="n">
+        <v>0.008999999999999999</v>
+      </c>
       <c r="K50" t="inlineStr">
         <is>
           <t>C079</t>
@@ -3111,7 +3209,9 @@
       <c r="I51" t="n">
         <v>2.16</v>
       </c>
-      <c r="J51" t="inlineStr"/>
+      <c r="J51" t="n">
+        <v>0.008999999999999999</v>
+      </c>
       <c r="K51" t="inlineStr">
         <is>
           <t>C079</t>
@@ -3163,7 +3263,9 @@
       <c r="I52" t="n">
         <v>3.33</v>
       </c>
-      <c r="J52" t="inlineStr"/>
+      <c r="J52" t="n">
+        <v>0.008999999999999999</v>
+      </c>
       <c r="K52" t="inlineStr">
         <is>
           <t>C079</t>
@@ -3215,7 +3317,9 @@
       <c r="I53" t="n">
         <v>1.85</v>
       </c>
-      <c r="J53" t="inlineStr"/>
+      <c r="J53" t="n">
+        <v>0.008999999999999999</v>
+      </c>
       <c r="K53" t="inlineStr">
         <is>
           <t>C079</t>
@@ -3267,7 +3371,9 @@
       <c r="I54" t="n">
         <v>4</v>
       </c>
-      <c r="J54" t="inlineStr"/>
+      <c r="J54" t="n">
+        <v>0.008999999999999999</v>
+      </c>
       <c r="K54" t="inlineStr">
         <is>
           <t>C079</t>
@@ -3319,7 +3425,9 @@
       <c r="I55" t="n">
         <v>4.33</v>
       </c>
-      <c r="J55" t="inlineStr"/>
+      <c r="J55" t="n">
+        <v>0.008999999999999999</v>
+      </c>
       <c r="K55" t="inlineStr">
         <is>
           <t>C079</t>
@@ -3371,7 +3479,9 @@
       <c r="I56" t="n">
         <v>4.64</v>
       </c>
-      <c r="J56" t="inlineStr"/>
+      <c r="J56" t="n">
+        <v>0.008999999999999999</v>
+      </c>
       <c r="K56" t="inlineStr">
         <is>
           <t>C079</t>
@@ -3423,7 +3533,9 @@
       <c r="I57" t="n">
         <v>4.68</v>
       </c>
-      <c r="J57" t="inlineStr"/>
+      <c r="J57" t="n">
+        <v>0.004</v>
+      </c>
       <c r="K57" t="inlineStr">
         <is>
           <t>C080</t>
@@ -3475,7 +3587,9 @@
       <c r="I58" t="n">
         <v>3.48</v>
       </c>
-      <c r="J58" t="inlineStr"/>
+      <c r="J58" t="n">
+        <v>0.004</v>
+      </c>
       <c r="K58" t="inlineStr">
         <is>
           <t>C080</t>
@@ -3527,7 +3641,9 @@
       <c r="I59" t="n">
         <v>3.35</v>
       </c>
-      <c r="J59" t="inlineStr"/>
+      <c r="J59" t="n">
+        <v>0.004</v>
+      </c>
       <c r="K59" t="inlineStr">
         <is>
           <t>C080</t>
@@ -3579,7 +3695,9 @@
       <c r="I60" t="n">
         <v>3.59</v>
       </c>
-      <c r="J60" t="inlineStr"/>
+      <c r="J60" t="n">
+        <v>0.004</v>
+      </c>
       <c r="K60" t="inlineStr">
         <is>
           <t>C080</t>
@@ -3631,7 +3749,9 @@
       <c r="I61" t="n">
         <v>4.39</v>
       </c>
-      <c r="J61" t="inlineStr"/>
+      <c r="J61" t="n">
+        <v>0.004</v>
+      </c>
       <c r="K61" t="inlineStr">
         <is>
           <t>C080</t>
@@ -3683,7 +3803,9 @@
       <c r="I62" t="n">
         <v>3.98</v>
       </c>
-      <c r="J62" t="inlineStr"/>
+      <c r="J62" t="n">
+        <v>0.004</v>
+      </c>
       <c r="K62" t="inlineStr">
         <is>
           <t>C080</t>
@@ -3735,7 +3857,9 @@
       <c r="I63" t="n">
         <v>4.64</v>
       </c>
-      <c r="J63" t="inlineStr"/>
+      <c r="J63" t="n">
+        <v>0.004</v>
+      </c>
       <c r="K63" t="inlineStr">
         <is>
           <t>C080</t>
@@ -3787,7 +3911,9 @@
       <c r="I64" t="n">
         <v>4.34</v>
       </c>
-      <c r="J64" t="inlineStr"/>
+      <c r="J64" t="n">
+        <v>0.004</v>
+      </c>
       <c r="K64" t="inlineStr">
         <is>
           <t>C080</t>
@@ -3839,7 +3965,9 @@
       <c r="I65" t="n">
         <v>4.31</v>
       </c>
-      <c r="J65" t="inlineStr"/>
+      <c r="J65" t="n">
+        <v>0.004</v>
+      </c>
       <c r="K65" t="inlineStr">
         <is>
           <t>C080</t>
@@ -3891,7 +4019,9 @@
       <c r="I66" t="n">
         <v>4.23</v>
       </c>
-      <c r="J66" t="inlineStr"/>
+      <c r="J66" t="n">
+        <v>0.004</v>
+      </c>
       <c r="K66" t="inlineStr">
         <is>
           <t>C080</t>
@@ -3943,7 +4073,9 @@
       <c r="I67" t="n">
         <v>4.27</v>
       </c>
-      <c r="J67" t="inlineStr"/>
+      <c r="J67" t="n">
+        <v>0.004</v>
+      </c>
       <c r="K67" t="inlineStr">
         <is>
           <t>C080</t>
@@ -3995,7 +4127,9 @@
       <c r="I68" t="n">
         <v>3.26</v>
       </c>
-      <c r="J68" t="inlineStr"/>
+      <c r="J68" t="n">
+        <v>0.004</v>
+      </c>
       <c r="K68" t="inlineStr">
         <is>
           <t>C080</t>
@@ -4047,7 +4181,9 @@
       <c r="I69" t="n">
         <v>4.73</v>
       </c>
-      <c r="J69" t="inlineStr"/>
+      <c r="J69" t="n">
+        <v>0.004</v>
+      </c>
       <c r="K69" t="inlineStr">
         <is>
           <t>C080</t>
@@ -4099,7 +4235,9 @@
       <c r="I70" t="n">
         <v>5.05</v>
       </c>
-      <c r="J70" t="inlineStr"/>
+      <c r="J70" t="n">
+        <v>0.004</v>
+      </c>
       <c r="K70" t="inlineStr">
         <is>
           <t>C080</t>
@@ -4151,7 +4289,9 @@
       <c r="I71" t="n">
         <v>5.05</v>
       </c>
-      <c r="J71" t="inlineStr"/>
+      <c r="J71" t="n">
+        <v>0.004</v>
+      </c>
       <c r="K71" t="inlineStr">
         <is>
           <t>C080</t>
@@ -4203,7 +4343,9 @@
       <c r="I72" t="n">
         <v>4.1</v>
       </c>
-      <c r="J72" t="inlineStr"/>
+      <c r="J72" t="n">
+        <v>0.004</v>
+      </c>
       <c r="K72" t="inlineStr">
         <is>
           <t>C080</t>
@@ -4255,7 +4397,9 @@
       <c r="I73" t="n">
         <v>5.49</v>
       </c>
-      <c r="J73" t="inlineStr"/>
+      <c r="J73" t="n">
+        <v>0.004</v>
+      </c>
       <c r="K73" t="inlineStr">
         <is>
           <t>C080</t>
@@ -4307,7 +4451,9 @@
       <c r="I74" t="n">
         <v>3.2</v>
       </c>
-      <c r="J74" t="inlineStr"/>
+      <c r="J74" t="n">
+        <v>0.004</v>
+      </c>
       <c r="K74" t="inlineStr">
         <is>
           <t>C080</t>
@@ -4359,7 +4505,9 @@
       <c r="I75" t="n">
         <v>4.77</v>
       </c>
-      <c r="J75" t="inlineStr"/>
+      <c r="J75" t="n">
+        <v>0.004</v>
+      </c>
       <c r="K75" t="inlineStr">
         <is>
           <t>C080</t>
@@ -4411,7 +4559,9 @@
       <c r="I76" t="n">
         <v>4.49</v>
       </c>
-      <c r="J76" t="inlineStr"/>
+      <c r="J76" t="n">
+        <v>0.004</v>
+      </c>
       <c r="K76" t="inlineStr">
         <is>
           <t>C080</t>
@@ -4463,7 +4613,9 @@
       <c r="I77" t="n">
         <v>4.99</v>
       </c>
-      <c r="J77" t="inlineStr"/>
+      <c r="J77" t="n">
+        <v>0.004</v>
+      </c>
       <c r="K77" t="inlineStr">
         <is>
           <t>C080</t>
@@ -4515,7 +4667,9 @@
       <c r="I78" t="n">
         <v>4.48</v>
       </c>
-      <c r="J78" t="inlineStr"/>
+      <c r="J78" t="n">
+        <v>0.004</v>
+      </c>
       <c r="K78" t="inlineStr">
         <is>
           <t>C080</t>
@@ -4567,7 +4721,9 @@
       <c r="I79" t="n">
         <v>4.62</v>
       </c>
-      <c r="J79" t="inlineStr"/>
+      <c r="J79" t="n">
+        <v>0.004</v>
+      </c>
       <c r="K79" t="inlineStr">
         <is>
           <t>C080</t>
@@ -4619,7 +4775,9 @@
       <c r="I80" t="n">
         <v>2.16</v>
       </c>
-      <c r="J80" t="inlineStr"/>
+      <c r="J80" t="n">
+        <v>0.004</v>
+      </c>
       <c r="K80" t="inlineStr">
         <is>
           <t>C080</t>
@@ -4671,7 +4829,9 @@
       <c r="I81" t="n">
         <v>3.98</v>
       </c>
-      <c r="J81" t="inlineStr"/>
+      <c r="J81" t="n">
+        <v>0.004</v>
+      </c>
       <c r="K81" t="inlineStr">
         <is>
           <t>C080</t>
@@ -4723,7 +4883,9 @@
       <c r="I82" t="n">
         <v>3.87</v>
       </c>
-      <c r="J82" t="inlineStr"/>
+      <c r="J82" t="n">
+        <v>0.004</v>
+      </c>
       <c r="K82" t="inlineStr">
         <is>
           <t>C080</t>
@@ -4775,7 +4937,9 @@
       <c r="I83" t="n">
         <v>4.54</v>
       </c>
-      <c r="J83" t="inlineStr"/>
+      <c r="J83" t="n">
+        <v>0.004</v>
+      </c>
       <c r="K83" t="inlineStr">
         <is>
           <t>C080</t>
@@ -4827,7 +4991,9 @@
       <c r="I84" t="n">
         <v>5.18</v>
       </c>
-      <c r="J84" t="inlineStr"/>
+      <c r="J84" t="n">
+        <v>0.004</v>
+      </c>
       <c r="K84" t="inlineStr">
         <is>
           <t>C080</t>
@@ -6281,7 +6447,9 @@
       <c r="I113" t="n">
         <v>3.22</v>
       </c>
-      <c r="J113" t="inlineStr"/>
+      <c r="J113" t="n">
+        <v>2</v>
+      </c>
       <c r="K113" t="inlineStr">
         <is>
           <t>C099</t>
@@ -6335,7 +6503,9 @@
       <c r="I114" t="n">
         <v>3.814</v>
       </c>
-      <c r="J114" t="inlineStr"/>
+      <c r="J114" t="n">
+        <v>2</v>
+      </c>
       <c r="K114" t="inlineStr">
         <is>
           <t>C099</t>
@@ -6389,7 +6559,9 @@
       <c r="I115" t="n">
         <v>3.631</v>
       </c>
-      <c r="J115" t="inlineStr"/>
+      <c r="J115" t="n">
+        <v>2</v>
+      </c>
       <c r="K115" t="inlineStr">
         <is>
           <t>C099</t>
@@ -6443,7 +6615,9 @@
       <c r="I116" t="n">
         <v>2.329</v>
       </c>
-      <c r="J116" t="inlineStr"/>
+      <c r="J116" t="n">
+        <v>2</v>
+      </c>
       <c r="K116" t="inlineStr">
         <is>
           <t>C099</t>
@@ -6497,7 +6671,9 @@
       <c r="I117" t="n">
         <v>2.9</v>
       </c>
-      <c r="J117" t="inlineStr"/>
+      <c r="J117" t="n">
+        <v>2</v>
+      </c>
       <c r="K117" t="inlineStr">
         <is>
           <t>C099</t>
@@ -6551,7 +6727,9 @@
       <c r="I118" t="n">
         <v>2.484</v>
       </c>
-      <c r="J118" t="inlineStr"/>
+      <c r="J118" t="n">
+        <v>2</v>
+      </c>
       <c r="K118" t="inlineStr">
         <is>
           <t>C099</t>
@@ -6605,7 +6783,9 @@
       <c r="I119" t="n">
         <v>2.694</v>
       </c>
-      <c r="J119" t="inlineStr"/>
+      <c r="J119" t="n">
+        <v>2</v>
+      </c>
       <c r="K119" t="inlineStr">
         <is>
           <t>C099</t>
@@ -6659,7 +6839,9 @@
       <c r="I120" t="n">
         <v>3.146</v>
       </c>
-      <c r="J120" t="inlineStr"/>
+      <c r="J120" t="n">
+        <v>2</v>
+      </c>
       <c r="K120" t="inlineStr">
         <is>
           <t>C099</t>
@@ -6713,7 +6895,9 @@
       <c r="I121" t="n">
         <v>3.616</v>
       </c>
-      <c r="J121" t="inlineStr"/>
+      <c r="J121" t="n">
+        <v>2</v>
+      </c>
       <c r="K121" t="inlineStr">
         <is>
           <t>C099</t>
@@ -6767,7 +6951,9 @@
       <c r="I122" t="n">
         <v>3.794</v>
       </c>
-      <c r="J122" t="inlineStr"/>
+      <c r="J122" t="n">
+        <v>2</v>
+      </c>
       <c r="K122" t="inlineStr">
         <is>
           <t>C099</t>
@@ -6821,7 +7007,9 @@
       <c r="I123" t="n">
         <v>3.551</v>
       </c>
-      <c r="J123" t="inlineStr"/>
+      <c r="J123" t="n">
+        <v>2</v>
+      </c>
       <c r="K123" t="inlineStr">
         <is>
           <t>C099</t>
@@ -6875,7 +7063,9 @@
       <c r="I124" t="n">
         <v>2.948</v>
       </c>
-      <c r="J124" t="inlineStr"/>
+      <c r="J124" t="n">
+        <v>2</v>
+      </c>
       <c r="K124" t="inlineStr">
         <is>
           <t>C099</t>
@@ -6929,7 +7119,9 @@
       <c r="I125" t="n">
         <v>3.744</v>
       </c>
-      <c r="J125" t="inlineStr"/>
+      <c r="J125" t="n">
+        <v>2</v>
+      </c>
       <c r="K125" t="inlineStr">
         <is>
           <t>C099</t>
@@ -6983,7 +7175,9 @@
       <c r="I126" t="n">
         <v>3.917</v>
       </c>
-      <c r="J126" t="inlineStr"/>
+      <c r="J126" t="n">
+        <v>2</v>
+      </c>
       <c r="K126" t="inlineStr">
         <is>
           <t>C099</t>
@@ -7037,7 +7231,9 @@
       <c r="I127" t="n">
         <v>3.879</v>
       </c>
-      <c r="J127" t="inlineStr"/>
+      <c r="J127" t="n">
+        <v>2</v>
+      </c>
       <c r="K127" t="inlineStr">
         <is>
           <t>C099</t>
@@ -7091,7 +7287,9 @@
       <c r="I128" t="n">
         <v>3.525</v>
       </c>
-      <c r="J128" t="inlineStr"/>
+      <c r="J128" t="n">
+        <v>2</v>
+      </c>
       <c r="K128" t="inlineStr">
         <is>
           <t>C099</t>
@@ -7145,7 +7343,9 @@
       <c r="I129" t="n">
         <v>3.823</v>
       </c>
-      <c r="J129" t="inlineStr"/>
+      <c r="J129" t="n">
+        <v>2</v>
+      </c>
       <c r="K129" t="inlineStr">
         <is>
           <t>C099</t>
@@ -7199,7 +7399,9 @@
       <c r="I130" t="n">
         <v>3.019</v>
       </c>
-      <c r="J130" t="inlineStr"/>
+      <c r="J130" t="n">
+        <v>2</v>
+      </c>
       <c r="K130" t="inlineStr">
         <is>
           <t>C099</t>
@@ -7253,7 +7455,9 @@
       <c r="I131" t="n">
         <v>4.238</v>
       </c>
-      <c r="J131" t="inlineStr"/>
+      <c r="J131" t="n">
+        <v>2</v>
+      </c>
       <c r="K131" t="inlineStr">
         <is>
           <t>C099</t>
@@ -7307,7 +7511,9 @@
       <c r="I132" t="n">
         <v>3.979</v>
       </c>
-      <c r="J132" t="inlineStr"/>
+      <c r="J132" t="n">
+        <v>2</v>
+      </c>
       <c r="K132" t="inlineStr">
         <is>
           <t>C099</t>
@@ -7361,7 +7567,9 @@
       <c r="I133" t="n">
         <v>3.423</v>
       </c>
-      <c r="J133" t="inlineStr"/>
+      <c r="J133" t="n">
+        <v>2</v>
+      </c>
       <c r="K133" t="inlineStr">
         <is>
           <t>C099</t>
@@ -7415,7 +7623,9 @@
       <c r="I134" t="n">
         <v>3.431</v>
       </c>
-      <c r="J134" t="inlineStr"/>
+      <c r="J134" t="n">
+        <v>2</v>
+      </c>
       <c r="K134" t="inlineStr">
         <is>
           <t>C099</t>
@@ -7469,7 +7679,9 @@
       <c r="I135" t="n">
         <v>3.69</v>
       </c>
-      <c r="J135" t="inlineStr"/>
+      <c r="J135" t="n">
+        <v>2</v>
+      </c>
       <c r="K135" t="inlineStr">
         <is>
           <t>C099</t>
@@ -7523,7 +7735,9 @@
       <c r="I136" t="n">
         <v>3.308</v>
       </c>
-      <c r="J136" t="inlineStr"/>
+      <c r="J136" t="n">
+        <v>2</v>
+      </c>
       <c r="K136" t="inlineStr">
         <is>
           <t>C099</t>
@@ -7577,7 +7791,9 @@
       <c r="I137" t="n">
         <v>3.36</v>
       </c>
-      <c r="J137" t="inlineStr"/>
+      <c r="J137" t="n">
+        <v>2</v>
+      </c>
       <c r="K137" t="inlineStr">
         <is>
           <t>C099</t>
@@ -7631,7 +7847,9 @@
       <c r="I138" t="n">
         <v>3.442</v>
       </c>
-      <c r="J138" t="inlineStr"/>
+      <c r="J138" t="n">
+        <v>2</v>
+      </c>
       <c r="K138" t="inlineStr">
         <is>
           <t>C099</t>
@@ -7685,7 +7903,9 @@
       <c r="I139" t="n">
         <v>3.356</v>
       </c>
-      <c r="J139" t="inlineStr"/>
+      <c r="J139" t="n">
+        <v>2</v>
+      </c>
       <c r="K139" t="inlineStr">
         <is>
           <t>C099</t>
@@ -7739,7 +7959,9 @@
       <c r="I140" t="n">
         <v>2.65</v>
       </c>
-      <c r="J140" t="inlineStr"/>
+      <c r="J140" t="n">
+        <v>2</v>
+      </c>
       <c r="K140" t="inlineStr">
         <is>
           <t>C099</t>
@@ -7793,7 +8015,9 @@
       <c r="I141" t="n">
         <v>3.064</v>
       </c>
-      <c r="J141" t="inlineStr"/>
+      <c r="J141" t="n">
+        <v>2</v>
+      </c>
       <c r="K141" t="inlineStr">
         <is>
           <t>C099</t>
@@ -7847,7 +8071,9 @@
       <c r="I142" t="n">
         <v>3.09</v>
       </c>
-      <c r="J142" t="inlineStr"/>
+      <c r="J142" t="n">
+        <v>2</v>
+      </c>
       <c r="K142" t="inlineStr">
         <is>
           <t>C099</t>
@@ -7901,7 +8127,9 @@
       <c r="I143" t="n">
         <v>2.249</v>
       </c>
-      <c r="J143" t="inlineStr"/>
+      <c r="J143" t="n">
+        <v>2</v>
+      </c>
       <c r="K143" t="inlineStr">
         <is>
           <t>C099</t>
@@ -7955,7 +8183,9 @@
       <c r="I144" t="n">
         <v>2.984</v>
       </c>
-      <c r="J144" t="inlineStr"/>
+      <c r="J144" t="n">
+        <v>2</v>
+      </c>
       <c r="K144" t="inlineStr">
         <is>
           <t>C099</t>
@@ -8009,7 +8239,9 @@
       <c r="I145" t="n">
         <v>3.616</v>
       </c>
-      <c r="J145" t="inlineStr"/>
+      <c r="J145" t="n">
+        <v>2</v>
+      </c>
       <c r="K145" t="inlineStr">
         <is>
           <t>C099</t>
@@ -8063,7 +8295,9 @@
       <c r="I146" t="n">
         <v>3.903</v>
       </c>
-      <c r="J146" t="inlineStr"/>
+      <c r="J146" t="n">
+        <v>2</v>
+      </c>
       <c r="K146" t="inlineStr">
         <is>
           <t>C099</t>
@@ -8117,7 +8351,9 @@
       <c r="I147" t="n">
         <v>2.98</v>
       </c>
-      <c r="J147" t="inlineStr"/>
+      <c r="J147" t="n">
+        <v>2</v>
+      </c>
       <c r="K147" t="inlineStr">
         <is>
           <t>C099</t>
@@ -8171,7 +8407,9 @@
       <c r="I148" t="n">
         <v>4.067</v>
       </c>
-      <c r="J148" t="inlineStr"/>
+      <c r="J148" t="n">
+        <v>2</v>
+      </c>
       <c r="K148" t="inlineStr">
         <is>
           <t>C099</t>
@@ -8225,7 +8463,9 @@
       <c r="I149" t="n">
         <v>3.466</v>
       </c>
-      <c r="J149" t="inlineStr"/>
+      <c r="J149" t="n">
+        <v>2</v>
+      </c>
       <c r="K149" t="inlineStr">
         <is>
           <t>C099</t>
@@ -8279,7 +8519,9 @@
       <c r="I150" t="n">
         <v>3.968</v>
       </c>
-      <c r="J150" t="inlineStr"/>
+      <c r="J150" t="n">
+        <v>2</v>
+      </c>
       <c r="K150" t="inlineStr">
         <is>
           <t>C099</t>
@@ -8333,7 +8575,9 @@
       <c r="I151" t="n">
         <v>3.385</v>
       </c>
-      <c r="J151" t="inlineStr"/>
+      <c r="J151" t="n">
+        <v>2</v>
+      </c>
       <c r="K151" t="inlineStr">
         <is>
           <t>C099</t>
@@ -8387,7 +8631,9 @@
       <c r="I152" t="n">
         <v>3.952</v>
       </c>
-      <c r="J152" t="inlineStr"/>
+      <c r="J152" t="n">
+        <v>2</v>
+      </c>
       <c r="K152" t="inlineStr">
         <is>
           <t>C099</t>
@@ -8441,7 +8687,9 @@
       <c r="I153" t="n">
         <v>3.032</v>
       </c>
-      <c r="J153" t="inlineStr"/>
+      <c r="J153" t="n">
+        <v>2</v>
+      </c>
       <c r="K153" t="inlineStr">
         <is>
           <t>C099</t>
@@ -8495,7 +8743,9 @@
       <c r="I154" t="n">
         <v>3.158</v>
       </c>
-      <c r="J154" t="inlineStr"/>
+      <c r="J154" t="n">
+        <v>2</v>
+      </c>
       <c r="K154" t="inlineStr">
         <is>
           <t>C099</t>
@@ -8549,7 +8799,9 @@
       <c r="I155" t="n">
         <v>4.06</v>
       </c>
-      <c r="J155" t="inlineStr"/>
+      <c r="J155" t="n">
+        <v>2</v>
+      </c>
       <c r="K155" t="inlineStr">
         <is>
           <t>C099</t>
@@ -8603,7 +8855,9 @@
       <c r="I156" t="n">
         <v>3.386</v>
       </c>
-      <c r="J156" t="inlineStr"/>
+      <c r="J156" t="n">
+        <v>2</v>
+      </c>
       <c r="K156" t="inlineStr">
         <is>
           <t>C099</t>
@@ -8657,7 +8911,9 @@
       <c r="I157" t="n">
         <v>4.835</v>
       </c>
-      <c r="J157" t="inlineStr"/>
+      <c r="J157" t="n">
+        <v>2</v>
+      </c>
       <c r="K157" t="inlineStr">
         <is>
           <t>C099</t>
@@ -8711,7 +8967,9 @@
       <c r="I158" t="n">
         <v>2.5</v>
       </c>
-      <c r="J158" t="inlineStr"/>
+      <c r="J158" t="n">
+        <v>2</v>
+      </c>
       <c r="K158" t="inlineStr">
         <is>
           <t>C099</t>
@@ -8765,7 +9023,9 @@
       <c r="I159" t="n">
         <v>3.603</v>
       </c>
-      <c r="J159" t="inlineStr"/>
+      <c r="J159" t="n">
+        <v>2</v>
+      </c>
       <c r="K159" t="inlineStr">
         <is>
           <t>C099</t>
@@ -8819,7 +9079,9 @@
       <c r="I160" t="n">
         <v>3.361</v>
       </c>
-      <c r="J160" t="inlineStr"/>
+      <c r="J160" t="n">
+        <v>2</v>
+      </c>
       <c r="K160" t="inlineStr">
         <is>
           <t>C099</t>
@@ -8873,7 +9135,9 @@
       <c r="I161" t="n">
         <v>3.767</v>
       </c>
-      <c r="J161" t="inlineStr"/>
+      <c r="J161" t="n">
+        <v>2</v>
+      </c>
       <c r="K161" t="inlineStr">
         <is>
           <t>C099</t>
@@ -8927,7 +9191,9 @@
       <c r="I162" t="n">
         <v>4.204</v>
       </c>
-      <c r="J162" t="inlineStr"/>
+      <c r="J162" t="n">
+        <v>2</v>
+      </c>
       <c r="K162" t="inlineStr">
         <is>
           <t>C099</t>
@@ -8981,7 +9247,9 @@
       <c r="I163" t="n">
         <v>3.129</v>
       </c>
-      <c r="J163" t="inlineStr"/>
+      <c r="J163" t="n">
+        <v>2</v>
+      </c>
       <c r="K163" t="inlineStr">
         <is>
           <t>C099</t>
@@ -9035,7 +9303,9 @@
       <c r="I164" t="n">
         <v>2.966</v>
       </c>
-      <c r="J164" t="inlineStr"/>
+      <c r="J164" t="n">
+        <v>2</v>
+      </c>
       <c r="K164" t="inlineStr">
         <is>
           <t>C099</t>
@@ -9089,7 +9359,9 @@
       <c r="I165" t="n">
         <v>2.943</v>
       </c>
-      <c r="J165" t="inlineStr"/>
+      <c r="J165" t="n">
+        <v>2</v>
+      </c>
       <c r="K165" t="inlineStr">
         <is>
           <t>C099</t>
@@ -9143,7 +9415,9 @@
       <c r="I166" t="n">
         <v>3.06</v>
       </c>
-      <c r="J166" t="inlineStr"/>
+      <c r="J166" t="n">
+        <v>2</v>
+      </c>
       <c r="K166" t="inlineStr">
         <is>
           <t>C099</t>
@@ -9197,7 +9471,9 @@
       <c r="I167" t="n">
         <v>2.68</v>
       </c>
-      <c r="J167" t="inlineStr"/>
+      <c r="J167" t="n">
+        <v>2</v>
+      </c>
       <c r="K167" t="inlineStr">
         <is>
           <t>C099</t>
@@ -9251,7 +9527,9 @@
       <c r="I168" t="n">
         <v>3.503</v>
       </c>
-      <c r="J168" t="inlineStr"/>
+      <c r="J168" t="n">
+        <v>2</v>
+      </c>
       <c r="K168" t="inlineStr">
         <is>
           <t>C099</t>
@@ -9305,7 +9583,9 @@
       <c r="I169" t="n">
         <v>3.404</v>
       </c>
-      <c r="J169" t="inlineStr"/>
+      <c r="J169" t="n">
+        <v>2</v>
+      </c>
       <c r="K169" t="inlineStr">
         <is>
           <t>C099</t>
@@ -20411,11 +20691,7 @@
       <c r="I387" t="n">
         <v>3.175</v>
       </c>
-      <c r="J387" t="inlineStr">
-        <is>
-          <t>one saturable site assumed for the specific term</t>
-        </is>
-      </c>
+      <c r="J387" t="inlineStr"/>
       <c r="K387" t="inlineStr">
         <is>
           <t>C057</t>
@@ -20519,11 +20795,7 @@
       <c r="I389" t="n">
         <v>2.305</v>
       </c>
-      <c r="J389" t="inlineStr">
-        <is>
-          <t>one saturable site assumed for the specific term</t>
-        </is>
-      </c>
+      <c r="J389" t="inlineStr"/>
       <c r="K389" t="inlineStr">
         <is>
           <t>C057</t>
@@ -20677,11 +20949,7 @@
       <c r="I392" t="n">
         <v>3.985</v>
       </c>
-      <c r="J392" t="inlineStr">
-        <is>
-          <t>one saturable site assumed for the specific term</t>
-        </is>
-      </c>
+      <c r="J392" t="inlineStr"/>
       <c r="K392" t="inlineStr">
         <is>
           <t>C057</t>
@@ -20835,11 +21103,7 @@
       <c r="I395" t="n">
         <v>3.125</v>
       </c>
-      <c r="J395" t="inlineStr">
-        <is>
-          <t>one saturable site assumed for the specific term</t>
-        </is>
-      </c>
+      <c r="J395" t="inlineStr"/>
       <c r="K395" t="inlineStr">
         <is>
           <t>C057</t>
@@ -20993,11 +21257,7 @@
       <c r="I398" t="n">
         <v>4.885</v>
       </c>
-      <c r="J398" t="inlineStr">
-        <is>
-          <t>one saturable site assumed for the specific term</t>
-        </is>
-      </c>
+      <c r="J398" t="inlineStr"/>
       <c r="K398" t="inlineStr">
         <is>
           <t>C057</t>
@@ -21253,11 +21513,7 @@
       <c r="I403" t="n">
         <v>4.445</v>
       </c>
-      <c r="J403" t="inlineStr">
-        <is>
-          <t>one saturable site assumed for the specific term</t>
-        </is>
-      </c>
+      <c r="J403" t="inlineStr"/>
       <c r="K403" t="inlineStr">
         <is>
           <t>C057</t>
@@ -21411,11 +21667,7 @@
       <c r="I406" t="n">
         <v>5.135</v>
       </c>
-      <c r="J406" t="inlineStr">
-        <is>
-          <t>one saturable site assumed for the specific term</t>
-        </is>
-      </c>
+      <c r="J406" t="inlineStr"/>
       <c r="K406" t="inlineStr">
         <is>
           <t>C057</t>
@@ -22081,11 +22333,7 @@
       <c r="I419" t="n">
         <v>3.215</v>
       </c>
-      <c r="J419" t="inlineStr">
-        <is>
-          <t>one saturable site assumed for the specific term</t>
-        </is>
-      </c>
+      <c r="J419" t="inlineStr"/>
       <c r="K419" t="inlineStr">
         <is>
           <t>C060</t>
@@ -22189,11 +22437,7 @@
       <c r="I421" t="n">
         <v>2.065</v>
       </c>
-      <c r="J421" t="inlineStr">
-        <is>
-          <t>one saturable site assumed for the specific term</t>
-        </is>
-      </c>
+      <c r="J421" t="inlineStr"/>
       <c r="K421" t="inlineStr">
         <is>
           <t>C060</t>
@@ -22347,11 +22591,7 @@
       <c r="I424" t="n">
         <v>3.965</v>
       </c>
-      <c r="J424" t="inlineStr">
-        <is>
-          <t>one saturable site assumed for the specific term</t>
-        </is>
-      </c>
+      <c r="J424" t="inlineStr"/>
       <c r="K424" t="inlineStr">
         <is>
           <t>C060</t>
@@ -22505,11 +22745,7 @@
       <c r="I427" t="n">
         <v>3.055</v>
       </c>
-      <c r="J427" t="inlineStr">
-        <is>
-          <t>one saturable site assumed for the specific term</t>
-        </is>
-      </c>
+      <c r="J427" t="inlineStr"/>
       <c r="K427" t="inlineStr">
         <is>
           <t>C060</t>
@@ -22663,11 +22899,7 @@
       <c r="I430" t="n">
         <v>4.845</v>
       </c>
-      <c r="J430" t="inlineStr">
-        <is>
-          <t>one saturable site assumed for the specific term</t>
-        </is>
-      </c>
+      <c r="J430" t="inlineStr"/>
       <c r="K430" t="inlineStr">
         <is>
           <t>C060</t>
@@ -22923,11 +23155,7 @@
       <c r="I435" t="n">
         <v>4.315</v>
       </c>
-      <c r="J435" t="inlineStr">
-        <is>
-          <t>one saturable site assumed for the specific term</t>
-        </is>
-      </c>
+      <c r="J435" t="inlineStr"/>
       <c r="K435" t="inlineStr">
         <is>
           <t>C060</t>
@@ -23081,11 +23309,7 @@
       <c r="I438" t="n">
         <v>4.685</v>
       </c>
-      <c r="J438" t="inlineStr">
-        <is>
-          <t>one saturable site assumed for the specific term</t>
-        </is>
-      </c>
+      <c r="J438" t="inlineStr"/>
       <c r="K438" t="inlineStr">
         <is>
           <t>C060</t>
@@ -23751,11 +23975,7 @@
       <c r="I451" t="n">
         <v>3.425</v>
       </c>
-      <c r="J451" t="inlineStr">
-        <is>
-          <t>one saturable site assumed for the specific term</t>
-        </is>
-      </c>
+      <c r="J451" t="inlineStr"/>
       <c r="K451" t="inlineStr">
         <is>
           <t>C063</t>
@@ -24471,11 +24691,7 @@
       <c r="I465" t="n">
         <v>5.355</v>
       </c>
-      <c r="J465" t="inlineStr">
-        <is>
-          <t>one saturable site assumed for the specific term</t>
-        </is>
-      </c>
+      <c r="J465" t="inlineStr"/>
       <c r="K465" t="inlineStr">
         <is>
           <t>C063</t>
@@ -24831,7 +25047,9 @@
       </c>
       <c r="H472" t="inlineStr"/>
       <c r="I472" t="inlineStr"/>
-      <c r="J472" t="inlineStr"/>
+      <c r="J472" t="n">
+        <v>5.556</v>
+      </c>
       <c r="K472" t="inlineStr">
         <is>
           <t>C086</t>
@@ -24883,7 +25101,9 @@
         <v>1390</v>
       </c>
       <c r="I473" t="inlineStr"/>
-      <c r="J473" t="inlineStr"/>
+      <c r="J473" t="n">
+        <v>5.556</v>
+      </c>
       <c r="K473" t="inlineStr">
         <is>
           <t>C086</t>
@@ -24935,7 +25155,9 @@
         <v>2550</v>
       </c>
       <c r="I474" t="inlineStr"/>
-      <c r="J474" t="inlineStr"/>
+      <c r="J474" t="n">
+        <v>5.556</v>
+      </c>
       <c r="K474" t="inlineStr">
         <is>
           <t>C086</t>
@@ -24987,7 +25209,9 @@
         <v>3060</v>
       </c>
       <c r="I475" t="inlineStr"/>
-      <c r="J475" t="inlineStr"/>
+      <c r="J475" t="n">
+        <v>5.556</v>
+      </c>
       <c r="K475" t="inlineStr">
         <is>
           <t>C086</t>
@@ -25039,7 +25263,9 @@
         <v>800</v>
       </c>
       <c r="I476" t="inlineStr"/>
-      <c r="J476" t="inlineStr"/>
+      <c r="J476" t="n">
+        <v>5.556</v>
+      </c>
       <c r="K476" t="inlineStr">
         <is>
           <t>C086</t>
@@ -25091,7 +25317,9 @@
         <v>2170</v>
       </c>
       <c r="I477" t="inlineStr"/>
-      <c r="J477" t="inlineStr"/>
+      <c r="J477" t="n">
+        <v>5.556</v>
+      </c>
       <c r="K477" t="inlineStr">
         <is>
           <t>C086</t>
@@ -25143,7 +25371,9 @@
         <v>990</v>
       </c>
       <c r="I478" t="inlineStr"/>
-      <c r="J478" t="inlineStr"/>
+      <c r="J478" t="n">
+        <v>5.556</v>
+      </c>
       <c r="K478" t="inlineStr">
         <is>
           <t>C086</t>
@@ -25195,7 +25425,9 @@
         <v>860</v>
       </c>
       <c r="I479" t="inlineStr"/>
-      <c r="J479" t="inlineStr"/>
+      <c r="J479" t="n">
+        <v>5.556</v>
+      </c>
       <c r="K479" t="inlineStr">
         <is>
           <t>C086</t>
@@ -25245,7 +25477,9 @@
       </c>
       <c r="H480" t="inlineStr"/>
       <c r="I480" t="inlineStr"/>
-      <c r="J480" t="inlineStr"/>
+      <c r="J480" t="n">
+        <v>7.692</v>
+      </c>
       <c r="K480" t="inlineStr">
         <is>
           <t>C087</t>
@@ -25297,7 +25531,9 @@
         <v>410</v>
       </c>
       <c r="I481" t="inlineStr"/>
-      <c r="J481" t="inlineStr"/>
+      <c r="J481" t="n">
+        <v>7.692</v>
+      </c>
       <c r="K481" t="inlineStr">
         <is>
           <t>C087</t>
@@ -25349,7 +25585,9 @@
         <v>1570</v>
       </c>
       <c r="I482" t="inlineStr"/>
-      <c r="J482" t="inlineStr"/>
+      <c r="J482" t="n">
+        <v>7.692</v>
+      </c>
       <c r="K482" t="inlineStr">
         <is>
           <t>C087</t>
@@ -25401,7 +25639,9 @@
         <v>2640</v>
       </c>
       <c r="I483" t="inlineStr"/>
-      <c r="J483" t="inlineStr"/>
+      <c r="J483" t="n">
+        <v>7.692</v>
+      </c>
       <c r="K483" t="inlineStr">
         <is>
           <t>C087</t>
@@ -25453,7 +25693,9 @@
         <v>1680</v>
       </c>
       <c r="I484" t="inlineStr"/>
-      <c r="J484" t="inlineStr"/>
+      <c r="J484" t="n">
+        <v>7.692</v>
+      </c>
       <c r="K484" t="inlineStr">
         <is>
           <t>C087</t>
@@ -25505,7 +25747,9 @@
         <v>1710</v>
       </c>
       <c r="I485" t="inlineStr"/>
-      <c r="J485" t="inlineStr"/>
+      <c r="J485" t="n">
+        <v>7.692</v>
+      </c>
       <c r="K485" t="inlineStr">
         <is>
           <t>C087</t>
@@ -25557,7 +25801,9 @@
         <v>790</v>
       </c>
       <c r="I486" t="inlineStr"/>
-      <c r="J486" t="inlineStr"/>
+      <c r="J486" t="n">
+        <v>7.692</v>
+      </c>
       <c r="K486" t="inlineStr">
         <is>
           <t>C087</t>
@@ -25609,7 +25855,9 @@
         <v>690</v>
       </c>
       <c r="I487" t="inlineStr"/>
-      <c r="J487" t="inlineStr"/>
+      <c r="J487" t="n">
+        <v>7.692</v>
+      </c>
       <c r="K487" t="inlineStr">
         <is>
           <t>C087</t>
@@ -25659,7 +25907,9 @@
       </c>
       <c r="H488" t="inlineStr"/>
       <c r="I488" t="inlineStr"/>
-      <c r="J488" t="inlineStr"/>
+      <c r="J488" t="n">
+        <v>9.090999999999999</v>
+      </c>
       <c r="K488" t="inlineStr">
         <is>
           <t>C088</t>
@@ -25711,7 +25961,9 @@
         <v>520</v>
       </c>
       <c r="I489" t="inlineStr"/>
-      <c r="J489" t="inlineStr"/>
+      <c r="J489" t="n">
+        <v>9.090999999999999</v>
+      </c>
       <c r="K489" t="inlineStr">
         <is>
           <t>C088</t>
@@ -25763,7 +26015,9 @@
         <v>2120</v>
       </c>
       <c r="I490" t="inlineStr"/>
-      <c r="J490" t="inlineStr"/>
+      <c r="J490" t="n">
+        <v>9.090999999999999</v>
+      </c>
       <c r="K490" t="inlineStr">
         <is>
           <t>C088</t>
@@ -25815,7 +26069,9 @@
         <v>1280</v>
       </c>
       <c r="I491" t="inlineStr"/>
-      <c r="J491" t="inlineStr"/>
+      <c r="J491" t="n">
+        <v>9.090999999999999</v>
+      </c>
       <c r="K491" t="inlineStr">
         <is>
           <t>C088</t>
@@ -25867,7 +26123,9 @@
         <v>1250</v>
       </c>
       <c r="I492" t="inlineStr"/>
-      <c r="J492" t="inlineStr"/>
+      <c r="J492" t="n">
+        <v>9.090999999999999</v>
+      </c>
       <c r="K492" t="inlineStr">
         <is>
           <t>C088</t>
@@ -25919,7 +26177,9 @@
         <v>950</v>
       </c>
       <c r="I493" t="inlineStr"/>
-      <c r="J493" t="inlineStr"/>
+      <c r="J493" t="n">
+        <v>9.090999999999999</v>
+      </c>
       <c r="K493" t="inlineStr">
         <is>
           <t>C088</t>
@@ -25971,7 +26231,9 @@
         <v>370</v>
       </c>
       <c r="I494" t="inlineStr"/>
-      <c r="J494" t="inlineStr"/>
+      <c r="J494" t="n">
+        <v>9.090999999999999</v>
+      </c>
       <c r="K494" t="inlineStr">
         <is>
           <t>C088</t>
@@ -26023,7 +26285,9 @@
         <v>380</v>
       </c>
       <c r="I495" t="inlineStr"/>
-      <c r="J495" t="inlineStr"/>
+      <c r="J495" t="n">
+        <v>9.090999999999999</v>
+      </c>
       <c r="K495" t="inlineStr">
         <is>
           <t>C088</t>
@@ -26073,7 +26337,9 @@
       </c>
       <c r="H496" t="inlineStr"/>
       <c r="I496" t="inlineStr"/>
-      <c r="J496" t="inlineStr"/>
+      <c r="J496" t="n">
+        <v>5.556</v>
+      </c>
       <c r="K496" t="inlineStr">
         <is>
           <t>C089</t>
@@ -26125,7 +26391,9 @@
         <v>330</v>
       </c>
       <c r="I497" t="inlineStr"/>
-      <c r="J497" t="inlineStr"/>
+      <c r="J497" t="n">
+        <v>5.556</v>
+      </c>
       <c r="K497" t="inlineStr">
         <is>
           <t>C089</t>
@@ -26177,7 +26445,9 @@
         <v>1640</v>
       </c>
       <c r="I498" t="inlineStr"/>
-      <c r="J498" t="inlineStr"/>
+      <c r="J498" t="n">
+        <v>5.556</v>
+      </c>
       <c r="K498" t="inlineStr">
         <is>
           <t>C089</t>
@@ -26229,7 +26499,9 @@
         <v>1900</v>
       </c>
       <c r="I499" t="inlineStr"/>
-      <c r="J499" t="inlineStr"/>
+      <c r="J499" t="n">
+        <v>5.556</v>
+      </c>
       <c r="K499" t="inlineStr">
         <is>
           <t>C089</t>
@@ -26281,7 +26553,9 @@
         <v>1410</v>
       </c>
       <c r="I500" t="inlineStr"/>
-      <c r="J500" t="inlineStr"/>
+      <c r="J500" t="n">
+        <v>5.556</v>
+      </c>
       <c r="K500" t="inlineStr">
         <is>
           <t>C089</t>
@@ -26333,7 +26607,9 @@
         <v>1330</v>
       </c>
       <c r="I501" t="inlineStr"/>
-      <c r="J501" t="inlineStr"/>
+      <c r="J501" t="n">
+        <v>5.556</v>
+      </c>
       <c r="K501" t="inlineStr">
         <is>
           <t>C089</t>
@@ -26385,7 +26661,9 @@
         <v>400</v>
       </c>
       <c r="I502" t="inlineStr"/>
-      <c r="J502" t="inlineStr"/>
+      <c r="J502" t="n">
+        <v>5.556</v>
+      </c>
       <c r="K502" t="inlineStr">
         <is>
           <t>C089</t>
@@ -26437,7 +26715,9 @@
         <v>420</v>
       </c>
       <c r="I503" t="inlineStr"/>
-      <c r="J503" t="inlineStr"/>
+      <c r="J503" t="n">
+        <v>5.556</v>
+      </c>
       <c r="K503" t="inlineStr">
         <is>
           <t>C089</t>
@@ -29861,7 +30141,9 @@
       <c r="I569" t="n">
         <v>3.725</v>
       </c>
-      <c r="J569" t="inlineStr"/>
+      <c r="J569" t="n">
+        <v>0.00285</v>
+      </c>
       <c r="K569" t="inlineStr">
         <is>
           <t>C035</t>
@@ -29913,7 +30195,9 @@
       <c r="I570" t="n">
         <v>3.725</v>
       </c>
-      <c r="J570" t="inlineStr"/>
+      <c r="J570" t="n">
+        <v>0.00235</v>
+      </c>
       <c r="K570" t="inlineStr">
         <is>
           <t>C043</t>
@@ -29965,7 +30249,9 @@
       <c r="I571" t="n">
         <v>3.165</v>
       </c>
-      <c r="J571" t="inlineStr"/>
+      <c r="J571" t="n">
+        <v>0.0034</v>
+      </c>
       <c r="K571" t="inlineStr">
         <is>
           <t>C045</t>
@@ -30017,7 +30303,9 @@
       <c r="I572" t="n">
         <v>4.095</v>
       </c>
-      <c r="J572" t="inlineStr"/>
+      <c r="J572" t="n">
+        <v>0.0015</v>
+      </c>
       <c r="K572" t="inlineStr">
         <is>
           <t>C040</t>
@@ -30069,7 +30357,9 @@
       <c r="I573" t="n">
         <v>3.915</v>
       </c>
-      <c r="J573" t="inlineStr"/>
+      <c r="J573" t="n">
+        <v>0.00215</v>
+      </c>
       <c r="K573" t="inlineStr">
         <is>
           <t>C039</t>
@@ -30121,7 +30411,9 @@
       <c r="I574" t="n">
         <v>4.165</v>
       </c>
-      <c r="J574" t="inlineStr"/>
+      <c r="J574" t="n">
+        <v>0.00135</v>
+      </c>
       <c r="K574" t="inlineStr">
         <is>
           <t>C036</t>
@@ -30173,7 +30465,9 @@
       <c r="I575" t="n">
         <v>3.915</v>
       </c>
-      <c r="J575" t="inlineStr"/>
+      <c r="J575" t="n">
+        <v>0.0023</v>
+      </c>
       <c r="K575" t="inlineStr">
         <is>
           <t>C042</t>
@@ -30225,7 +30519,9 @@
       <c r="I576" t="n">
         <v>4.005</v>
       </c>
-      <c r="J576" t="inlineStr"/>
+      <c r="J576" t="n">
+        <v>0.0016</v>
+      </c>
       <c r="K576" t="inlineStr">
         <is>
           <t>C041</t>
@@ -30277,7 +30573,9 @@
       <c r="I577" t="n">
         <v>3.965</v>
       </c>
-      <c r="J577" t="inlineStr"/>
+      <c r="J577" t="n">
+        <v>0.0013</v>
+      </c>
       <c r="K577" t="inlineStr">
         <is>
           <t>C037</t>
@@ -30329,7 +30627,9 @@
       <c r="I578" t="n">
         <v>3.265</v>
       </c>
-      <c r="J578" t="inlineStr"/>
+      <c r="J578" t="n">
+        <v>0.0028</v>
+      </c>
       <c r="K578" t="inlineStr">
         <is>
           <t>C038</t>
@@ -30381,7 +30681,9 @@
       <c r="I579" t="n">
         <v>3.565</v>
       </c>
-      <c r="J579" t="inlineStr"/>
+      <c r="J579" t="n">
+        <v>0.0019</v>
+      </c>
       <c r="K579" t="inlineStr">
         <is>
           <t>C044</t>
@@ -34466,7 +34768,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B34"/>
+  <dimension ref="A1:B35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -34683,12 +34985,12 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>binding_site</t>
+          <t>ligand_protein_ratio_max</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>The site, where the paper identifies one. A property of the compound-protein pair, so it sits with the measurement and not with the assay.</t>
+          <t>The highest ratio this assay reached: most ligand over least protein. Below about 0.01 a measurement sees the specific site; above about 1 it sees non-specific partitioning, and the two differ by orders of magnitude, so two constants measured at different ratios are not comparable even for the same compound and protein. It is a property of the assay and also sits on the Conditions sheet; it is repeated here because it is the column you filter on, and having to do a lookup to learn which regime a number came from is a lookup too many.</t>
         </is>
       </c>
     </row>
@@ -34824,7 +35126,19 @@
       <c r="A34" s="4" t="inlineStr"/>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>Moving them to their own sheet does not weaken that check -- the ratio is a property of the assay, so it belongs with the assay, and `ligand_protein_ratio_max` now sits beside the concentrations it is computed from instead of being repeated down 578 rows.</t>
+          <t>Moving them to their own sheet does not weaken that check -- the ratio sits in both places: beside the concentrations it is computed from, on Conditions, and on every measurement row, where it is actually used.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>What is NOT here</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>The binding site, and the per-row basis for each converted value. This file is the reading copy and stays narrow. Both are in db/binding_affinity.xlsx and in db/combined/binding.csv: the site in its own column, the basis through a `basis_id` key into a Conversion basis table that says how every kd_uM and logK was reached, or why either is blank.</t>
         </is>
       </c>
     </row>

--- a/tk_review/db/binding_major_sources.xlsx
+++ b/tk_review/db/binding_major_sources.xlsx
@@ -36500,7 +36500,7 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Whether that n was FITTED by the paper or ASSUMED by it. Every n_used in this file reads `assumed`, because Chen 2025 fitted a single-site model, which fixes n = 1 by construction rather than measuring it. Elsewhere in the database the fitted values are not all near 1 -- Wu 2024 reports 0.469 to 0.869 and Chen &amp; Guo 2009 reaches 14 -- so the word matters even where this file only shows one of them.</t>
+          <t>WHICH EXPERIMENT produced that n: `ITC` or `displacement` (a counted site), `assumed` (n = 1 because the paper fitted a single-site model, which fixes it by construction), or `quenching fit` (the slope of a double-logarithmic, Scatchard or modified Stern-Volmer plot, which is a fitted exponent and not a site count -- those rows are NOT converted to a logK anywhere in this database). Every n_used in this file reads `assumed`, because Chen 2025 is its only Kd-and-n source and it fitted a single-site model. The word still matters here: it says the 57 converted coefficients below rest on a modelling choice, not a measurement.</t>
         </is>
       </c>
     </row>

--- a/tk_review/db/binding_major_sources.xlsx
+++ b/tk_review/db/binding_major_sources.xlsx
@@ -582,7 +582,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>C078</t>
+          <t>C088</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>C078</t>
+          <t>C088</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>C078</t>
+          <t>C088</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>C078</t>
+          <t>C088</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>C078</t>
+          <t>C088</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>C078</t>
+          <t>C088</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>C078</t>
+          <t>C088</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>C078</t>
+          <t>C088</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>C078</t>
+          <t>C088</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>C078</t>
+          <t>C088</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1142,7 +1142,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>C078</t>
+          <t>C088</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>C078</t>
+          <t>C088</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>C078</t>
+          <t>C088</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>C078</t>
+          <t>C088</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1366,7 +1366,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>C078</t>
+          <t>C088</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>C078</t>
+          <t>C088</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>C078</t>
+          <t>C088</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1534,7 +1534,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>C078</t>
+          <t>C088</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>C078</t>
+          <t>C088</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>C078</t>
+          <t>C088</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1702,7 +1702,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>C078</t>
+          <t>C088</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>C078</t>
+          <t>C088</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>C078</t>
+          <t>C088</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -1870,7 +1870,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>C078</t>
+          <t>C088</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>C078</t>
+          <t>C088</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>C078</t>
+          <t>C088</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2038,7 +2038,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>C078</t>
+          <t>C088</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2094,7 +2094,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>C079</t>
+          <t>C089</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>C079</t>
+          <t>C089</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>C079</t>
+          <t>C089</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>C079</t>
+          <t>C089</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>C079</t>
+          <t>C089</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>C079</t>
+          <t>C089</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2430,7 +2430,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>C079</t>
+          <t>C089</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>C079</t>
+          <t>C089</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -2542,7 +2542,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>C079</t>
+          <t>C089</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -2598,7 +2598,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>C079</t>
+          <t>C089</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>C079</t>
+          <t>C089</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -2710,7 +2710,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>C079</t>
+          <t>C089</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -2766,7 +2766,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>C079</t>
+          <t>C089</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -2822,7 +2822,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>C079</t>
+          <t>C089</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>C079</t>
+          <t>C089</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>C079</t>
+          <t>C089</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -2990,7 +2990,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>C079</t>
+          <t>C089</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3046,7 +3046,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>C079</t>
+          <t>C089</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>C079</t>
+          <t>C089</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3158,7 +3158,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>C079</t>
+          <t>C089</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3214,7 +3214,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>C079</t>
+          <t>C089</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -3270,7 +3270,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>C079</t>
+          <t>C089</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -3326,7 +3326,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>C079</t>
+          <t>C089</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -3382,7 +3382,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>C079</t>
+          <t>C089</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -3438,7 +3438,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>C079</t>
+          <t>C089</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -3494,7 +3494,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>C079</t>
+          <t>C089</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>C079</t>
+          <t>C089</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>C079</t>
+          <t>C089</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -3662,7 +3662,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>C080</t>
+          <t>C090</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -3718,7 +3718,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>C080</t>
+          <t>C090</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>C080</t>
+          <t>C090</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -3830,7 +3830,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>C080</t>
+          <t>C090</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -3886,7 +3886,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>C080</t>
+          <t>C090</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -3942,7 +3942,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>C080</t>
+          <t>C090</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -3998,7 +3998,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>C080</t>
+          <t>C090</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -4054,7 +4054,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>C080</t>
+          <t>C090</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>C080</t>
+          <t>C090</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>C080</t>
+          <t>C090</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -4222,7 +4222,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>C080</t>
+          <t>C090</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -4278,7 +4278,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>C080</t>
+          <t>C090</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -4334,7 +4334,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>C080</t>
+          <t>C090</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -4390,7 +4390,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>C080</t>
+          <t>C090</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -4446,7 +4446,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>C080</t>
+          <t>C090</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -4502,7 +4502,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>C080</t>
+          <t>C090</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -4558,7 +4558,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>C080</t>
+          <t>C090</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -4614,7 +4614,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>C080</t>
+          <t>C090</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>C080</t>
+          <t>C090</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -4726,7 +4726,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>C080</t>
+          <t>C090</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>C080</t>
+          <t>C090</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -4838,7 +4838,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>C080</t>
+          <t>C090</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -4894,7 +4894,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>C080</t>
+          <t>C090</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -4950,7 +4950,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>C080</t>
+          <t>C090</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -5006,7 +5006,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>C080</t>
+          <t>C090</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -5062,7 +5062,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>C080</t>
+          <t>C090</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>C080</t>
+          <t>C090</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>C080</t>
+          <t>C090</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -5226,7 +5226,7 @@
       <c r="L85" t="inlineStr"/>
       <c r="M85" t="inlineStr">
         <is>
-          <t>C081</t>
+          <t>C091</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -5278,7 +5278,7 @@
       <c r="L86" t="inlineStr"/>
       <c r="M86" t="inlineStr">
         <is>
-          <t>C081</t>
+          <t>C091</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -5330,7 +5330,7 @@
       <c r="L87" t="inlineStr"/>
       <c r="M87" t="inlineStr">
         <is>
-          <t>C081</t>
+          <t>C091</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -5382,7 +5382,7 @@
       <c r="L88" t="inlineStr"/>
       <c r="M88" t="inlineStr">
         <is>
-          <t>C081</t>
+          <t>C091</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -5434,7 +5434,7 @@
       <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr">
         <is>
-          <t>C081</t>
+          <t>C091</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -5486,7 +5486,7 @@
       <c r="L90" t="inlineStr"/>
       <c r="M90" t="inlineStr">
         <is>
-          <t>C081</t>
+          <t>C091</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -5538,7 +5538,7 @@
       <c r="L91" t="inlineStr"/>
       <c r="M91" t="inlineStr">
         <is>
-          <t>C081</t>
+          <t>C091</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -5590,7 +5590,7 @@
       <c r="L92" t="inlineStr"/>
       <c r="M92" t="inlineStr">
         <is>
-          <t>C081</t>
+          <t>C091</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -5642,7 +5642,7 @@
       <c r="L93" t="inlineStr"/>
       <c r="M93" t="inlineStr">
         <is>
-          <t>C081</t>
+          <t>C091</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -5694,7 +5694,7 @@
       <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr">
         <is>
-          <t>C081</t>
+          <t>C091</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -5746,7 +5746,7 @@
       <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr">
         <is>
-          <t>C081</t>
+          <t>C091</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -5798,7 +5798,7 @@
       <c r="L96" t="inlineStr"/>
       <c r="M96" t="inlineStr">
         <is>
-          <t>C081</t>
+          <t>C091</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -5850,7 +5850,7 @@
       <c r="L97" t="inlineStr"/>
       <c r="M97" t="inlineStr">
         <is>
-          <t>C081</t>
+          <t>C091</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -5902,7 +5902,7 @@
       <c r="L98" t="inlineStr"/>
       <c r="M98" t="inlineStr">
         <is>
-          <t>C081</t>
+          <t>C091</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -5954,7 +5954,7 @@
       <c r="L99" t="inlineStr"/>
       <c r="M99" t="inlineStr">
         <is>
-          <t>C081</t>
+          <t>C091</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -6006,7 +6006,7 @@
       <c r="L100" t="inlineStr"/>
       <c r="M100" t="inlineStr">
         <is>
-          <t>C081</t>
+          <t>C091</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -6058,7 +6058,7 @@
       <c r="L101" t="inlineStr"/>
       <c r="M101" t="inlineStr">
         <is>
-          <t>C081</t>
+          <t>C091</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -6110,7 +6110,7 @@
       <c r="L102" t="inlineStr"/>
       <c r="M102" t="inlineStr">
         <is>
-          <t>C081</t>
+          <t>C091</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -6162,7 +6162,7 @@
       <c r="L103" t="inlineStr"/>
       <c r="M103" t="inlineStr">
         <is>
-          <t>C081</t>
+          <t>C091</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -6214,7 +6214,7 @@
       <c r="L104" t="inlineStr"/>
       <c r="M104" t="inlineStr">
         <is>
-          <t>C081</t>
+          <t>C091</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -6266,7 +6266,7 @@
       <c r="L105" t="inlineStr"/>
       <c r="M105" t="inlineStr">
         <is>
-          <t>C081</t>
+          <t>C091</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -6318,7 +6318,7 @@
       <c r="L106" t="inlineStr"/>
       <c r="M106" t="inlineStr">
         <is>
-          <t>C081</t>
+          <t>C091</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -6370,7 +6370,7 @@
       <c r="L107" t="inlineStr"/>
       <c r="M107" t="inlineStr">
         <is>
-          <t>C081</t>
+          <t>C091</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
@@ -6422,7 +6422,7 @@
       <c r="L108" t="inlineStr"/>
       <c r="M108" t="inlineStr">
         <is>
-          <t>C081</t>
+          <t>C091</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -6474,7 +6474,7 @@
       <c r="L109" t="inlineStr"/>
       <c r="M109" t="inlineStr">
         <is>
-          <t>C081</t>
+          <t>C091</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
@@ -6526,7 +6526,7 @@
       <c r="L110" t="inlineStr"/>
       <c r="M110" t="inlineStr">
         <is>
-          <t>C081</t>
+          <t>C091</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -6578,7 +6578,7 @@
       <c r="L111" t="inlineStr"/>
       <c r="M111" t="inlineStr">
         <is>
-          <t>C081</t>
+          <t>C091</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -6630,7 +6630,7 @@
       <c r="L112" t="inlineStr"/>
       <c r="M112" t="inlineStr">
         <is>
-          <t>C081</t>
+          <t>C091</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -6694,7 +6694,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>C099</t>
+          <t>C105</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
@@ -6758,7 +6758,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>C099</t>
+          <t>C105</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -6822,7 +6822,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>C099</t>
+          <t>C105</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -6886,7 +6886,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>C099</t>
+          <t>C105</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -6950,7 +6950,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>C099</t>
+          <t>C105</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>C099</t>
+          <t>C105</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -7078,7 +7078,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>C099</t>
+          <t>C105</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
@@ -7142,7 +7142,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>C099</t>
+          <t>C105</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -7206,7 +7206,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>C099</t>
+          <t>C105</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -7270,7 +7270,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>C099</t>
+          <t>C105</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -7334,7 +7334,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>C099</t>
+          <t>C105</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -7398,7 +7398,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>C099</t>
+          <t>C105</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
@@ -7462,7 +7462,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>C099</t>
+          <t>C105</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -7526,7 +7526,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>C099</t>
+          <t>C105</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -7590,7 +7590,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>C099</t>
+          <t>C105</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
@@ -7654,7 +7654,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>C099</t>
+          <t>C105</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -7718,7 +7718,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>C099</t>
+          <t>C105</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
@@ -7782,7 +7782,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>C099</t>
+          <t>C105</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>C099</t>
+          <t>C105</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
@@ -7910,7 +7910,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>C099</t>
+          <t>C105</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
@@ -7974,7 +7974,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>C099</t>
+          <t>C105</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
@@ -8038,7 +8038,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>C099</t>
+          <t>C105</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -8102,7 +8102,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>C099</t>
+          <t>C105</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
@@ -8166,7 +8166,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>C099</t>
+          <t>C105</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
@@ -8230,7 +8230,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>C099</t>
+          <t>C105</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
@@ -8294,7 +8294,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>C099</t>
+          <t>C105</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>C099</t>
+          <t>C105</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
@@ -8422,7 +8422,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>C099</t>
+          <t>C105</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
@@ -8486,7 +8486,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>C099</t>
+          <t>C105</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
@@ -8550,7 +8550,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>C099</t>
+          <t>C105</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
@@ -8614,7 +8614,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>C099</t>
+          <t>C105</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -8678,7 +8678,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>C099</t>
+          <t>C105</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -8742,7 +8742,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>C099</t>
+          <t>C105</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -8806,7 +8806,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>C099</t>
+          <t>C105</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
@@ -8870,7 +8870,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>C099</t>
+          <t>C105</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
@@ -8934,7 +8934,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>C099</t>
+          <t>C105</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
@@ -8998,7 +8998,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>C099</t>
+          <t>C105</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
@@ -9062,7 +9062,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>C099</t>
+          <t>C105</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
@@ -9126,7 +9126,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>C099</t>
+          <t>C105</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
@@ -9190,7 +9190,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>C099</t>
+          <t>C105</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -9254,7 +9254,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>C099</t>
+          <t>C105</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
@@ -9318,7 +9318,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>C099</t>
+          <t>C105</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -9382,7 +9382,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>C099</t>
+          <t>C105</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
@@ -9446,7 +9446,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>C099</t>
+          <t>C105</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
@@ -9510,7 +9510,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>C099</t>
+          <t>C105</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
@@ -9574,7 +9574,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>C099</t>
+          <t>C105</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
@@ -9638,7 +9638,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>C099</t>
+          <t>C105</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
@@ -9702,7 +9702,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>C099</t>
+          <t>C105</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -9766,7 +9766,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>C099</t>
+          <t>C105</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -9830,7 +9830,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>C099</t>
+          <t>C105</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
@@ -9894,7 +9894,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>C099</t>
+          <t>C105</t>
         </is>
       </c>
       <c r="N163" t="inlineStr">
@@ -9958,7 +9958,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>C099</t>
+          <t>C105</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
@@ -10022,7 +10022,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>C099</t>
+          <t>C105</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
@@ -10086,7 +10086,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>C099</t>
+          <t>C105</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
@@ -10150,7 +10150,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>C099</t>
+          <t>C105</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
@@ -10214,7 +10214,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>C099</t>
+          <t>C105</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
@@ -10278,7 +10278,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>C099</t>
+          <t>C105</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
@@ -10330,7 +10330,7 @@
       <c r="L170" t="inlineStr"/>
       <c r="M170" t="inlineStr">
         <is>
-          <t>C100</t>
+          <t>C106</t>
         </is>
       </c>
       <c r="N170" t="inlineStr">
@@ -10382,7 +10382,7 @@
       <c r="L171" t="inlineStr"/>
       <c r="M171" t="inlineStr">
         <is>
-          <t>C100</t>
+          <t>C106</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
@@ -10434,7 +10434,7 @@
       <c r="L172" t="inlineStr"/>
       <c r="M172" t="inlineStr">
         <is>
-          <t>C100</t>
+          <t>C106</t>
         </is>
       </c>
       <c r="N172" t="inlineStr">
@@ -10486,7 +10486,7 @@
       <c r="L173" t="inlineStr"/>
       <c r="M173" t="inlineStr">
         <is>
-          <t>C100</t>
+          <t>C106</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
@@ -10538,7 +10538,7 @@
       <c r="L174" t="inlineStr"/>
       <c r="M174" t="inlineStr">
         <is>
-          <t>C100</t>
+          <t>C106</t>
         </is>
       </c>
       <c r="N174" t="inlineStr">
@@ -10590,7 +10590,7 @@
       <c r="L175" t="inlineStr"/>
       <c r="M175" t="inlineStr">
         <is>
-          <t>C100</t>
+          <t>C106</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
@@ -10642,7 +10642,7 @@
       <c r="L176" t="inlineStr"/>
       <c r="M176" t="inlineStr">
         <is>
-          <t>C100</t>
+          <t>C106</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
@@ -10694,7 +10694,7 @@
       <c r="L177" t="inlineStr"/>
       <c r="M177" t="inlineStr">
         <is>
-          <t>C100</t>
+          <t>C106</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
@@ -10746,7 +10746,7 @@
       <c r="L178" t="inlineStr"/>
       <c r="M178" t="inlineStr">
         <is>
-          <t>C100</t>
+          <t>C106</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
@@ -10798,7 +10798,7 @@
       <c r="L179" t="inlineStr"/>
       <c r="M179" t="inlineStr">
         <is>
-          <t>C100</t>
+          <t>C106</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
@@ -10850,7 +10850,7 @@
       <c r="L180" t="inlineStr"/>
       <c r="M180" t="inlineStr">
         <is>
-          <t>C100</t>
+          <t>C106</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
@@ -10902,7 +10902,7 @@
       <c r="L181" t="inlineStr"/>
       <c r="M181" t="inlineStr">
         <is>
-          <t>C100</t>
+          <t>C106</t>
         </is>
       </c>
       <c r="N181" t="inlineStr">
@@ -10954,7 +10954,7 @@
       <c r="L182" t="inlineStr"/>
       <c r="M182" t="inlineStr">
         <is>
-          <t>C100</t>
+          <t>C106</t>
         </is>
       </c>
       <c r="N182" t="inlineStr">
@@ -11006,7 +11006,7 @@
       <c r="L183" t="inlineStr"/>
       <c r="M183" t="inlineStr">
         <is>
-          <t>C100</t>
+          <t>C106</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
@@ -11058,7 +11058,7 @@
       <c r="L184" t="inlineStr"/>
       <c r="M184" t="inlineStr">
         <is>
-          <t>C100</t>
+          <t>C106</t>
         </is>
       </c>
       <c r="N184" t="inlineStr">
@@ -11110,7 +11110,7 @@
       <c r="L185" t="inlineStr"/>
       <c r="M185" t="inlineStr">
         <is>
-          <t>C100</t>
+          <t>C106</t>
         </is>
       </c>
       <c r="N185" t="inlineStr">
@@ -11162,7 +11162,7 @@
       <c r="L186" t="inlineStr"/>
       <c r="M186" t="inlineStr">
         <is>
-          <t>C100</t>
+          <t>C106</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
@@ -11214,7 +11214,7 @@
       <c r="L187" t="inlineStr"/>
       <c r="M187" t="inlineStr">
         <is>
-          <t>C100</t>
+          <t>C106</t>
         </is>
       </c>
       <c r="N187" t="inlineStr">
@@ -11266,7 +11266,7 @@
       <c r="L188" t="inlineStr"/>
       <c r="M188" t="inlineStr">
         <is>
-          <t>C100</t>
+          <t>C106</t>
         </is>
       </c>
       <c r="N188" t="inlineStr">
@@ -11318,7 +11318,7 @@
       <c r="L189" t="inlineStr"/>
       <c r="M189" t="inlineStr">
         <is>
-          <t>C100</t>
+          <t>C106</t>
         </is>
       </c>
       <c r="N189" t="inlineStr">
@@ -11370,7 +11370,7 @@
       <c r="L190" t="inlineStr"/>
       <c r="M190" t="inlineStr">
         <is>
-          <t>C100</t>
+          <t>C106</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
@@ -11422,7 +11422,7 @@
       <c r="L191" t="inlineStr"/>
       <c r="M191" t="inlineStr">
         <is>
-          <t>C100</t>
+          <t>C106</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
@@ -11474,7 +11474,7 @@
       <c r="L192" t="inlineStr"/>
       <c r="M192" t="inlineStr">
         <is>
-          <t>C100</t>
+          <t>C106</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
@@ -11526,7 +11526,7 @@
       <c r="L193" t="inlineStr"/>
       <c r="M193" t="inlineStr">
         <is>
-          <t>C100</t>
+          <t>C106</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
@@ -11578,7 +11578,7 @@
       <c r="L194" t="inlineStr"/>
       <c r="M194" t="inlineStr">
         <is>
-          <t>C100</t>
+          <t>C106</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
@@ -11630,7 +11630,7 @@
       <c r="L195" t="inlineStr"/>
       <c r="M195" t="inlineStr">
         <is>
-          <t>C100</t>
+          <t>C106</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
@@ -11682,7 +11682,7 @@
       <c r="L196" t="inlineStr"/>
       <c r="M196" t="inlineStr">
         <is>
-          <t>C100</t>
+          <t>C106</t>
         </is>
       </c>
       <c r="N196" t="inlineStr">
@@ -11734,7 +11734,7 @@
       <c r="L197" t="inlineStr"/>
       <c r="M197" t="inlineStr">
         <is>
-          <t>C100</t>
+          <t>C106</t>
         </is>
       </c>
       <c r="N197" t="inlineStr">
@@ -11786,7 +11786,7 @@
       <c r="L198" t="inlineStr"/>
       <c r="M198" t="inlineStr">
         <is>
-          <t>C100</t>
+          <t>C106</t>
         </is>
       </c>
       <c r="N198" t="inlineStr">
@@ -11838,7 +11838,7 @@
       <c r="L199" t="inlineStr"/>
       <c r="M199" t="inlineStr">
         <is>
-          <t>C100</t>
+          <t>C106</t>
         </is>
       </c>
       <c r="N199" t="inlineStr">
@@ -11890,7 +11890,7 @@
       <c r="L200" t="inlineStr"/>
       <c r="M200" t="inlineStr">
         <is>
-          <t>C100</t>
+          <t>C106</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
@@ -11942,7 +11942,7 @@
       <c r="L201" t="inlineStr"/>
       <c r="M201" t="inlineStr">
         <is>
-          <t>C100</t>
+          <t>C106</t>
         </is>
       </c>
       <c r="N201" t="inlineStr">
@@ -11994,7 +11994,7 @@
       <c r="L202" t="inlineStr"/>
       <c r="M202" t="inlineStr">
         <is>
-          <t>C100</t>
+          <t>C106</t>
         </is>
       </c>
       <c r="N202" t="inlineStr">
@@ -12046,7 +12046,7 @@
       <c r="L203" t="inlineStr"/>
       <c r="M203" t="inlineStr">
         <is>
-          <t>C100</t>
+          <t>C106</t>
         </is>
       </c>
       <c r="N203" t="inlineStr">
@@ -12098,7 +12098,7 @@
       <c r="L204" t="inlineStr"/>
       <c r="M204" t="inlineStr">
         <is>
-          <t>C100</t>
+          <t>C106</t>
         </is>
       </c>
       <c r="N204" t="inlineStr">
@@ -12150,7 +12150,7 @@
       <c r="L205" t="inlineStr"/>
       <c r="M205" t="inlineStr">
         <is>
-          <t>C100</t>
+          <t>C106</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
@@ -12202,7 +12202,7 @@
       <c r="L206" t="inlineStr"/>
       <c r="M206" t="inlineStr">
         <is>
-          <t>C100</t>
+          <t>C106</t>
         </is>
       </c>
       <c r="N206" t="inlineStr">
@@ -12254,7 +12254,7 @@
       <c r="L207" t="inlineStr"/>
       <c r="M207" t="inlineStr">
         <is>
-          <t>C100</t>
+          <t>C106</t>
         </is>
       </c>
       <c r="N207" t="inlineStr">
@@ -12306,7 +12306,7 @@
       <c r="L208" t="inlineStr"/>
       <c r="M208" t="inlineStr">
         <is>
-          <t>C100</t>
+          <t>C106</t>
         </is>
       </c>
       <c r="N208" t="inlineStr">
@@ -12358,7 +12358,7 @@
       <c r="L209" t="inlineStr"/>
       <c r="M209" t="inlineStr">
         <is>
-          <t>C100</t>
+          <t>C106</t>
         </is>
       </c>
       <c r="N209" t="inlineStr">
@@ -12410,7 +12410,7 @@
       <c r="L210" t="inlineStr"/>
       <c r="M210" t="inlineStr">
         <is>
-          <t>C100</t>
+          <t>C106</t>
         </is>
       </c>
       <c r="N210" t="inlineStr">
@@ -12462,7 +12462,7 @@
       <c r="L211" t="inlineStr"/>
       <c r="M211" t="inlineStr">
         <is>
-          <t>C100</t>
+          <t>C106</t>
         </is>
       </c>
       <c r="N211" t="inlineStr">
@@ -12514,7 +12514,7 @@
       <c r="L212" t="inlineStr"/>
       <c r="M212" t="inlineStr">
         <is>
-          <t>C100</t>
+          <t>C106</t>
         </is>
       </c>
       <c r="N212" t="inlineStr">
@@ -12566,7 +12566,7 @@
       <c r="L213" t="inlineStr"/>
       <c r="M213" t="inlineStr">
         <is>
-          <t>C100</t>
+          <t>C106</t>
         </is>
       </c>
       <c r="N213" t="inlineStr">
@@ -12618,7 +12618,7 @@
       <c r="L214" t="inlineStr"/>
       <c r="M214" t="inlineStr">
         <is>
-          <t>C100</t>
+          <t>C106</t>
         </is>
       </c>
       <c r="N214" t="inlineStr">
@@ -12670,7 +12670,7 @@
       <c r="L215" t="inlineStr"/>
       <c r="M215" t="inlineStr">
         <is>
-          <t>C100</t>
+          <t>C106</t>
         </is>
       </c>
       <c r="N215" t="inlineStr">
@@ -12722,7 +12722,7 @@
       <c r="L216" t="inlineStr"/>
       <c r="M216" t="inlineStr">
         <is>
-          <t>C100</t>
+          <t>C106</t>
         </is>
       </c>
       <c r="N216" t="inlineStr">
@@ -12774,7 +12774,7 @@
       <c r="L217" t="inlineStr"/>
       <c r="M217" t="inlineStr">
         <is>
-          <t>C100</t>
+          <t>C106</t>
         </is>
       </c>
       <c r="N217" t="inlineStr">
@@ -12826,7 +12826,7 @@
       <c r="L218" t="inlineStr"/>
       <c r="M218" t="inlineStr">
         <is>
-          <t>C100</t>
+          <t>C106</t>
         </is>
       </c>
       <c r="N218" t="inlineStr">
@@ -12878,7 +12878,7 @@
       <c r="L219" t="inlineStr"/>
       <c r="M219" t="inlineStr">
         <is>
-          <t>C100</t>
+          <t>C106</t>
         </is>
       </c>
       <c r="N219" t="inlineStr">
@@ -12930,7 +12930,7 @@
       <c r="L220" t="inlineStr"/>
       <c r="M220" t="inlineStr">
         <is>
-          <t>C100</t>
+          <t>C106</t>
         </is>
       </c>
       <c r="N220" t="inlineStr">
@@ -12982,7 +12982,7 @@
       <c r="L221" t="inlineStr"/>
       <c r="M221" t="inlineStr">
         <is>
-          <t>C100</t>
+          <t>C106</t>
         </is>
       </c>
       <c r="N221" t="inlineStr">
@@ -13034,7 +13034,7 @@
       <c r="L222" t="inlineStr"/>
       <c r="M222" t="inlineStr">
         <is>
-          <t>C100</t>
+          <t>C106</t>
         </is>
       </c>
       <c r="N222" t="inlineStr">
@@ -13086,7 +13086,7 @@
       <c r="L223" t="inlineStr"/>
       <c r="M223" t="inlineStr">
         <is>
-          <t>C100</t>
+          <t>C106</t>
         </is>
       </c>
       <c r="N223" t="inlineStr">
@@ -13138,7 +13138,7 @@
       <c r="L224" t="inlineStr"/>
       <c r="M224" t="inlineStr">
         <is>
-          <t>C100</t>
+          <t>C106</t>
         </is>
       </c>
       <c r="N224" t="inlineStr">
@@ -13190,7 +13190,7 @@
       <c r="L225" t="inlineStr"/>
       <c r="M225" t="inlineStr">
         <is>
-          <t>C100</t>
+          <t>C106</t>
         </is>
       </c>
       <c r="N225" t="inlineStr">
@@ -13242,7 +13242,7 @@
       <c r="L226" t="inlineStr"/>
       <c r="M226" t="inlineStr">
         <is>
-          <t>C100</t>
+          <t>C106</t>
         </is>
       </c>
       <c r="N226" t="inlineStr">
@@ -13296,7 +13296,7 @@
       <c r="L227" t="inlineStr"/>
       <c r="M227" t="inlineStr">
         <is>
-          <t>C113</t>
+          <t>C119</t>
         </is>
       </c>
       <c r="N227" t="inlineStr">
@@ -13350,7 +13350,7 @@
       <c r="L228" t="inlineStr"/>
       <c r="M228" t="inlineStr">
         <is>
-          <t>C113</t>
+          <t>C119</t>
         </is>
       </c>
       <c r="N228" t="inlineStr">
@@ -13404,7 +13404,7 @@
       <c r="L229" t="inlineStr"/>
       <c r="M229" t="inlineStr">
         <is>
-          <t>C113</t>
+          <t>C119</t>
         </is>
       </c>
       <c r="N229" t="inlineStr">
@@ -13458,7 +13458,7 @@
       <c r="L230" t="inlineStr"/>
       <c r="M230" t="inlineStr">
         <is>
-          <t>C113</t>
+          <t>C119</t>
         </is>
       </c>
       <c r="N230" t="inlineStr">
@@ -13512,7 +13512,7 @@
       <c r="L231" t="inlineStr"/>
       <c r="M231" t="inlineStr">
         <is>
-          <t>C113</t>
+          <t>C119</t>
         </is>
       </c>
       <c r="N231" t="inlineStr">
@@ -13566,7 +13566,7 @@
       <c r="L232" t="inlineStr"/>
       <c r="M232" t="inlineStr">
         <is>
-          <t>C113</t>
+          <t>C119</t>
         </is>
       </c>
       <c r="N232" t="inlineStr">
@@ -13620,7 +13620,7 @@
       <c r="L233" t="inlineStr"/>
       <c r="M233" t="inlineStr">
         <is>
-          <t>C113</t>
+          <t>C119</t>
         </is>
       </c>
       <c r="N233" t="inlineStr">
@@ -13674,7 +13674,7 @@
       <c r="L234" t="inlineStr"/>
       <c r="M234" t="inlineStr">
         <is>
-          <t>C113</t>
+          <t>C119</t>
         </is>
       </c>
       <c r="N234" t="inlineStr">
@@ -13728,7 +13728,7 @@
       <c r="L235" t="inlineStr"/>
       <c r="M235" t="inlineStr">
         <is>
-          <t>C113</t>
+          <t>C119</t>
         </is>
       </c>
       <c r="N235" t="inlineStr">
@@ -13782,7 +13782,7 @@
       <c r="L236" t="inlineStr"/>
       <c r="M236" t="inlineStr">
         <is>
-          <t>C113</t>
+          <t>C119</t>
         </is>
       </c>
       <c r="N236" t="inlineStr">
@@ -13836,7 +13836,7 @@
       <c r="L237" t="inlineStr"/>
       <c r="M237" t="inlineStr">
         <is>
-          <t>C113</t>
+          <t>C119</t>
         </is>
       </c>
       <c r="N237" t="inlineStr">
@@ -13890,7 +13890,7 @@
       <c r="L238" t="inlineStr"/>
       <c r="M238" t="inlineStr">
         <is>
-          <t>C113</t>
+          <t>C119</t>
         </is>
       </c>
       <c r="N238" t="inlineStr">
@@ -13944,7 +13944,7 @@
       <c r="L239" t="inlineStr"/>
       <c r="M239" t="inlineStr">
         <is>
-          <t>C113</t>
+          <t>C119</t>
         </is>
       </c>
       <c r="N239" t="inlineStr">
@@ -13998,7 +13998,7 @@
       <c r="L240" t="inlineStr"/>
       <c r="M240" t="inlineStr">
         <is>
-          <t>C113</t>
+          <t>C119</t>
         </is>
       </c>
       <c r="N240" t="inlineStr">
@@ -14052,7 +14052,7 @@
       <c r="L241" t="inlineStr"/>
       <c r="M241" t="inlineStr">
         <is>
-          <t>C113</t>
+          <t>C119</t>
         </is>
       </c>
       <c r="N241" t="inlineStr">
@@ -14106,7 +14106,7 @@
       <c r="L242" t="inlineStr"/>
       <c r="M242" t="inlineStr">
         <is>
-          <t>C113</t>
+          <t>C119</t>
         </is>
       </c>
       <c r="N242" t="inlineStr">
@@ -14160,7 +14160,7 @@
       <c r="L243" t="inlineStr"/>
       <c r="M243" t="inlineStr">
         <is>
-          <t>C113</t>
+          <t>C119</t>
         </is>
       </c>
       <c r="N243" t="inlineStr">
@@ -14214,7 +14214,7 @@
       <c r="L244" t="inlineStr"/>
       <c r="M244" t="inlineStr">
         <is>
-          <t>C113</t>
+          <t>C119</t>
         </is>
       </c>
       <c r="N244" t="inlineStr">
@@ -14268,7 +14268,7 @@
       <c r="L245" t="inlineStr"/>
       <c r="M245" t="inlineStr">
         <is>
-          <t>C113</t>
+          <t>C119</t>
         </is>
       </c>
       <c r="N245" t="inlineStr">
@@ -14322,7 +14322,7 @@
       <c r="L246" t="inlineStr"/>
       <c r="M246" t="inlineStr">
         <is>
-          <t>C113</t>
+          <t>C119</t>
         </is>
       </c>
       <c r="N246" t="inlineStr">
@@ -14376,7 +14376,7 @@
       <c r="L247" t="inlineStr"/>
       <c r="M247" t="inlineStr">
         <is>
-          <t>C113</t>
+          <t>C119</t>
         </is>
       </c>
       <c r="N247" t="inlineStr">
@@ -14430,7 +14430,7 @@
       <c r="L248" t="inlineStr"/>
       <c r="M248" t="inlineStr">
         <is>
-          <t>C113</t>
+          <t>C119</t>
         </is>
       </c>
       <c r="N248" t="inlineStr">
@@ -14484,7 +14484,7 @@
       <c r="L249" t="inlineStr"/>
       <c r="M249" t="inlineStr">
         <is>
-          <t>C113</t>
+          <t>C119</t>
         </is>
       </c>
       <c r="N249" t="inlineStr">
@@ -14538,7 +14538,7 @@
       <c r="L250" t="inlineStr"/>
       <c r="M250" t="inlineStr">
         <is>
-          <t>C113</t>
+          <t>C119</t>
         </is>
       </c>
       <c r="N250" t="inlineStr">
@@ -14592,7 +14592,7 @@
       <c r="L251" t="inlineStr"/>
       <c r="M251" t="inlineStr">
         <is>
-          <t>C113</t>
+          <t>C119</t>
         </is>
       </c>
       <c r="N251" t="inlineStr">
@@ -14646,7 +14646,7 @@
       <c r="L252" t="inlineStr"/>
       <c r="M252" t="inlineStr">
         <is>
-          <t>C113</t>
+          <t>C119</t>
         </is>
       </c>
       <c r="N252" t="inlineStr">
@@ -14700,7 +14700,7 @@
       <c r="L253" t="inlineStr"/>
       <c r="M253" t="inlineStr">
         <is>
-          <t>C113</t>
+          <t>C119</t>
         </is>
       </c>
       <c r="N253" t="inlineStr">
@@ -14754,7 +14754,7 @@
       <c r="L254" t="inlineStr"/>
       <c r="M254" t="inlineStr">
         <is>
-          <t>C113</t>
+          <t>C119</t>
         </is>
       </c>
       <c r="N254" t="inlineStr">
@@ -14808,7 +14808,7 @@
       <c r="L255" t="inlineStr"/>
       <c r="M255" t="inlineStr">
         <is>
-          <t>C113</t>
+          <t>C119</t>
         </is>
       </c>
       <c r="N255" t="inlineStr">
@@ -14862,7 +14862,7 @@
       <c r="L256" t="inlineStr"/>
       <c r="M256" t="inlineStr">
         <is>
-          <t>C113</t>
+          <t>C119</t>
         </is>
       </c>
       <c r="N256" t="inlineStr">
@@ -14916,7 +14916,7 @@
       <c r="L257" t="inlineStr"/>
       <c r="M257" t="inlineStr">
         <is>
-          <t>C113</t>
+          <t>C119</t>
         </is>
       </c>
       <c r="N257" t="inlineStr">
@@ -14970,7 +14970,7 @@
       <c r="L258" t="inlineStr"/>
       <c r="M258" t="inlineStr">
         <is>
-          <t>C113</t>
+          <t>C119</t>
         </is>
       </c>
       <c r="N258" t="inlineStr">
@@ -15024,7 +15024,7 @@
       <c r="L259" t="inlineStr"/>
       <c r="M259" t="inlineStr">
         <is>
-          <t>C113</t>
+          <t>C119</t>
         </is>
       </c>
       <c r="N259" t="inlineStr">
@@ -15078,7 +15078,7 @@
       <c r="L260" t="inlineStr"/>
       <c r="M260" t="inlineStr">
         <is>
-          <t>C113</t>
+          <t>C119</t>
         </is>
       </c>
       <c r="N260" t="inlineStr">
@@ -15132,7 +15132,7 @@
       <c r="L261" t="inlineStr"/>
       <c r="M261" t="inlineStr">
         <is>
-          <t>C113</t>
+          <t>C119</t>
         </is>
       </c>
       <c r="N261" t="inlineStr">
@@ -15186,7 +15186,7 @@
       <c r="L262" t="inlineStr"/>
       <c r="M262" t="inlineStr">
         <is>
-          <t>C113</t>
+          <t>C119</t>
         </is>
       </c>
       <c r="N262" t="inlineStr">
@@ -15240,7 +15240,7 @@
       <c r="L263" t="inlineStr"/>
       <c r="M263" t="inlineStr">
         <is>
-          <t>C113</t>
+          <t>C119</t>
         </is>
       </c>
       <c r="N263" t="inlineStr">
@@ -15294,7 +15294,7 @@
       <c r="L264" t="inlineStr"/>
       <c r="M264" t="inlineStr">
         <is>
-          <t>C113</t>
+          <t>C119</t>
         </is>
       </c>
       <c r="N264" t="inlineStr">
@@ -15348,7 +15348,7 @@
       <c r="L265" t="inlineStr"/>
       <c r="M265" t="inlineStr">
         <is>
-          <t>C113</t>
+          <t>C119</t>
         </is>
       </c>
       <c r="N265" t="inlineStr">
@@ -15402,7 +15402,7 @@
       <c r="L266" t="inlineStr"/>
       <c r="M266" t="inlineStr">
         <is>
-          <t>C113</t>
+          <t>C119</t>
         </is>
       </c>
       <c r="N266" t="inlineStr">
@@ -15456,7 +15456,7 @@
       <c r="L267" t="inlineStr"/>
       <c r="M267" t="inlineStr">
         <is>
-          <t>C113</t>
+          <t>C119</t>
         </is>
       </c>
       <c r="N267" t="inlineStr">
@@ -15510,7 +15510,7 @@
       <c r="L268" t="inlineStr"/>
       <c r="M268" t="inlineStr">
         <is>
-          <t>C113</t>
+          <t>C119</t>
         </is>
       </c>
       <c r="N268" t="inlineStr">
@@ -15564,7 +15564,7 @@
       <c r="L269" t="inlineStr"/>
       <c r="M269" t="inlineStr">
         <is>
-          <t>C113</t>
+          <t>C119</t>
         </is>
       </c>
       <c r="N269" t="inlineStr">
@@ -15618,7 +15618,7 @@
       <c r="L270" t="inlineStr"/>
       <c r="M270" t="inlineStr">
         <is>
-          <t>C113</t>
+          <t>C119</t>
         </is>
       </c>
       <c r="N270" t="inlineStr">
@@ -15672,7 +15672,7 @@
       <c r="L271" t="inlineStr"/>
       <c r="M271" t="inlineStr">
         <is>
-          <t>C113</t>
+          <t>C119</t>
         </is>
       </c>
       <c r="N271" t="inlineStr">
@@ -15726,7 +15726,7 @@
       <c r="L272" t="inlineStr"/>
       <c r="M272" t="inlineStr">
         <is>
-          <t>C113</t>
+          <t>C119</t>
         </is>
       </c>
       <c r="N272" t="inlineStr">
@@ -15780,7 +15780,7 @@
       <c r="L273" t="inlineStr"/>
       <c r="M273" t="inlineStr">
         <is>
-          <t>C113</t>
+          <t>C119</t>
         </is>
       </c>
       <c r="N273" t="inlineStr">
@@ -15834,7 +15834,7 @@
       <c r="L274" t="inlineStr"/>
       <c r="M274" t="inlineStr">
         <is>
-          <t>C113</t>
+          <t>C119</t>
         </is>
       </c>
       <c r="N274" t="inlineStr">
@@ -15888,7 +15888,7 @@
       <c r="L275" t="inlineStr"/>
       <c r="M275" t="inlineStr">
         <is>
-          <t>C113</t>
+          <t>C119</t>
         </is>
       </c>
       <c r="N275" t="inlineStr">
@@ -15942,7 +15942,7 @@
       <c r="L276" t="inlineStr"/>
       <c r="M276" t="inlineStr">
         <is>
-          <t>C113</t>
+          <t>C119</t>
         </is>
       </c>
       <c r="N276" t="inlineStr">
@@ -15996,7 +15996,7 @@
       <c r="L277" t="inlineStr"/>
       <c r="M277" t="inlineStr">
         <is>
-          <t>C113</t>
+          <t>C119</t>
         </is>
       </c>
       <c r="N277" t="inlineStr">
@@ -16050,7 +16050,7 @@
       <c r="L278" t="inlineStr"/>
       <c r="M278" t="inlineStr">
         <is>
-          <t>C113</t>
+          <t>C119</t>
         </is>
       </c>
       <c r="N278" t="inlineStr">
@@ -16104,7 +16104,7 @@
       <c r="L279" t="inlineStr"/>
       <c r="M279" t="inlineStr">
         <is>
-          <t>C113</t>
+          <t>C119</t>
         </is>
       </c>
       <c r="N279" t="inlineStr">
@@ -16158,7 +16158,7 @@
       <c r="L280" t="inlineStr"/>
       <c r="M280" t="inlineStr">
         <is>
-          <t>C113</t>
+          <t>C119</t>
         </is>
       </c>
       <c r="N280" t="inlineStr">
@@ -16212,7 +16212,7 @@
       <c r="L281" t="inlineStr"/>
       <c r="M281" t="inlineStr">
         <is>
-          <t>C113</t>
+          <t>C119</t>
         </is>
       </c>
       <c r="N281" t="inlineStr">
@@ -16266,7 +16266,7 @@
       <c r="L282" t="inlineStr"/>
       <c r="M282" t="inlineStr">
         <is>
-          <t>C113</t>
+          <t>C119</t>
         </is>
       </c>
       <c r="N282" t="inlineStr">
@@ -16318,7 +16318,7 @@
       <c r="L283" t="inlineStr"/>
       <c r="M283" t="inlineStr">
         <is>
-          <t>C114</t>
+          <t>C120</t>
         </is>
       </c>
       <c r="N283" t="inlineStr">
@@ -16370,7 +16370,7 @@
       <c r="L284" t="inlineStr"/>
       <c r="M284" t="inlineStr">
         <is>
-          <t>C114</t>
+          <t>C120</t>
         </is>
       </c>
       <c r="N284" t="inlineStr">
@@ -16422,7 +16422,7 @@
       <c r="L285" t="inlineStr"/>
       <c r="M285" t="inlineStr">
         <is>
-          <t>C114</t>
+          <t>C120</t>
         </is>
       </c>
       <c r="N285" t="inlineStr">
@@ -16474,7 +16474,7 @@
       <c r="L286" t="inlineStr"/>
       <c r="M286" t="inlineStr">
         <is>
-          <t>C114</t>
+          <t>C120</t>
         </is>
       </c>
       <c r="N286" t="inlineStr">
@@ -16526,7 +16526,7 @@
       <c r="L287" t="inlineStr"/>
       <c r="M287" t="inlineStr">
         <is>
-          <t>C114</t>
+          <t>C120</t>
         </is>
       </c>
       <c r="N287" t="inlineStr">
@@ -16578,7 +16578,7 @@
       <c r="L288" t="inlineStr"/>
       <c r="M288" t="inlineStr">
         <is>
-          <t>C114</t>
+          <t>C120</t>
         </is>
       </c>
       <c r="N288" t="inlineStr">
@@ -16630,7 +16630,7 @@
       <c r="L289" t="inlineStr"/>
       <c r="M289" t="inlineStr">
         <is>
-          <t>C114</t>
+          <t>C120</t>
         </is>
       </c>
       <c r="N289" t="inlineStr">
@@ -16682,7 +16682,7 @@
       <c r="L290" t="inlineStr"/>
       <c r="M290" t="inlineStr">
         <is>
-          <t>C114</t>
+          <t>C120</t>
         </is>
       </c>
       <c r="N290" t="inlineStr">
@@ -16734,7 +16734,7 @@
       <c r="L291" t="inlineStr"/>
       <c r="M291" t="inlineStr">
         <is>
-          <t>C114</t>
+          <t>C120</t>
         </is>
       </c>
       <c r="N291" t="inlineStr">
@@ -16786,7 +16786,7 @@
       <c r="L292" t="inlineStr"/>
       <c r="M292" t="inlineStr">
         <is>
-          <t>C114</t>
+          <t>C120</t>
         </is>
       </c>
       <c r="N292" t="inlineStr">
@@ -16838,7 +16838,7 @@
       <c r="L293" t="inlineStr"/>
       <c r="M293" t="inlineStr">
         <is>
-          <t>C114</t>
+          <t>C120</t>
         </is>
       </c>
       <c r="N293" t="inlineStr">
@@ -16890,7 +16890,7 @@
       <c r="L294" t="inlineStr"/>
       <c r="M294" t="inlineStr">
         <is>
-          <t>C114</t>
+          <t>C120</t>
         </is>
       </c>
       <c r="N294" t="inlineStr">
@@ -16942,7 +16942,7 @@
       <c r="L295" t="inlineStr"/>
       <c r="M295" t="inlineStr">
         <is>
-          <t>C114</t>
+          <t>C120</t>
         </is>
       </c>
       <c r="N295" t="inlineStr">
@@ -16994,7 +16994,7 @@
       <c r="L296" t="inlineStr"/>
       <c r="M296" t="inlineStr">
         <is>
-          <t>C114</t>
+          <t>C120</t>
         </is>
       </c>
       <c r="N296" t="inlineStr">
@@ -17046,7 +17046,7 @@
       <c r="L297" t="inlineStr"/>
       <c r="M297" t="inlineStr">
         <is>
-          <t>C114</t>
+          <t>C120</t>
         </is>
       </c>
       <c r="N297" t="inlineStr">
@@ -17098,7 +17098,7 @@
       <c r="L298" t="inlineStr"/>
       <c r="M298" t="inlineStr">
         <is>
-          <t>C114</t>
+          <t>C120</t>
         </is>
       </c>
       <c r="N298" t="inlineStr">
@@ -17150,7 +17150,7 @@
       <c r="L299" t="inlineStr"/>
       <c r="M299" t="inlineStr">
         <is>
-          <t>C114</t>
+          <t>C120</t>
         </is>
       </c>
       <c r="N299" t="inlineStr">
@@ -17202,7 +17202,7 @@
       <c r="L300" t="inlineStr"/>
       <c r="M300" t="inlineStr">
         <is>
-          <t>C114</t>
+          <t>C120</t>
         </is>
       </c>
       <c r="N300" t="inlineStr">
@@ -17254,7 +17254,7 @@
       <c r="L301" t="inlineStr"/>
       <c r="M301" t="inlineStr">
         <is>
-          <t>C114</t>
+          <t>C120</t>
         </is>
       </c>
       <c r="N301" t="inlineStr">
@@ -17306,7 +17306,7 @@
       <c r="L302" t="inlineStr"/>
       <c r="M302" t="inlineStr">
         <is>
-          <t>C114</t>
+          <t>C120</t>
         </is>
       </c>
       <c r="N302" t="inlineStr">
@@ -17358,7 +17358,7 @@
       <c r="L303" t="inlineStr"/>
       <c r="M303" t="inlineStr">
         <is>
-          <t>C114</t>
+          <t>C120</t>
         </is>
       </c>
       <c r="N303" t="inlineStr">
@@ -17410,7 +17410,7 @@
       <c r="L304" t="inlineStr"/>
       <c r="M304" t="inlineStr">
         <is>
-          <t>C114</t>
+          <t>C120</t>
         </is>
       </c>
       <c r="N304" t="inlineStr">
@@ -17462,7 +17462,7 @@
       <c r="L305" t="inlineStr"/>
       <c r="M305" t="inlineStr">
         <is>
-          <t>C114</t>
+          <t>C120</t>
         </is>
       </c>
       <c r="N305" t="inlineStr">
@@ -17514,7 +17514,7 @@
       <c r="L306" t="inlineStr"/>
       <c r="M306" t="inlineStr">
         <is>
-          <t>C114</t>
+          <t>C120</t>
         </is>
       </c>
       <c r="N306" t="inlineStr">
@@ -17566,7 +17566,7 @@
       <c r="L307" t="inlineStr"/>
       <c r="M307" t="inlineStr">
         <is>
-          <t>C114</t>
+          <t>C120</t>
         </is>
       </c>
       <c r="N307" t="inlineStr">
@@ -17618,7 +17618,7 @@
       <c r="L308" t="inlineStr"/>
       <c r="M308" t="inlineStr">
         <is>
-          <t>C114</t>
+          <t>C120</t>
         </is>
       </c>
       <c r="N308" t="inlineStr">
@@ -17670,7 +17670,7 @@
       <c r="L309" t="inlineStr"/>
       <c r="M309" t="inlineStr">
         <is>
-          <t>C114</t>
+          <t>C120</t>
         </is>
       </c>
       <c r="N309" t="inlineStr">
@@ -17722,7 +17722,7 @@
       <c r="L310" t="inlineStr"/>
       <c r="M310" t="inlineStr">
         <is>
-          <t>C114</t>
+          <t>C120</t>
         </is>
       </c>
       <c r="N310" t="inlineStr">
@@ -17774,7 +17774,7 @@
       <c r="L311" t="inlineStr"/>
       <c r="M311" t="inlineStr">
         <is>
-          <t>C114</t>
+          <t>C120</t>
         </is>
       </c>
       <c r="N311" t="inlineStr">
@@ -17826,7 +17826,7 @@
       <c r="L312" t="inlineStr"/>
       <c r="M312" t="inlineStr">
         <is>
-          <t>C114</t>
+          <t>C120</t>
         </is>
       </c>
       <c r="N312" t="inlineStr">
@@ -17878,7 +17878,7 @@
       <c r="L313" t="inlineStr"/>
       <c r="M313" t="inlineStr">
         <is>
-          <t>C114</t>
+          <t>C120</t>
         </is>
       </c>
       <c r="N313" t="inlineStr">
@@ -17930,7 +17930,7 @@
       <c r="L314" t="inlineStr"/>
       <c r="M314" t="inlineStr">
         <is>
-          <t>C114</t>
+          <t>C120</t>
         </is>
       </c>
       <c r="N314" t="inlineStr">
@@ -17982,7 +17982,7 @@
       <c r="L315" t="inlineStr"/>
       <c r="M315" t="inlineStr">
         <is>
-          <t>C114</t>
+          <t>C120</t>
         </is>
       </c>
       <c r="N315" t="inlineStr">
@@ -18034,7 +18034,7 @@
       <c r="L316" t="inlineStr"/>
       <c r="M316" t="inlineStr">
         <is>
-          <t>C114</t>
+          <t>C120</t>
         </is>
       </c>
       <c r="N316" t="inlineStr">
@@ -18086,7 +18086,7 @@
       <c r="L317" t="inlineStr"/>
       <c r="M317" t="inlineStr">
         <is>
-          <t>C114</t>
+          <t>C120</t>
         </is>
       </c>
       <c r="N317" t="inlineStr">
@@ -18138,7 +18138,7 @@
       <c r="L318" t="inlineStr"/>
       <c r="M318" t="inlineStr">
         <is>
-          <t>C114</t>
+          <t>C120</t>
         </is>
       </c>
       <c r="N318" t="inlineStr">
@@ -18190,7 +18190,7 @@
       <c r="L319" t="inlineStr"/>
       <c r="M319" t="inlineStr">
         <is>
-          <t>C114</t>
+          <t>C120</t>
         </is>
       </c>
       <c r="N319" t="inlineStr">
@@ -18242,7 +18242,7 @@
       <c r="L320" t="inlineStr"/>
       <c r="M320" t="inlineStr">
         <is>
-          <t>C114</t>
+          <t>C120</t>
         </is>
       </c>
       <c r="N320" t="inlineStr">
@@ -18294,7 +18294,7 @@
       <c r="L321" t="inlineStr"/>
       <c r="M321" t="inlineStr">
         <is>
-          <t>C114</t>
+          <t>C120</t>
         </is>
       </c>
       <c r="N321" t="inlineStr">
@@ -18346,7 +18346,7 @@
       <c r="L322" t="inlineStr"/>
       <c r="M322" t="inlineStr">
         <is>
-          <t>C114</t>
+          <t>C120</t>
         </is>
       </c>
       <c r="N322" t="inlineStr">
@@ -18398,7 +18398,7 @@
       <c r="L323" t="inlineStr"/>
       <c r="M323" t="inlineStr">
         <is>
-          <t>C114</t>
+          <t>C120</t>
         </is>
       </c>
       <c r="N323" t="inlineStr">
@@ -18450,7 +18450,7 @@
       <c r="L324" t="inlineStr"/>
       <c r="M324" t="inlineStr">
         <is>
-          <t>C114</t>
+          <t>C120</t>
         </is>
       </c>
       <c r="N324" t="inlineStr">
@@ -18502,7 +18502,7 @@
       <c r="L325" t="inlineStr"/>
       <c r="M325" t="inlineStr">
         <is>
-          <t>C114</t>
+          <t>C120</t>
         </is>
       </c>
       <c r="N325" t="inlineStr">
@@ -18554,7 +18554,7 @@
       <c r="L326" t="inlineStr"/>
       <c r="M326" t="inlineStr">
         <is>
-          <t>C114</t>
+          <t>C120</t>
         </is>
       </c>
       <c r="N326" t="inlineStr">
@@ -18606,7 +18606,7 @@
       <c r="L327" t="inlineStr"/>
       <c r="M327" t="inlineStr">
         <is>
-          <t>C114</t>
+          <t>C120</t>
         </is>
       </c>
       <c r="N327" t="inlineStr">
@@ -18658,7 +18658,7 @@
       <c r="L328" t="inlineStr"/>
       <c r="M328" t="inlineStr">
         <is>
-          <t>C114</t>
+          <t>C120</t>
         </is>
       </c>
       <c r="N328" t="inlineStr">
@@ -18710,7 +18710,7 @@
       <c r="L329" t="inlineStr"/>
       <c r="M329" t="inlineStr">
         <is>
-          <t>C114</t>
+          <t>C120</t>
         </is>
       </c>
       <c r="N329" t="inlineStr">
@@ -18762,7 +18762,7 @@
       <c r="L330" t="inlineStr"/>
       <c r="M330" t="inlineStr">
         <is>
-          <t>C114</t>
+          <t>C120</t>
         </is>
       </c>
       <c r="N330" t="inlineStr">
@@ -18814,7 +18814,7 @@
       <c r="L331" t="inlineStr"/>
       <c r="M331" t="inlineStr">
         <is>
-          <t>C114</t>
+          <t>C120</t>
         </is>
       </c>
       <c r="N331" t="inlineStr">
@@ -18866,7 +18866,7 @@
       <c r="L332" t="inlineStr"/>
       <c r="M332" t="inlineStr">
         <is>
-          <t>C114</t>
+          <t>C120</t>
         </is>
       </c>
       <c r="N332" t="inlineStr">
@@ -18918,7 +18918,7 @@
       <c r="L333" t="inlineStr"/>
       <c r="M333" t="inlineStr">
         <is>
-          <t>C114</t>
+          <t>C120</t>
         </is>
       </c>
       <c r="N333" t="inlineStr">
@@ -18970,7 +18970,7 @@
       <c r="L334" t="inlineStr"/>
       <c r="M334" t="inlineStr">
         <is>
-          <t>C114</t>
+          <t>C120</t>
         </is>
       </c>
       <c r="N334" t="inlineStr">
@@ -19022,7 +19022,7 @@
       <c r="L335" t="inlineStr"/>
       <c r="M335" t="inlineStr">
         <is>
-          <t>C114</t>
+          <t>C120</t>
         </is>
       </c>
       <c r="N335" t="inlineStr">
@@ -19074,7 +19074,7 @@
       <c r="L336" t="inlineStr"/>
       <c r="M336" t="inlineStr">
         <is>
-          <t>C114</t>
+          <t>C120</t>
         </is>
       </c>
       <c r="N336" t="inlineStr">
@@ -19126,7 +19126,7 @@
       <c r="L337" t="inlineStr"/>
       <c r="M337" t="inlineStr">
         <is>
-          <t>C114</t>
+          <t>C120</t>
         </is>
       </c>
       <c r="N337" t="inlineStr">
@@ -19178,7 +19178,7 @@
       <c r="L338" t="inlineStr"/>
       <c r="M338" t="inlineStr">
         <is>
-          <t>C114</t>
+          <t>C120</t>
         </is>
       </c>
       <c r="N338" t="inlineStr">
@@ -19232,7 +19232,7 @@
       <c r="L339" t="inlineStr"/>
       <c r="M339" t="inlineStr">
         <is>
-          <t>C065</t>
+          <t>C075</t>
         </is>
       </c>
       <c r="N339" t="inlineStr">
@@ -19286,7 +19286,7 @@
       <c r="L340" t="inlineStr"/>
       <c r="M340" t="inlineStr">
         <is>
-          <t>C067</t>
+          <t>C077</t>
         </is>
       </c>
       <c r="N340" t="inlineStr">
@@ -19340,7 +19340,7 @@
       <c r="L341" t="inlineStr"/>
       <c r="M341" t="inlineStr">
         <is>
-          <t>C068</t>
+          <t>C078</t>
         </is>
       </c>
       <c r="N341" t="inlineStr">
@@ -19394,7 +19394,7 @@
       <c r="L342" t="inlineStr"/>
       <c r="M342" t="inlineStr">
         <is>
-          <t>C069</t>
+          <t>C079</t>
         </is>
       </c>
       <c r="N342" t="inlineStr">
@@ -19448,7 +19448,7 @@
       <c r="L343" t="inlineStr"/>
       <c r="M343" t="inlineStr">
         <is>
-          <t>C065</t>
+          <t>C075</t>
         </is>
       </c>
       <c r="N343" t="inlineStr">
@@ -19502,7 +19502,7 @@
       <c r="L344" t="inlineStr"/>
       <c r="M344" t="inlineStr">
         <is>
-          <t>C066</t>
+          <t>C076</t>
         </is>
       </c>
       <c r="N344" t="inlineStr">
@@ -19556,7 +19556,7 @@
       <c r="L345" t="inlineStr"/>
       <c r="M345" t="inlineStr">
         <is>
-          <t>C065</t>
+          <t>C075</t>
         </is>
       </c>
       <c r="N345" t="inlineStr">
@@ -19610,7 +19610,7 @@
       <c r="L346" t="inlineStr"/>
       <c r="M346" t="inlineStr">
         <is>
-          <t>C066</t>
+          <t>C076</t>
         </is>
       </c>
       <c r="N346" t="inlineStr">
@@ -19664,7 +19664,7 @@
       <c r="L347" t="inlineStr"/>
       <c r="M347" t="inlineStr">
         <is>
-          <t>C065</t>
+          <t>C075</t>
         </is>
       </c>
       <c r="N347" t="inlineStr">
@@ -19718,7 +19718,7 @@
       <c r="L348" t="inlineStr"/>
       <c r="M348" t="inlineStr">
         <is>
-          <t>C067</t>
+          <t>C077</t>
         </is>
       </c>
       <c r="N348" t="inlineStr">
@@ -19772,7 +19772,7 @@
       <c r="L349" t="inlineStr"/>
       <c r="M349" t="inlineStr">
         <is>
-          <t>C068</t>
+          <t>C078</t>
         </is>
       </c>
       <c r="N349" t="inlineStr">
@@ -19826,7 +19826,7 @@
       <c r="L350" t="inlineStr"/>
       <c r="M350" t="inlineStr">
         <is>
-          <t>C069</t>
+          <t>C079</t>
         </is>
       </c>
       <c r="N350" t="inlineStr">
@@ -19880,7 +19880,7 @@
       <c r="L351" t="inlineStr"/>
       <c r="M351" t="inlineStr">
         <is>
-          <t>C065</t>
+          <t>C075</t>
         </is>
       </c>
       <c r="N351" t="inlineStr">
@@ -19934,7 +19934,7 @@
       <c r="L352" t="inlineStr"/>
       <c r="M352" t="inlineStr">
         <is>
-          <t>C067</t>
+          <t>C077</t>
         </is>
       </c>
       <c r="N352" t="inlineStr">
@@ -19988,7 +19988,7 @@
       <c r="L353" t="inlineStr"/>
       <c r="M353" t="inlineStr">
         <is>
-          <t>C068</t>
+          <t>C078</t>
         </is>
       </c>
       <c r="N353" t="inlineStr">
@@ -20042,7 +20042,7 @@
       <c r="L354" t="inlineStr"/>
       <c r="M354" t="inlineStr">
         <is>
-          <t>C069</t>
+          <t>C079</t>
         </is>
       </c>
       <c r="N354" t="inlineStr">
@@ -20096,7 +20096,7 @@
       <c r="L355" t="inlineStr"/>
       <c r="M355" t="inlineStr">
         <is>
-          <t>C066</t>
+          <t>C076</t>
         </is>
       </c>
       <c r="N355" t="inlineStr">
@@ -20150,7 +20150,7 @@
       <c r="L356" t="inlineStr"/>
       <c r="M356" t="inlineStr">
         <is>
-          <t>C070</t>
+          <t>C080</t>
         </is>
       </c>
       <c r="N356" t="inlineStr">
@@ -20204,7 +20204,7 @@
       <c r="L357" t="inlineStr"/>
       <c r="M357" t="inlineStr">
         <is>
-          <t>C071</t>
+          <t>C081</t>
         </is>
       </c>
       <c r="N357" t="inlineStr">
@@ -20258,7 +20258,7 @@
       <c r="L358" t="inlineStr"/>
       <c r="M358" t="inlineStr">
         <is>
-          <t>C065</t>
+          <t>C075</t>
         </is>
       </c>
       <c r="N358" t="inlineStr">
@@ -20312,7 +20312,7 @@
       <c r="L359" t="inlineStr"/>
       <c r="M359" t="inlineStr">
         <is>
-          <t>C067</t>
+          <t>C077</t>
         </is>
       </c>
       <c r="N359" t="inlineStr">
@@ -20366,7 +20366,7 @@
       <c r="L360" t="inlineStr"/>
       <c r="M360" t="inlineStr">
         <is>
-          <t>C068</t>
+          <t>C078</t>
         </is>
       </c>
       <c r="N360" t="inlineStr">
@@ -20420,7 +20420,7 @@
       <c r="L361" t="inlineStr"/>
       <c r="M361" t="inlineStr">
         <is>
-          <t>C069</t>
+          <t>C079</t>
         </is>
       </c>
       <c r="N361" t="inlineStr">
@@ -20474,7 +20474,7 @@
       <c r="L362" t="inlineStr"/>
       <c r="M362" t="inlineStr">
         <is>
-          <t>C065</t>
+          <t>C075</t>
         </is>
       </c>
       <c r="N362" t="inlineStr">
@@ -20528,7 +20528,7 @@
       <c r="L363" t="inlineStr"/>
       <c r="M363" t="inlineStr">
         <is>
-          <t>C067</t>
+          <t>C077</t>
         </is>
       </c>
       <c r="N363" t="inlineStr">
@@ -20582,7 +20582,7 @@
       <c r="L364" t="inlineStr"/>
       <c r="M364" t="inlineStr">
         <is>
-          <t>C068</t>
+          <t>C078</t>
         </is>
       </c>
       <c r="N364" t="inlineStr">
@@ -20636,7 +20636,7 @@
       <c r="L365" t="inlineStr"/>
       <c r="M365" t="inlineStr">
         <is>
-          <t>C069</t>
+          <t>C079</t>
         </is>
       </c>
       <c r="N365" t="inlineStr">
@@ -20690,7 +20690,7 @@
       <c r="L366" t="inlineStr"/>
       <c r="M366" t="inlineStr">
         <is>
-          <t>C065</t>
+          <t>C075</t>
         </is>
       </c>
       <c r="N366" t="inlineStr">
@@ -20744,7 +20744,7 @@
       <c r="L367" t="inlineStr"/>
       <c r="M367" t="inlineStr">
         <is>
-          <t>C067</t>
+          <t>C077</t>
         </is>
       </c>
       <c r="N367" t="inlineStr">
@@ -20798,7 +20798,7 @@
       <c r="L368" t="inlineStr"/>
       <c r="M368" t="inlineStr">
         <is>
-          <t>C068</t>
+          <t>C078</t>
         </is>
       </c>
       <c r="N368" t="inlineStr">
@@ -20852,7 +20852,7 @@
       <c r="L369" t="inlineStr"/>
       <c r="M369" t="inlineStr">
         <is>
-          <t>C069</t>
+          <t>C079</t>
         </is>
       </c>
       <c r="N369" t="inlineStr">
@@ -20906,7 +20906,7 @@
       <c r="L370" t="inlineStr"/>
       <c r="M370" t="inlineStr">
         <is>
-          <t>C065</t>
+          <t>C075</t>
         </is>
       </c>
       <c r="N370" t="inlineStr">
@@ -20960,7 +20960,7 @@
       <c r="L371" t="inlineStr"/>
       <c r="M371" t="inlineStr">
         <is>
-          <t>C067</t>
+          <t>C077</t>
         </is>
       </c>
       <c r="N371" t="inlineStr">
@@ -21014,7 +21014,7 @@
       <c r="L372" t="inlineStr"/>
       <c r="M372" t="inlineStr">
         <is>
-          <t>C068</t>
+          <t>C078</t>
         </is>
       </c>
       <c r="N372" t="inlineStr">
@@ -21068,7 +21068,7 @@
       <c r="L373" t="inlineStr"/>
       <c r="M373" t="inlineStr">
         <is>
-          <t>C069</t>
+          <t>C079</t>
         </is>
       </c>
       <c r="N373" t="inlineStr">
@@ -21122,7 +21122,7 @@
       <c r="L374" t="inlineStr"/>
       <c r="M374" t="inlineStr">
         <is>
-          <t>C065</t>
+          <t>C075</t>
         </is>
       </c>
       <c r="N374" t="inlineStr">
@@ -21176,7 +21176,7 @@
       <c r="L375" t="inlineStr"/>
       <c r="M375" t="inlineStr">
         <is>
-          <t>C067</t>
+          <t>C077</t>
         </is>
       </c>
       <c r="N375" t="inlineStr">
@@ -21230,7 +21230,7 @@
       <c r="L376" t="inlineStr"/>
       <c r="M376" t="inlineStr">
         <is>
-          <t>C068</t>
+          <t>C078</t>
         </is>
       </c>
       <c r="N376" t="inlineStr">
@@ -21284,7 +21284,7 @@
       <c r="L377" t="inlineStr"/>
       <c r="M377" t="inlineStr">
         <is>
-          <t>C069</t>
+          <t>C079</t>
         </is>
       </c>
       <c r="N377" t="inlineStr">
@@ -21338,7 +21338,7 @@
       <c r="L378" t="inlineStr"/>
       <c r="M378" t="inlineStr">
         <is>
-          <t>C066</t>
+          <t>C076</t>
         </is>
       </c>
       <c r="N378" t="inlineStr">
@@ -21392,7 +21392,7 @@
       <c r="L379" t="inlineStr"/>
       <c r="M379" t="inlineStr">
         <is>
-          <t>C070</t>
+          <t>C080</t>
         </is>
       </c>
       <c r="N379" t="inlineStr">
@@ -21446,7 +21446,7 @@
       <c r="L380" t="inlineStr"/>
       <c r="M380" t="inlineStr">
         <is>
-          <t>C071</t>
+          <t>C081</t>
         </is>
       </c>
       <c r="N380" t="inlineStr">
@@ -21500,7 +21500,7 @@
       <c r="L381" t="inlineStr"/>
       <c r="M381" t="inlineStr">
         <is>
-          <t>C058</t>
+          <t>C068</t>
         </is>
       </c>
       <c r="N381" t="inlineStr">
@@ -21554,7 +21554,7 @@
       <c r="L382" t="inlineStr"/>
       <c r="M382" t="inlineStr">
         <is>
-          <t>C058</t>
+          <t>C068</t>
         </is>
       </c>
       <c r="N382" t="inlineStr">
@@ -21608,7 +21608,7 @@
       <c r="L383" t="inlineStr"/>
       <c r="M383" t="inlineStr">
         <is>
-          <t>C057</t>
+          <t>C067</t>
         </is>
       </c>
       <c r="N383" t="inlineStr">
@@ -21660,7 +21660,7 @@
       <c r="L384" t="inlineStr"/>
       <c r="M384" t="inlineStr">
         <is>
-          <t>C056</t>
+          <t>C066</t>
         </is>
       </c>
       <c r="N384" t="inlineStr">
@@ -21714,7 +21714,7 @@
       <c r="L385" t="inlineStr"/>
       <c r="M385" t="inlineStr">
         <is>
-          <t>C058</t>
+          <t>C068</t>
         </is>
       </c>
       <c r="N385" t="inlineStr">
@@ -21766,7 +21766,7 @@
       <c r="L386" t="inlineStr"/>
       <c r="M386" t="inlineStr">
         <is>
-          <t>C056</t>
+          <t>C066</t>
         </is>
       </c>
       <c r="N386" t="inlineStr">
@@ -21820,7 +21820,7 @@
       <c r="L387" t="inlineStr"/>
       <c r="M387" t="inlineStr">
         <is>
-          <t>C057</t>
+          <t>C067</t>
         </is>
       </c>
       <c r="N387" t="inlineStr">
@@ -21874,7 +21874,7 @@
       <c r="L388" t="inlineStr"/>
       <c r="M388" t="inlineStr">
         <is>
-          <t>C057</t>
+          <t>C067</t>
         </is>
       </c>
       <c r="N388" t="inlineStr">
@@ -21928,7 +21928,7 @@
       <c r="L389" t="inlineStr"/>
       <c r="M389" t="inlineStr">
         <is>
-          <t>C057</t>
+          <t>C067</t>
         </is>
       </c>
       <c r="N389" t="inlineStr">
@@ -21982,7 +21982,7 @@
       <c r="L390" t="inlineStr"/>
       <c r="M390" t="inlineStr">
         <is>
-          <t>C057</t>
+          <t>C067</t>
         </is>
       </c>
       <c r="N390" t="inlineStr">
@@ -22034,7 +22034,7 @@
       <c r="L391" t="inlineStr"/>
       <c r="M391" t="inlineStr">
         <is>
-          <t>C056</t>
+          <t>C066</t>
         </is>
       </c>
       <c r="N391" t="inlineStr">
@@ -22088,7 +22088,7 @@
       <c r="L392" t="inlineStr"/>
       <c r="M392" t="inlineStr">
         <is>
-          <t>C057</t>
+          <t>C067</t>
         </is>
       </c>
       <c r="N392" t="inlineStr">
@@ -22142,7 +22142,7 @@
       <c r="L393" t="inlineStr"/>
       <c r="M393" t="inlineStr">
         <is>
-          <t>C057</t>
+          <t>C067</t>
         </is>
       </c>
       <c r="N393" t="inlineStr">
@@ -22194,7 +22194,7 @@
       <c r="L394" t="inlineStr"/>
       <c r="M394" t="inlineStr">
         <is>
-          <t>C056</t>
+          <t>C066</t>
         </is>
       </c>
       <c r="N394" t="inlineStr">
@@ -22248,7 +22248,7 @@
       <c r="L395" t="inlineStr"/>
       <c r="M395" t="inlineStr">
         <is>
-          <t>C057</t>
+          <t>C067</t>
         </is>
       </c>
       <c r="N395" t="inlineStr">
@@ -22302,7 +22302,7 @@
       <c r="L396" t="inlineStr"/>
       <c r="M396" t="inlineStr">
         <is>
-          <t>C057</t>
+          <t>C067</t>
         </is>
       </c>
       <c r="N396" t="inlineStr">
@@ -22354,7 +22354,7 @@
       <c r="L397" t="inlineStr"/>
       <c r="M397" t="inlineStr">
         <is>
-          <t>C056</t>
+          <t>C066</t>
         </is>
       </c>
       <c r="N397" t="inlineStr">
@@ -22408,7 +22408,7 @@
       <c r="L398" t="inlineStr"/>
       <c r="M398" t="inlineStr">
         <is>
-          <t>C057</t>
+          <t>C067</t>
         </is>
       </c>
       <c r="N398" t="inlineStr">
@@ -22462,7 +22462,7 @@
       <c r="L399" t="inlineStr"/>
       <c r="M399" t="inlineStr">
         <is>
-          <t>C057</t>
+          <t>C067</t>
         </is>
       </c>
       <c r="N399" t="inlineStr">
@@ -22514,7 +22514,7 @@
       <c r="L400" t="inlineStr"/>
       <c r="M400" t="inlineStr">
         <is>
-          <t>C056</t>
+          <t>C066</t>
         </is>
       </c>
       <c r="N400" t="inlineStr">
@@ -22568,7 +22568,7 @@
       <c r="L401" t="inlineStr"/>
       <c r="M401" t="inlineStr">
         <is>
-          <t>C057</t>
+          <t>C067</t>
         </is>
       </c>
       <c r="N401" t="inlineStr">
@@ -22620,7 +22620,7 @@
       <c r="L402" t="inlineStr"/>
       <c r="M402" t="inlineStr">
         <is>
-          <t>C056</t>
+          <t>C066</t>
         </is>
       </c>
       <c r="N402" t="inlineStr">
@@ -22674,7 +22674,7 @@
       <c r="L403" t="inlineStr"/>
       <c r="M403" t="inlineStr">
         <is>
-          <t>C057</t>
+          <t>C067</t>
         </is>
       </c>
       <c r="N403" t="inlineStr">
@@ -22728,7 +22728,7 @@
       <c r="L404" t="inlineStr"/>
       <c r="M404" t="inlineStr">
         <is>
-          <t>C057</t>
+          <t>C067</t>
         </is>
       </c>
       <c r="N404" t="inlineStr">
@@ -22780,7 +22780,7 @@
       <c r="L405" t="inlineStr"/>
       <c r="M405" t="inlineStr">
         <is>
-          <t>C056</t>
+          <t>C066</t>
         </is>
       </c>
       <c r="N405" t="inlineStr">
@@ -22834,7 +22834,7 @@
       <c r="L406" t="inlineStr"/>
       <c r="M406" t="inlineStr">
         <is>
-          <t>C057</t>
+          <t>C067</t>
         </is>
       </c>
       <c r="N406" t="inlineStr">
@@ -22888,7 +22888,7 @@
       <c r="L407" t="inlineStr"/>
       <c r="M407" t="inlineStr">
         <is>
-          <t>C057</t>
+          <t>C067</t>
         </is>
       </c>
       <c r="N407" t="inlineStr">
@@ -22940,7 +22940,7 @@
       <c r="L408" t="inlineStr"/>
       <c r="M408" t="inlineStr">
         <is>
-          <t>C056</t>
+          <t>C066</t>
         </is>
       </c>
       <c r="N408" t="inlineStr">
@@ -22994,7 +22994,7 @@
       <c r="L409" t="inlineStr"/>
       <c r="M409" t="inlineStr">
         <is>
-          <t>C057</t>
+          <t>C067</t>
         </is>
       </c>
       <c r="N409" t="inlineStr">
@@ -23046,7 +23046,7 @@
       <c r="L410" t="inlineStr"/>
       <c r="M410" t="inlineStr">
         <is>
-          <t>C056</t>
+          <t>C066</t>
         </is>
       </c>
       <c r="N410" t="inlineStr">
@@ -23098,7 +23098,7 @@
       <c r="L411" t="inlineStr"/>
       <c r="M411" t="inlineStr">
         <is>
-          <t>C056</t>
+          <t>C066</t>
         </is>
       </c>
       <c r="N411" t="inlineStr">
@@ -23152,7 +23152,7 @@
       <c r="L412" t="inlineStr"/>
       <c r="M412" t="inlineStr">
         <is>
-          <t>C057</t>
+          <t>C067</t>
         </is>
       </c>
       <c r="N412" t="inlineStr">
@@ -23206,7 +23206,7 @@
       <c r="L413" t="inlineStr"/>
       <c r="M413" t="inlineStr">
         <is>
-          <t>C061</t>
+          <t>C071</t>
         </is>
       </c>
       <c r="N413" t="inlineStr">
@@ -23260,7 +23260,7 @@
       <c r="L414" t="inlineStr"/>
       <c r="M414" t="inlineStr">
         <is>
-          <t>C061</t>
+          <t>C071</t>
         </is>
       </c>
       <c r="N414" t="inlineStr">
@@ -23314,7 +23314,7 @@
       <c r="L415" t="inlineStr"/>
       <c r="M415" t="inlineStr">
         <is>
-          <t>C060</t>
+          <t>C070</t>
         </is>
       </c>
       <c r="N415" t="inlineStr">
@@ -23366,7 +23366,7 @@
       <c r="L416" t="inlineStr"/>
       <c r="M416" t="inlineStr">
         <is>
-          <t>C059</t>
+          <t>C069</t>
         </is>
       </c>
       <c r="N416" t="inlineStr">
@@ -23420,7 +23420,7 @@
       <c r="L417" t="inlineStr"/>
       <c r="M417" t="inlineStr">
         <is>
-          <t>C061</t>
+          <t>C071</t>
         </is>
       </c>
       <c r="N417" t="inlineStr">
@@ -23472,7 +23472,7 @@
       <c r="L418" t="inlineStr"/>
       <c r="M418" t="inlineStr">
         <is>
-          <t>C059</t>
+          <t>C069</t>
         </is>
       </c>
       <c r="N418" t="inlineStr">
@@ -23526,7 +23526,7 @@
       <c r="L419" t="inlineStr"/>
       <c r="M419" t="inlineStr">
         <is>
-          <t>C060</t>
+          <t>C070</t>
         </is>
       </c>
       <c r="N419" t="inlineStr">
@@ -23580,7 +23580,7 @@
       <c r="L420" t="inlineStr"/>
       <c r="M420" t="inlineStr">
         <is>
-          <t>C060</t>
+          <t>C070</t>
         </is>
       </c>
       <c r="N420" t="inlineStr">
@@ -23634,7 +23634,7 @@
       <c r="L421" t="inlineStr"/>
       <c r="M421" t="inlineStr">
         <is>
-          <t>C060</t>
+          <t>C070</t>
         </is>
       </c>
       <c r="N421" t="inlineStr">
@@ -23688,7 +23688,7 @@
       <c r="L422" t="inlineStr"/>
       <c r="M422" t="inlineStr">
         <is>
-          <t>C060</t>
+          <t>C070</t>
         </is>
       </c>
       <c r="N422" t="inlineStr">
@@ -23740,7 +23740,7 @@
       <c r="L423" t="inlineStr"/>
       <c r="M423" t="inlineStr">
         <is>
-          <t>C059</t>
+          <t>C069</t>
         </is>
       </c>
       <c r="N423" t="inlineStr">
@@ -23794,7 +23794,7 @@
       <c r="L424" t="inlineStr"/>
       <c r="M424" t="inlineStr">
         <is>
-          <t>C060</t>
+          <t>C070</t>
         </is>
       </c>
       <c r="N424" t="inlineStr">
@@ -23848,7 +23848,7 @@
       <c r="L425" t="inlineStr"/>
       <c r="M425" t="inlineStr">
         <is>
-          <t>C060</t>
+          <t>C070</t>
         </is>
       </c>
       <c r="N425" t="inlineStr">
@@ -23900,7 +23900,7 @@
       <c r="L426" t="inlineStr"/>
       <c r="M426" t="inlineStr">
         <is>
-          <t>C059</t>
+          <t>C069</t>
         </is>
       </c>
       <c r="N426" t="inlineStr">
@@ -23954,7 +23954,7 @@
       <c r="L427" t="inlineStr"/>
       <c r="M427" t="inlineStr">
         <is>
-          <t>C060</t>
+          <t>C070</t>
         </is>
       </c>
       <c r="N427" t="inlineStr">
@@ -24008,7 +24008,7 @@
       <c r="L428" t="inlineStr"/>
       <c r="M428" t="inlineStr">
         <is>
-          <t>C060</t>
+          <t>C070</t>
         </is>
       </c>
       <c r="N428" t="inlineStr">
@@ -24060,7 +24060,7 @@
       <c r="L429" t="inlineStr"/>
       <c r="M429" t="inlineStr">
         <is>
-          <t>C059</t>
+          <t>C069</t>
         </is>
       </c>
       <c r="N429" t="inlineStr">
@@ -24114,7 +24114,7 @@
       <c r="L430" t="inlineStr"/>
       <c r="M430" t="inlineStr">
         <is>
-          <t>C060</t>
+          <t>C070</t>
         </is>
       </c>
       <c r="N430" t="inlineStr">
@@ -24168,7 +24168,7 @@
       <c r="L431" t="inlineStr"/>
       <c r="M431" t="inlineStr">
         <is>
-          <t>C060</t>
+          <t>C070</t>
         </is>
       </c>
       <c r="N431" t="inlineStr">
@@ -24220,7 +24220,7 @@
       <c r="L432" t="inlineStr"/>
       <c r="M432" t="inlineStr">
         <is>
-          <t>C059</t>
+          <t>C069</t>
         </is>
       </c>
       <c r="N432" t="inlineStr">
@@ -24274,7 +24274,7 @@
       <c r="L433" t="inlineStr"/>
       <c r="M433" t="inlineStr">
         <is>
-          <t>C060</t>
+          <t>C070</t>
         </is>
       </c>
       <c r="N433" t="inlineStr">
@@ -24326,7 +24326,7 @@
       <c r="L434" t="inlineStr"/>
       <c r="M434" t="inlineStr">
         <is>
-          <t>C059</t>
+          <t>C069</t>
         </is>
       </c>
       <c r="N434" t="inlineStr">
@@ -24380,7 +24380,7 @@
       <c r="L435" t="inlineStr"/>
       <c r="M435" t="inlineStr">
         <is>
-          <t>C060</t>
+          <t>C070</t>
         </is>
       </c>
       <c r="N435" t="inlineStr">
@@ -24434,7 +24434,7 @@
       <c r="L436" t="inlineStr"/>
       <c r="M436" t="inlineStr">
         <is>
-          <t>C060</t>
+          <t>C070</t>
         </is>
       </c>
       <c r="N436" t="inlineStr">
@@ -24486,7 +24486,7 @@
       <c r="L437" t="inlineStr"/>
       <c r="M437" t="inlineStr">
         <is>
-          <t>C059</t>
+          <t>C069</t>
         </is>
       </c>
       <c r="N437" t="inlineStr">
@@ -24540,7 +24540,7 @@
       <c r="L438" t="inlineStr"/>
       <c r="M438" t="inlineStr">
         <is>
-          <t>C060</t>
+          <t>C070</t>
         </is>
       </c>
       <c r="N438" t="inlineStr">
@@ -24594,7 +24594,7 @@
       <c r="L439" t="inlineStr"/>
       <c r="M439" t="inlineStr">
         <is>
-          <t>C060</t>
+          <t>C070</t>
         </is>
       </c>
       <c r="N439" t="inlineStr">
@@ -24646,7 +24646,7 @@
       <c r="L440" t="inlineStr"/>
       <c r="M440" t="inlineStr">
         <is>
-          <t>C059</t>
+          <t>C069</t>
         </is>
       </c>
       <c r="N440" t="inlineStr">
@@ -24700,7 +24700,7 @@
       <c r="L441" t="inlineStr"/>
       <c r="M441" t="inlineStr">
         <is>
-          <t>C060</t>
+          <t>C070</t>
         </is>
       </c>
       <c r="N441" t="inlineStr">
@@ -24752,7 +24752,7 @@
       <c r="L442" t="inlineStr"/>
       <c r="M442" t="inlineStr">
         <is>
-          <t>C059</t>
+          <t>C069</t>
         </is>
       </c>
       <c r="N442" t="inlineStr">
@@ -24804,7 +24804,7 @@
       <c r="L443" t="inlineStr"/>
       <c r="M443" t="inlineStr">
         <is>
-          <t>C059</t>
+          <t>C069</t>
         </is>
       </c>
       <c r="N443" t="inlineStr">
@@ -24858,7 +24858,7 @@
       <c r="L444" t="inlineStr"/>
       <c r="M444" t="inlineStr">
         <is>
-          <t>C060</t>
+          <t>C070</t>
         </is>
       </c>
       <c r="N444" t="inlineStr">
@@ -24912,7 +24912,7 @@
       <c r="L445" t="inlineStr"/>
       <c r="M445" t="inlineStr">
         <is>
-          <t>C064</t>
+          <t>C074</t>
         </is>
       </c>
       <c r="N445" t="inlineStr">
@@ -24966,7 +24966,7 @@
       <c r="L446" t="inlineStr"/>
       <c r="M446" t="inlineStr">
         <is>
-          <t>C064</t>
+          <t>C074</t>
         </is>
       </c>
       <c r="N446" t="inlineStr">
@@ -25020,7 +25020,7 @@
       <c r="L447" t="inlineStr"/>
       <c r="M447" t="inlineStr">
         <is>
-          <t>C063</t>
+          <t>C073</t>
         </is>
       </c>
       <c r="N447" t="inlineStr">
@@ -25072,7 +25072,7 @@
       <c r="L448" t="inlineStr"/>
       <c r="M448" t="inlineStr">
         <is>
-          <t>C062</t>
+          <t>C072</t>
         </is>
       </c>
       <c r="N448" t="inlineStr">
@@ -25126,7 +25126,7 @@
       <c r="L449" t="inlineStr"/>
       <c r="M449" t="inlineStr">
         <is>
-          <t>C064</t>
+          <t>C074</t>
         </is>
       </c>
       <c r="N449" t="inlineStr">
@@ -25178,7 +25178,7 @@
       <c r="L450" t="inlineStr"/>
       <c r="M450" t="inlineStr">
         <is>
-          <t>C062</t>
+          <t>C072</t>
         </is>
       </c>
       <c r="N450" t="inlineStr">
@@ -25232,7 +25232,7 @@
       <c r="L451" t="inlineStr"/>
       <c r="M451" t="inlineStr">
         <is>
-          <t>C063</t>
+          <t>C073</t>
         </is>
       </c>
       <c r="N451" t="inlineStr">
@@ -25286,7 +25286,7 @@
       <c r="L452" t="inlineStr"/>
       <c r="M452" t="inlineStr">
         <is>
-          <t>C063</t>
+          <t>C073</t>
         </is>
       </c>
       <c r="N452" t="inlineStr">
@@ -25340,7 +25340,7 @@
       <c r="L453" t="inlineStr"/>
       <c r="M453" t="inlineStr">
         <is>
-          <t>C063</t>
+          <t>C073</t>
         </is>
       </c>
       <c r="N453" t="inlineStr">
@@ -25392,7 +25392,7 @@
       <c r="L454" t="inlineStr"/>
       <c r="M454" t="inlineStr">
         <is>
-          <t>C062</t>
+          <t>C072</t>
         </is>
       </c>
       <c r="N454" t="inlineStr">
@@ -25446,7 +25446,7 @@
       <c r="L455" t="inlineStr"/>
       <c r="M455" t="inlineStr">
         <is>
-          <t>C063</t>
+          <t>C073</t>
         </is>
       </c>
       <c r="N455" t="inlineStr">
@@ -25498,7 +25498,7 @@
       <c r="L456" t="inlineStr"/>
       <c r="M456" t="inlineStr">
         <is>
-          <t>C062</t>
+          <t>C072</t>
         </is>
       </c>
       <c r="N456" t="inlineStr">
@@ -25552,7 +25552,7 @@
       <c r="L457" t="inlineStr"/>
       <c r="M457" t="inlineStr">
         <is>
-          <t>C063</t>
+          <t>C073</t>
         </is>
       </c>
       <c r="N457" t="inlineStr">
@@ -25604,7 +25604,7 @@
       <c r="L458" t="inlineStr"/>
       <c r="M458" t="inlineStr">
         <is>
-          <t>C062</t>
+          <t>C072</t>
         </is>
       </c>
       <c r="N458" t="inlineStr">
@@ -25658,7 +25658,7 @@
       <c r="L459" t="inlineStr"/>
       <c r="M459" t="inlineStr">
         <is>
-          <t>C063</t>
+          <t>C073</t>
         </is>
       </c>
       <c r="N459" t="inlineStr">
@@ -25710,7 +25710,7 @@
       <c r="L460" t="inlineStr"/>
       <c r="M460" t="inlineStr">
         <is>
-          <t>C062</t>
+          <t>C072</t>
         </is>
       </c>
       <c r="N460" t="inlineStr">
@@ -25764,7 +25764,7 @@
       <c r="L461" t="inlineStr"/>
       <c r="M461" t="inlineStr">
         <is>
-          <t>C063</t>
+          <t>C073</t>
         </is>
       </c>
       <c r="N461" t="inlineStr">
@@ -25816,7 +25816,7 @@
       <c r="L462" t="inlineStr"/>
       <c r="M462" t="inlineStr">
         <is>
-          <t>C062</t>
+          <t>C072</t>
         </is>
       </c>
       <c r="N462" t="inlineStr">
@@ -25870,7 +25870,7 @@
       <c r="L463" t="inlineStr"/>
       <c r="M463" t="inlineStr">
         <is>
-          <t>C063</t>
+          <t>C073</t>
         </is>
       </c>
       <c r="N463" t="inlineStr">
@@ -25922,7 +25922,7 @@
       <c r="L464" t="inlineStr"/>
       <c r="M464" t="inlineStr">
         <is>
-          <t>C062</t>
+          <t>C072</t>
         </is>
       </c>
       <c r="N464" t="inlineStr">
@@ -25976,7 +25976,7 @@
       <c r="L465" t="inlineStr"/>
       <c r="M465" t="inlineStr">
         <is>
-          <t>C063</t>
+          <t>C073</t>
         </is>
       </c>
       <c r="N465" t="inlineStr">
@@ -26030,7 +26030,7 @@
       <c r="L466" t="inlineStr"/>
       <c r="M466" t="inlineStr">
         <is>
-          <t>C063</t>
+          <t>C073</t>
         </is>
       </c>
       <c r="N466" t="inlineStr">
@@ -26082,7 +26082,7 @@
       <c r="L467" t="inlineStr"/>
       <c r="M467" t="inlineStr">
         <is>
-          <t>C062</t>
+          <t>C072</t>
         </is>
       </c>
       <c r="N467" t="inlineStr">
@@ -26136,7 +26136,7 @@
       <c r="L468" t="inlineStr"/>
       <c r="M468" t="inlineStr">
         <is>
-          <t>C063</t>
+          <t>C073</t>
         </is>
       </c>
       <c r="N468" t="inlineStr">
@@ -26188,7 +26188,7 @@
       <c r="L469" t="inlineStr"/>
       <c r="M469" t="inlineStr">
         <is>
-          <t>C062</t>
+          <t>C072</t>
         </is>
       </c>
       <c r="N469" t="inlineStr">
@@ -26240,7 +26240,7 @@
       <c r="L470" t="inlineStr"/>
       <c r="M470" t="inlineStr">
         <is>
-          <t>C062</t>
+          <t>C072</t>
         </is>
       </c>
       <c r="N470" t="inlineStr">
@@ -26294,7 +26294,7 @@
       <c r="L471" t="inlineStr"/>
       <c r="M471" t="inlineStr">
         <is>
-          <t>C063</t>
+          <t>C073</t>
         </is>
       </c>
       <c r="N471" t="inlineStr">
@@ -26348,7 +26348,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>C086</t>
+          <t>C092</t>
         </is>
       </c>
       <c r="N472" t="inlineStr">
@@ -26404,7 +26404,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>C086</t>
+          <t>C092</t>
         </is>
       </c>
       <c r="N473" t="inlineStr">
@@ -26460,7 +26460,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>C086</t>
+          <t>C092</t>
         </is>
       </c>
       <c r="N474" t="inlineStr">
@@ -26516,7 +26516,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>C086</t>
+          <t>C092</t>
         </is>
       </c>
       <c r="N475" t="inlineStr">
@@ -26572,7 +26572,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>C086</t>
+          <t>C092</t>
         </is>
       </c>
       <c r="N476" t="inlineStr">
@@ -26628,7 +26628,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>C086</t>
+          <t>C092</t>
         </is>
       </c>
       <c r="N477" t="inlineStr">
@@ -26684,7 +26684,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>C086</t>
+          <t>C092</t>
         </is>
       </c>
       <c r="N478" t="inlineStr">
@@ -26740,7 +26740,7 @@
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t>C086</t>
+          <t>C092</t>
         </is>
       </c>
       <c r="N479" t="inlineStr">
@@ -26794,7 +26794,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>C087</t>
+          <t>C093</t>
         </is>
       </c>
       <c r="N480" t="inlineStr">
@@ -26850,7 +26850,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>C087</t>
+          <t>C093</t>
         </is>
       </c>
       <c r="N481" t="inlineStr">
@@ -26906,7 +26906,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>C087</t>
+          <t>C093</t>
         </is>
       </c>
       <c r="N482" t="inlineStr">
@@ -26962,7 +26962,7 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>C087</t>
+          <t>C093</t>
         </is>
       </c>
       <c r="N483" t="inlineStr">
@@ -27018,7 +27018,7 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>C087</t>
+          <t>C093</t>
         </is>
       </c>
       <c r="N484" t="inlineStr">
@@ -27074,7 +27074,7 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>C087</t>
+          <t>C093</t>
         </is>
       </c>
       <c r="N485" t="inlineStr">
@@ -27130,7 +27130,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>C087</t>
+          <t>C093</t>
         </is>
       </c>
       <c r="N486" t="inlineStr">
@@ -27186,7 +27186,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>C087</t>
+          <t>C093</t>
         </is>
       </c>
       <c r="N487" t="inlineStr">
@@ -27240,7 +27240,7 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>C088</t>
+          <t>C094</t>
         </is>
       </c>
       <c r="N488" t="inlineStr">
@@ -27296,7 +27296,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>C088</t>
+          <t>C094</t>
         </is>
       </c>
       <c r="N489" t="inlineStr">
@@ -27352,7 +27352,7 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>C088</t>
+          <t>C094</t>
         </is>
       </c>
       <c r="N490" t="inlineStr">
@@ -27408,7 +27408,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>C088</t>
+          <t>C094</t>
         </is>
       </c>
       <c r="N491" t="inlineStr">
@@ -27464,7 +27464,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>C088</t>
+          <t>C094</t>
         </is>
       </c>
       <c r="N492" t="inlineStr">
@@ -27520,7 +27520,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>C088</t>
+          <t>C094</t>
         </is>
       </c>
       <c r="N493" t="inlineStr">
@@ -27576,7 +27576,7 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>C088</t>
+          <t>C094</t>
         </is>
       </c>
       <c r="N494" t="inlineStr">
@@ -27632,7 +27632,7 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>C088</t>
+          <t>C094</t>
         </is>
       </c>
       <c r="N495" t="inlineStr">
@@ -27686,7 +27686,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>C089</t>
+          <t>C095</t>
         </is>
       </c>
       <c r="N496" t="inlineStr">
@@ -27742,7 +27742,7 @@
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t>C089</t>
+          <t>C095</t>
         </is>
       </c>
       <c r="N497" t="inlineStr">
@@ -27798,7 +27798,7 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>C089</t>
+          <t>C095</t>
         </is>
       </c>
       <c r="N498" t="inlineStr">
@@ -27854,7 +27854,7 @@
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t>C089</t>
+          <t>C095</t>
         </is>
       </c>
       <c r="N499" t="inlineStr">
@@ -27910,7 +27910,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>C089</t>
+          <t>C095</t>
         </is>
       </c>
       <c r="N500" t="inlineStr">
@@ -27966,7 +27966,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>C089</t>
+          <t>C095</t>
         </is>
       </c>
       <c r="N501" t="inlineStr">
@@ -28022,7 +28022,7 @@
       </c>
       <c r="M502" t="inlineStr">
         <is>
-          <t>C089</t>
+          <t>C095</t>
         </is>
       </c>
       <c r="N502" t="inlineStr">
@@ -28078,7 +28078,7 @@
       </c>
       <c r="M503" t="inlineStr">
         <is>
-          <t>C089</t>
+          <t>C095</t>
         </is>
       </c>
       <c r="N503" t="inlineStr">
@@ -28130,7 +28130,7 @@
       <c r="L504" t="inlineStr"/>
       <c r="M504" t="inlineStr">
         <is>
-          <t>C143</t>
+          <t>C149</t>
         </is>
       </c>
       <c r="N504" t="inlineStr">
@@ -28184,7 +28184,7 @@
       <c r="L505" t="inlineStr"/>
       <c r="M505" t="inlineStr">
         <is>
-          <t>C143</t>
+          <t>C149</t>
         </is>
       </c>
       <c r="N505" t="inlineStr">
@@ -28236,7 +28236,7 @@
       <c r="L506" t="inlineStr"/>
       <c r="M506" t="inlineStr">
         <is>
-          <t>C143</t>
+          <t>C149</t>
         </is>
       </c>
       <c r="N506" t="inlineStr">
@@ -28290,7 +28290,7 @@
       <c r="L507" t="inlineStr"/>
       <c r="M507" t="inlineStr">
         <is>
-          <t>C143</t>
+          <t>C149</t>
         </is>
       </c>
       <c r="N507" t="inlineStr">
@@ -28342,7 +28342,7 @@
       <c r="L508" t="inlineStr"/>
       <c r="M508" t="inlineStr">
         <is>
-          <t>C143</t>
+          <t>C149</t>
         </is>
       </c>
       <c r="N508" t="inlineStr">
@@ -28396,7 +28396,7 @@
       <c r="L509" t="inlineStr"/>
       <c r="M509" t="inlineStr">
         <is>
-          <t>C143</t>
+          <t>C149</t>
         </is>
       </c>
       <c r="N509" t="inlineStr">
@@ -28450,7 +28450,7 @@
       <c r="L510" t="inlineStr"/>
       <c r="M510" t="inlineStr">
         <is>
-          <t>C143</t>
+          <t>C149</t>
         </is>
       </c>
       <c r="N510" t="inlineStr">
@@ -28502,7 +28502,7 @@
       <c r="L511" t="inlineStr"/>
       <c r="M511" t="inlineStr">
         <is>
-          <t>C143</t>
+          <t>C149</t>
         </is>
       </c>
       <c r="N511" t="inlineStr">
@@ -28556,7 +28556,7 @@
       <c r="L512" t="inlineStr"/>
       <c r="M512" t="inlineStr">
         <is>
-          <t>C143</t>
+          <t>C149</t>
         </is>
       </c>
       <c r="N512" t="inlineStr">
@@ -28610,7 +28610,7 @@
       <c r="L513" t="inlineStr"/>
       <c r="M513" t="inlineStr">
         <is>
-          <t>C143</t>
+          <t>C149</t>
         </is>
       </c>
       <c r="N513" t="inlineStr">
@@ -28664,7 +28664,7 @@
       <c r="L514" t="inlineStr"/>
       <c r="M514" t="inlineStr">
         <is>
-          <t>C143</t>
+          <t>C149</t>
         </is>
       </c>
       <c r="N514" t="inlineStr">
@@ -28718,7 +28718,7 @@
       <c r="L515" t="inlineStr"/>
       <c r="M515" t="inlineStr">
         <is>
-          <t>C143</t>
+          <t>C149</t>
         </is>
       </c>
       <c r="N515" t="inlineStr">
@@ -28772,7 +28772,7 @@
       <c r="L516" t="inlineStr"/>
       <c r="M516" t="inlineStr">
         <is>
-          <t>C143</t>
+          <t>C149</t>
         </is>
       </c>
       <c r="N516" t="inlineStr">
@@ -28826,7 +28826,7 @@
       <c r="L517" t="inlineStr"/>
       <c r="M517" t="inlineStr">
         <is>
-          <t>C143</t>
+          <t>C149</t>
         </is>
       </c>
       <c r="N517" t="inlineStr">
@@ -28880,7 +28880,7 @@
       <c r="L518" t="inlineStr"/>
       <c r="M518" t="inlineStr">
         <is>
-          <t>C143</t>
+          <t>C149</t>
         </is>
       </c>
       <c r="N518" t="inlineStr">
@@ -28934,7 +28934,7 @@
       <c r="L519" t="inlineStr"/>
       <c r="M519" t="inlineStr">
         <is>
-          <t>C143</t>
+          <t>C149</t>
         </is>
       </c>
       <c r="N519" t="inlineStr">
@@ -28988,7 +28988,7 @@
       <c r="L520" t="inlineStr"/>
       <c r="M520" t="inlineStr">
         <is>
-          <t>C143</t>
+          <t>C149</t>
         </is>
       </c>
       <c r="N520" t="inlineStr">
@@ -29042,7 +29042,7 @@
       <c r="L521" t="inlineStr"/>
       <c r="M521" t="inlineStr">
         <is>
-          <t>C143</t>
+          <t>C149</t>
         </is>
       </c>
       <c r="N521" t="inlineStr">
@@ -29096,7 +29096,7 @@
       <c r="L522" t="inlineStr"/>
       <c r="M522" t="inlineStr">
         <is>
-          <t>C143</t>
+          <t>C149</t>
         </is>
       </c>
       <c r="N522" t="inlineStr">
@@ -29150,7 +29150,7 @@
       <c r="L523" t="inlineStr"/>
       <c r="M523" t="inlineStr">
         <is>
-          <t>C143</t>
+          <t>C149</t>
         </is>
       </c>
       <c r="N523" t="inlineStr">
@@ -29204,7 +29204,7 @@
       <c r="L524" t="inlineStr"/>
       <c r="M524" t="inlineStr">
         <is>
-          <t>C143</t>
+          <t>C149</t>
         </is>
       </c>
       <c r="N524" t="inlineStr">
@@ -29258,7 +29258,7 @@
       <c r="L525" t="inlineStr"/>
       <c r="M525" t="inlineStr">
         <is>
-          <t>C143</t>
+          <t>C149</t>
         </is>
       </c>
       <c r="N525" t="inlineStr">
@@ -29312,7 +29312,7 @@
       <c r="L526" t="inlineStr"/>
       <c r="M526" t="inlineStr">
         <is>
-          <t>C143</t>
+          <t>C149</t>
         </is>
       </c>
       <c r="N526" t="inlineStr">
@@ -29366,7 +29366,7 @@
       <c r="L527" t="inlineStr"/>
       <c r="M527" t="inlineStr">
         <is>
-          <t>C143</t>
+          <t>C149</t>
         </is>
       </c>
       <c r="N527" t="inlineStr">
@@ -29420,7 +29420,7 @@
       <c r="L528" t="inlineStr"/>
       <c r="M528" t="inlineStr">
         <is>
-          <t>C143</t>
+          <t>C149</t>
         </is>
       </c>
       <c r="N528" t="inlineStr">
@@ -29474,7 +29474,7 @@
       <c r="L529" t="inlineStr"/>
       <c r="M529" t="inlineStr">
         <is>
-          <t>C143</t>
+          <t>C149</t>
         </is>
       </c>
       <c r="N529" t="inlineStr">
@@ -29528,7 +29528,7 @@
       <c r="L530" t="inlineStr"/>
       <c r="M530" t="inlineStr">
         <is>
-          <t>C143</t>
+          <t>C149</t>
         </is>
       </c>
       <c r="N530" t="inlineStr">
@@ -29582,7 +29582,7 @@
       <c r="L531" t="inlineStr"/>
       <c r="M531" t="inlineStr">
         <is>
-          <t>C143</t>
+          <t>C149</t>
         </is>
       </c>
       <c r="N531" t="inlineStr">
@@ -29633,7 +29633,9 @@
       </c>
       <c r="J532" t="inlineStr"/>
       <c r="K532" t="inlineStr"/>
-      <c r="L532" t="inlineStr"/>
+      <c r="L532" t="n">
+        <v>0.1</v>
+      </c>
       <c r="M532" t="inlineStr">
         <is>
           <t>C050</t>
@@ -29687,7 +29689,9 @@
       </c>
       <c r="J533" t="inlineStr"/>
       <c r="K533" t="inlineStr"/>
-      <c r="L533" t="inlineStr"/>
+      <c r="L533" t="n">
+        <v>0.1</v>
+      </c>
       <c r="M533" t="inlineStr">
         <is>
           <t>C048</t>
@@ -29741,7 +29745,9 @@
       </c>
       <c r="J534" t="inlineStr"/>
       <c r="K534" t="inlineStr"/>
-      <c r="L534" t="inlineStr"/>
+      <c r="L534" t="n">
+        <v>0.1</v>
+      </c>
       <c r="M534" t="inlineStr">
         <is>
           <t>C046</t>
@@ -29795,7 +29801,9 @@
       </c>
       <c r="J535" t="inlineStr"/>
       <c r="K535" t="inlineStr"/>
-      <c r="L535" t="inlineStr"/>
+      <c r="L535" t="n">
+        <v>0.1</v>
+      </c>
       <c r="M535" t="inlineStr">
         <is>
           <t>C046</t>
@@ -29849,7 +29857,9 @@
       </c>
       <c r="J536" t="inlineStr"/>
       <c r="K536" t="inlineStr"/>
-      <c r="L536" t="inlineStr"/>
+      <c r="L536" t="n">
+        <v>0.1</v>
+      </c>
       <c r="M536" t="inlineStr">
         <is>
           <t>C047</t>
@@ -29903,7 +29913,9 @@
       </c>
       <c r="J537" t="inlineStr"/>
       <c r="K537" t="inlineStr"/>
-      <c r="L537" t="inlineStr"/>
+      <c r="L537" t="n">
+        <v>0.1</v>
+      </c>
       <c r="M537" t="inlineStr">
         <is>
           <t>C049</t>
@@ -29957,7 +29969,9 @@
       </c>
       <c r="J538" t="inlineStr"/>
       <c r="K538" t="inlineStr"/>
-      <c r="L538" t="inlineStr"/>
+      <c r="L538" t="n">
+        <v>0.1</v>
+      </c>
       <c r="M538" t="inlineStr">
         <is>
           <t>C048</t>
@@ -30011,7 +30025,9 @@
       </c>
       <c r="J539" t="inlineStr"/>
       <c r="K539" t="inlineStr"/>
-      <c r="L539" t="inlineStr"/>
+      <c r="L539" t="n">
+        <v>0.1</v>
+      </c>
       <c r="M539" t="inlineStr">
         <is>
           <t>C048</t>
@@ -30065,7 +30081,9 @@
       </c>
       <c r="J540" t="inlineStr"/>
       <c r="K540" t="inlineStr"/>
-      <c r="L540" t="inlineStr"/>
+      <c r="L540" t="n">
+        <v>0.1</v>
+      </c>
       <c r="M540" t="inlineStr">
         <is>
           <t>C047</t>
@@ -30119,7 +30137,9 @@
       </c>
       <c r="J541" t="inlineStr"/>
       <c r="K541" t="inlineStr"/>
-      <c r="L541" t="inlineStr"/>
+      <c r="L541" t="n">
+        <v>0.1</v>
+      </c>
       <c r="M541" t="inlineStr">
         <is>
           <t>C049</t>
@@ -30173,7 +30193,9 @@
       </c>
       <c r="J542" t="inlineStr"/>
       <c r="K542" t="inlineStr"/>
-      <c r="L542" t="inlineStr"/>
+      <c r="L542" t="n">
+        <v>0.1</v>
+      </c>
       <c r="M542" t="inlineStr">
         <is>
           <t>C049</t>
@@ -30227,7 +30249,9 @@
       </c>
       <c r="J543" t="inlineStr"/>
       <c r="K543" t="inlineStr"/>
-      <c r="L543" t="inlineStr"/>
+      <c r="L543" t="n">
+        <v>0.1</v>
+      </c>
       <c r="M543" t="inlineStr">
         <is>
           <t>C048</t>
@@ -30281,7 +30305,9 @@
       </c>
       <c r="J544" t="inlineStr"/>
       <c r="K544" t="inlineStr"/>
-      <c r="L544" t="inlineStr"/>
+      <c r="L544" t="n">
+        <v>0.1</v>
+      </c>
       <c r="M544" t="inlineStr">
         <is>
           <t>C050</t>
@@ -30335,7 +30361,9 @@
       </c>
       <c r="J545" t="inlineStr"/>
       <c r="K545" t="inlineStr"/>
-      <c r="L545" t="inlineStr"/>
+      <c r="L545" t="n">
+        <v>0.1</v>
+      </c>
       <c r="M545" t="inlineStr">
         <is>
           <t>C050</t>
@@ -30389,7 +30417,9 @@
       </c>
       <c r="J546" t="inlineStr"/>
       <c r="K546" t="inlineStr"/>
-      <c r="L546" t="inlineStr"/>
+      <c r="L546" t="n">
+        <v>0.1</v>
+      </c>
       <c r="M546" t="inlineStr">
         <is>
           <t>C053</t>
@@ -30443,7 +30473,9 @@
       </c>
       <c r="J547" t="inlineStr"/>
       <c r="K547" t="inlineStr"/>
-      <c r="L547" t="inlineStr"/>
+      <c r="L547" t="n">
+        <v>0.1</v>
+      </c>
       <c r="M547" t="inlineStr">
         <is>
           <t>C051</t>
@@ -30497,7 +30529,9 @@
       </c>
       <c r="J548" t="inlineStr"/>
       <c r="K548" t="inlineStr"/>
-      <c r="L548" t="inlineStr"/>
+      <c r="L548" t="n">
+        <v>0.1</v>
+      </c>
       <c r="M548" t="inlineStr">
         <is>
           <t>C051</t>
@@ -30551,7 +30585,9 @@
       </c>
       <c r="J549" t="inlineStr"/>
       <c r="K549" t="inlineStr"/>
-      <c r="L549" t="inlineStr"/>
+      <c r="L549" t="n">
+        <v>0.1</v>
+      </c>
       <c r="M549" t="inlineStr">
         <is>
           <t>C052</t>
@@ -30605,7 +30641,9 @@
       </c>
       <c r="J550" t="inlineStr"/>
       <c r="K550" t="inlineStr"/>
-      <c r="L550" t="inlineStr"/>
+      <c r="L550" t="n">
+        <v>0.1</v>
+      </c>
       <c r="M550" t="inlineStr">
         <is>
           <t>C054</t>
@@ -30659,7 +30697,9 @@
       </c>
       <c r="J551" t="inlineStr"/>
       <c r="K551" t="inlineStr"/>
-      <c r="L551" t="inlineStr"/>
+      <c r="L551" t="n">
+        <v>0.1</v>
+      </c>
       <c r="M551" t="inlineStr">
         <is>
           <t>C053</t>
@@ -30713,7 +30753,9 @@
       </c>
       <c r="J552" t="inlineStr"/>
       <c r="K552" t="inlineStr"/>
-      <c r="L552" t="inlineStr"/>
+      <c r="L552" t="n">
+        <v>0.1</v>
+      </c>
       <c r="M552" t="inlineStr">
         <is>
           <t>C052</t>
@@ -30767,7 +30809,9 @@
       </c>
       <c r="J553" t="inlineStr"/>
       <c r="K553" t="inlineStr"/>
-      <c r="L553" t="inlineStr"/>
+      <c r="L553" t="n">
+        <v>0.1</v>
+      </c>
       <c r="M553" t="inlineStr">
         <is>
           <t>C054</t>
@@ -30821,7 +30865,9 @@
       </c>
       <c r="J554" t="inlineStr"/>
       <c r="K554" t="inlineStr"/>
-      <c r="L554" t="inlineStr"/>
+      <c r="L554" t="n">
+        <v>0.1</v>
+      </c>
       <c r="M554" t="inlineStr">
         <is>
           <t>C053</t>
@@ -30875,7 +30921,9 @@
       </c>
       <c r="J555" t="inlineStr"/>
       <c r="K555" t="inlineStr"/>
-      <c r="L555" t="inlineStr"/>
+      <c r="L555" t="n">
+        <v>0.1</v>
+      </c>
       <c r="M555" t="inlineStr">
         <is>
           <t>C055</t>
@@ -30932,7 +30980,7 @@
       <c r="L556" t="inlineStr"/>
       <c r="M556" t="inlineStr">
         <is>
-          <t>C097</t>
+          <t>C103</t>
         </is>
       </c>
       <c r="N556" t="inlineStr">
@@ -30986,7 +31034,7 @@
       <c r="L557" t="inlineStr"/>
       <c r="M557" t="inlineStr">
         <is>
-          <t>C097</t>
+          <t>C103</t>
         </is>
       </c>
       <c r="N557" t="inlineStr">
@@ -31040,7 +31088,7 @@
       <c r="L558" t="inlineStr"/>
       <c r="M558" t="inlineStr">
         <is>
-          <t>C097</t>
+          <t>C103</t>
         </is>
       </c>
       <c r="N558" t="inlineStr">
@@ -31094,7 +31142,7 @@
       <c r="L559" t="inlineStr"/>
       <c r="M559" t="inlineStr">
         <is>
-          <t>C097</t>
+          <t>C103</t>
         </is>
       </c>
       <c r="N559" t="inlineStr">
@@ -31148,7 +31196,7 @@
       <c r="L560" t="inlineStr"/>
       <c r="M560" t="inlineStr">
         <is>
-          <t>C098</t>
+          <t>C104</t>
         </is>
       </c>
       <c r="N560" t="inlineStr">
@@ -31202,7 +31250,7 @@
       <c r="L561" t="inlineStr"/>
       <c r="M561" t="inlineStr">
         <is>
-          <t>C098</t>
+          <t>C104</t>
         </is>
       </c>
       <c r="N561" t="inlineStr">
@@ -31256,7 +31304,7 @@
       <c r="L562" t="inlineStr"/>
       <c r="M562" t="inlineStr">
         <is>
-          <t>C098</t>
+          <t>C104</t>
         </is>
       </c>
       <c r="N562" t="inlineStr">
@@ -31310,7 +31358,7 @@
       <c r="L563" t="inlineStr"/>
       <c r="M563" t="inlineStr">
         <is>
-          <t>C098</t>
+          <t>C104</t>
         </is>
       </c>
       <c r="N563" t="inlineStr">
@@ -31364,7 +31412,7 @@
       <c r="L564" t="inlineStr"/>
       <c r="M564" t="inlineStr">
         <is>
-          <t>C098</t>
+          <t>C104</t>
         </is>
       </c>
       <c r="N564" t="inlineStr">
@@ -31418,7 +31466,7 @@
       <c r="L565" t="inlineStr"/>
       <c r="M565" t="inlineStr">
         <is>
-          <t>C098</t>
+          <t>C104</t>
         </is>
       </c>
       <c r="N565" t="inlineStr">
@@ -31472,7 +31520,7 @@
       <c r="L566" t="inlineStr"/>
       <c r="M566" t="inlineStr">
         <is>
-          <t>C098</t>
+          <t>C104</t>
         </is>
       </c>
       <c r="N566" t="inlineStr">
@@ -31526,7 +31574,7 @@
       <c r="L567" t="inlineStr"/>
       <c r="M567" t="inlineStr">
         <is>
-          <t>C098</t>
+          <t>C104</t>
         </is>
       </c>
       <c r="N567" t="inlineStr">
@@ -31580,7 +31628,7 @@
       <c r="L568" t="inlineStr"/>
       <c r="M568" t="inlineStr">
         <is>
-          <t>C098</t>
+          <t>C104</t>
         </is>
       </c>
       <c r="N568" t="inlineStr">
@@ -33164,10 +33212,12 @@
           <t>3e0 g/L</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
+      <c r="J13" t="n">
+        <v>0.1</v>
+      </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>neither both concentrations nor a stated ratio</t>
+          <t>upper bound stated by the paper</t>
         </is>
       </c>
       <c r="L13" t="n">
@@ -33234,10 +33284,12 @@
           <t>1e0 g/L</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
+      <c r="J14" t="n">
+        <v>0.1</v>
+      </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>neither both concentrations nor a stated ratio</t>
+          <t>upper bound stated by the paper</t>
         </is>
       </c>
       <c r="L14" t="n">
@@ -33304,10 +33356,12 @@
           <t>1e-1 g/L</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
+      <c r="J15" t="n">
+        <v>0.1</v>
+      </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>neither both concentrations nor a stated ratio</t>
+          <t>upper bound stated by the paper</t>
         </is>
       </c>
       <c r="L15" t="n">
@@ -33374,10 +33428,12 @@
           <t>5e-2 g/L</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
+      <c r="J16" t="n">
+        <v>0.1</v>
+      </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>neither both concentrations nor a stated ratio</t>
+          <t>upper bound stated by the paper</t>
         </is>
       </c>
       <c r="L16" t="n">
@@ -33444,10 +33500,12 @@
           <t>2.5e-2 g/L</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
+      <c r="J17" t="n">
+        <v>0.1</v>
+      </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>neither both concentrations nor a stated ratio</t>
+          <t>upper bound stated by the paper</t>
         </is>
       </c>
       <c r="L17" t="n">
@@ -33514,10 +33572,12 @@
           <t>3e0 g/L</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
+      <c r="J18" t="n">
+        <v>0.1</v>
+      </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>neither both concentrations nor a stated ratio</t>
+          <t>upper bound stated by the paper</t>
         </is>
       </c>
       <c r="L18" t="n">
@@ -33584,10 +33644,12 @@
           <t>1e0 g/L</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
+      <c r="J19" t="n">
+        <v>0.1</v>
+      </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>neither both concentrations nor a stated ratio</t>
+          <t>upper bound stated by the paper</t>
         </is>
       </c>
       <c r="L19" t="n">
@@ -33654,10 +33716,12 @@
           <t>1e-1 g/L</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr"/>
+      <c r="J20" t="n">
+        <v>0.1</v>
+      </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>neither both concentrations nor a stated ratio</t>
+          <t>upper bound stated by the paper</t>
         </is>
       </c>
       <c r="L20" t="n">
@@ -33724,10 +33788,12 @@
           <t>5e-2 g/L</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr"/>
+      <c r="J21" t="n">
+        <v>0.1</v>
+      </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>neither both concentrations nor a stated ratio</t>
+          <t>upper bound stated by the paper</t>
         </is>
       </c>
       <c r="L21" t="n">
@@ -33794,10 +33860,12 @@
           <t>2.5e-2 g/L</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr"/>
+      <c r="J22" t="n">
+        <v>0.1</v>
+      </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>neither both concentrations nor a stated ratio</t>
+          <t>upper bound stated by the paper</t>
         </is>
       </c>
       <c r="L22" t="n">
@@ -33827,7 +33895,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>C056</t>
+          <t>C066</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -33897,7 +33965,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>C057</t>
+          <t>C067</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -33967,7 +34035,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>C058</t>
+          <t>C068</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -34037,7 +34105,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>C059</t>
+          <t>C069</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -34105,7 +34173,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>C060</t>
+          <t>C070</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -34173,7 +34241,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>C061</t>
+          <t>C071</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -34241,7 +34309,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>C062</t>
+          <t>C072</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -34309,7 +34377,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>C063</t>
+          <t>C073</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -34377,7 +34445,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>C064</t>
+          <t>C074</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -34445,7 +34513,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>C065</t>
+          <t>C075</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -34517,7 +34585,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>C066</t>
+          <t>C076</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -34589,7 +34657,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>C067</t>
+          <t>C077</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -34661,7 +34729,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>C068</t>
+          <t>C078</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -34733,7 +34801,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>C069</t>
+          <t>C079</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -34805,7 +34873,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>C070</t>
+          <t>C080</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -34877,7 +34945,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>C071</t>
+          <t>C081</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -34949,7 +35017,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>C078</t>
+          <t>C088</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -35021,7 +35089,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>C079</t>
+          <t>C089</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -35093,7 +35161,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>C080</t>
+          <t>C090</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -35165,7 +35233,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>C081</t>
+          <t>C091</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -35235,7 +35303,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>C086</t>
+          <t>C092</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -35309,7 +35377,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>C087</t>
+          <t>C093</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -35383,7 +35451,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>C088</t>
+          <t>C094</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -35457,7 +35525,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>C089</t>
+          <t>C095</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -35531,7 +35599,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>C097</t>
+          <t>C103</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -35599,7 +35667,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>C098</t>
+          <t>C104</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -35667,7 +35735,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>C099</t>
+          <t>C105</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -35739,7 +35807,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>C100</t>
+          <t>C106</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -35805,7 +35873,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>C113</t>
+          <t>C119</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -35873,7 +35941,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>C114</t>
+          <t>C120</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -35941,7 +36009,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>C143</t>
+          <t>C149</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">

--- a/tk_review/db/binding_major_sources.xlsx
+++ b/tk_review/db/binding_major_sources.xlsx
@@ -72302,7 +72302,7 @@
       <c r="T277" t="inlineStr"/>
       <c r="U277" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>unknown (ITC)</t>
         </is>
       </c>
       <c r="V277" t="inlineStr">
@@ -72402,7 +72402,7 @@
       <c r="T278" t="inlineStr"/>
       <c r="U278" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>unknown (ITC)</t>
         </is>
       </c>
       <c r="V278" t="inlineStr">
@@ -72508,7 +72508,7 @@
       <c r="T279" t="inlineStr"/>
       <c r="U279" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>unknown (ITC)</t>
         </is>
       </c>
       <c r="V279" t="inlineStr">
@@ -72614,7 +72614,7 @@
       <c r="T280" t="inlineStr"/>
       <c r="U280" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>unknown (ITC)</t>
         </is>
       </c>
       <c r="V280" t="inlineStr">

--- a/tk_review/db/binding_major_sources.xlsx
+++ b/tk_review/db/binding_major_sources.xlsx
@@ -15,7 +15,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Binding'!$A$1:$R$579</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Conditions'!$A$1:$R$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Conditions'!$A$1:$R$54</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Albumin Kd to K'!$A$1:$AB$303</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -8068,7 +8068,7 @@
       </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t>C105</t>
+          <t>C109</t>
         </is>
       </c>
       <c r="R113" t="inlineStr">
@@ -8148,7 +8148,7 @@
       </c>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>C105</t>
+          <t>C109</t>
         </is>
       </c>
       <c r="R114" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>C105</t>
+          <t>C109</t>
         </is>
       </c>
       <c r="R115" t="inlineStr">
@@ -8308,7 +8308,7 @@
       </c>
       <c r="Q116" t="inlineStr">
         <is>
-          <t>C105</t>
+          <t>C109</t>
         </is>
       </c>
       <c r="R116" t="inlineStr">
@@ -8388,7 +8388,7 @@
       </c>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>C105</t>
+          <t>C109</t>
         </is>
       </c>
       <c r="R117" t="inlineStr">
@@ -8468,7 +8468,7 @@
       </c>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>C105</t>
+          <t>C109</t>
         </is>
       </c>
       <c r="R118" t="inlineStr">
@@ -8548,7 +8548,7 @@
       </c>
       <c r="Q119" t="inlineStr">
         <is>
-          <t>C105</t>
+          <t>C109</t>
         </is>
       </c>
       <c r="R119" t="inlineStr">
@@ -8628,7 +8628,7 @@
       </c>
       <c r="Q120" t="inlineStr">
         <is>
-          <t>C105</t>
+          <t>C109</t>
         </is>
       </c>
       <c r="R120" t="inlineStr">
@@ -8708,7 +8708,7 @@
       </c>
       <c r="Q121" t="inlineStr">
         <is>
-          <t>C105</t>
+          <t>C109</t>
         </is>
       </c>
       <c r="R121" t="inlineStr">
@@ -8788,7 +8788,7 @@
       </c>
       <c r="Q122" t="inlineStr">
         <is>
-          <t>C105</t>
+          <t>C109</t>
         </is>
       </c>
       <c r="R122" t="inlineStr">
@@ -8868,7 +8868,7 @@
       </c>
       <c r="Q123" t="inlineStr">
         <is>
-          <t>C105</t>
+          <t>C109</t>
         </is>
       </c>
       <c r="R123" t="inlineStr">
@@ -8948,7 +8948,7 @@
       </c>
       <c r="Q124" t="inlineStr">
         <is>
-          <t>C105</t>
+          <t>C109</t>
         </is>
       </c>
       <c r="R124" t="inlineStr">
@@ -9028,7 +9028,7 @@
       </c>
       <c r="Q125" t="inlineStr">
         <is>
-          <t>C105</t>
+          <t>C109</t>
         </is>
       </c>
       <c r="R125" t="inlineStr">
@@ -9108,7 +9108,7 @@
       </c>
       <c r="Q126" t="inlineStr">
         <is>
-          <t>C105</t>
+          <t>C109</t>
         </is>
       </c>
       <c r="R126" t="inlineStr">
@@ -9188,7 +9188,7 @@
       </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>C105</t>
+          <t>C109</t>
         </is>
       </c>
       <c r="R127" t="inlineStr">
@@ -9268,7 +9268,7 @@
       </c>
       <c r="Q128" t="inlineStr">
         <is>
-          <t>C105</t>
+          <t>C109</t>
         </is>
       </c>
       <c r="R128" t="inlineStr">
@@ -9348,7 +9348,7 @@
       </c>
       <c r="Q129" t="inlineStr">
         <is>
-          <t>C105</t>
+          <t>C109</t>
         </is>
       </c>
       <c r="R129" t="inlineStr">
@@ -9428,7 +9428,7 @@
       </c>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>C105</t>
+          <t>C109</t>
         </is>
       </c>
       <c r="R130" t="inlineStr">
@@ -9508,7 +9508,7 @@
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>C105</t>
+          <t>C109</t>
         </is>
       </c>
       <c r="R131" t="inlineStr">
@@ -9588,7 +9588,7 @@
       </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>C105</t>
+          <t>C109</t>
         </is>
       </c>
       <c r="R132" t="inlineStr">
@@ -9668,7 +9668,7 @@
       </c>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>C105</t>
+          <t>C109</t>
         </is>
       </c>
       <c r="R133" t="inlineStr">
@@ -9748,7 +9748,7 @@
       </c>
       <c r="Q134" t="inlineStr">
         <is>
-          <t>C105</t>
+          <t>C109</t>
         </is>
       </c>
       <c r="R134" t="inlineStr">
@@ -9828,7 +9828,7 @@
       </c>
       <c r="Q135" t="inlineStr">
         <is>
-          <t>C105</t>
+          <t>C109</t>
         </is>
       </c>
       <c r="R135" t="inlineStr">
@@ -9908,7 +9908,7 @@
       </c>
       <c r="Q136" t="inlineStr">
         <is>
-          <t>C105</t>
+          <t>C109</t>
         </is>
       </c>
       <c r="R136" t="inlineStr">
@@ -9988,7 +9988,7 @@
       </c>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>C105</t>
+          <t>C109</t>
         </is>
       </c>
       <c r="R137" t="inlineStr">
@@ -10068,7 +10068,7 @@
       </c>
       <c r="Q138" t="inlineStr">
         <is>
-          <t>C105</t>
+          <t>C109</t>
         </is>
       </c>
       <c r="R138" t="inlineStr">
@@ -10148,7 +10148,7 @@
       </c>
       <c r="Q139" t="inlineStr">
         <is>
-          <t>C105</t>
+          <t>C109</t>
         </is>
       </c>
       <c r="R139" t="inlineStr">
@@ -10228,7 +10228,7 @@
       </c>
       <c r="Q140" t="inlineStr">
         <is>
-          <t>C105</t>
+          <t>C109</t>
         </is>
       </c>
       <c r="R140" t="inlineStr">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="Q141" t="inlineStr">
         <is>
-          <t>C105</t>
+          <t>C109</t>
         </is>
       </c>
       <c r="R141" t="inlineStr">
@@ -10388,7 +10388,7 @@
       </c>
       <c r="Q142" t="inlineStr">
         <is>
-          <t>C105</t>
+          <t>C109</t>
         </is>
       </c>
       <c r="R142" t="inlineStr">
@@ -10468,7 +10468,7 @@
       </c>
       <c r="Q143" t="inlineStr">
         <is>
-          <t>C105</t>
+          <t>C109</t>
         </is>
       </c>
       <c r="R143" t="inlineStr">
@@ -10548,7 +10548,7 @@
       </c>
       <c r="Q144" t="inlineStr">
         <is>
-          <t>C105</t>
+          <t>C109</t>
         </is>
       </c>
       <c r="R144" t="inlineStr">
@@ -10628,7 +10628,7 @@
       </c>
       <c r="Q145" t="inlineStr">
         <is>
-          <t>C105</t>
+          <t>C109</t>
         </is>
       </c>
       <c r="R145" t="inlineStr">
@@ -10708,7 +10708,7 @@
       </c>
       <c r="Q146" t="inlineStr">
         <is>
-          <t>C105</t>
+          <t>C109</t>
         </is>
       </c>
       <c r="R146" t="inlineStr">
@@ -10788,7 +10788,7 @@
       </c>
       <c r="Q147" t="inlineStr">
         <is>
-          <t>C105</t>
+          <t>C109</t>
         </is>
       </c>
       <c r="R147" t="inlineStr">
@@ -10868,7 +10868,7 @@
       </c>
       <c r="Q148" t="inlineStr">
         <is>
-          <t>C105</t>
+          <t>C109</t>
         </is>
       </c>
       <c r="R148" t="inlineStr">
@@ -10948,7 +10948,7 @@
       </c>
       <c r="Q149" t="inlineStr">
         <is>
-          <t>C105</t>
+          <t>C109</t>
         </is>
       </c>
       <c r="R149" t="inlineStr">
@@ -11028,7 +11028,7 @@
       </c>
       <c r="Q150" t="inlineStr">
         <is>
-          <t>C105</t>
+          <t>C109</t>
         </is>
       </c>
       <c r="R150" t="inlineStr">
@@ -11108,7 +11108,7 @@
       </c>
       <c r="Q151" t="inlineStr">
         <is>
-          <t>C105</t>
+          <t>C109</t>
         </is>
       </c>
       <c r="R151" t="inlineStr">
@@ -11188,7 +11188,7 @@
       </c>
       <c r="Q152" t="inlineStr">
         <is>
-          <t>C105</t>
+          <t>C109</t>
         </is>
       </c>
       <c r="R152" t="inlineStr">
@@ -11268,7 +11268,7 @@
       </c>
       <c r="Q153" t="inlineStr">
         <is>
-          <t>C105</t>
+          <t>C109</t>
         </is>
       </c>
       <c r="R153" t="inlineStr">
@@ -11348,7 +11348,7 @@
       </c>
       <c r="Q154" t="inlineStr">
         <is>
-          <t>C105</t>
+          <t>C109</t>
         </is>
       </c>
       <c r="R154" t="inlineStr">
@@ -11428,7 +11428,7 @@
       </c>
       <c r="Q155" t="inlineStr">
         <is>
-          <t>C105</t>
+          <t>C109</t>
         </is>
       </c>
       <c r="R155" t="inlineStr">
@@ -11508,7 +11508,7 @@
       </c>
       <c r="Q156" t="inlineStr">
         <is>
-          <t>C105</t>
+          <t>C109</t>
         </is>
       </c>
       <c r="R156" t="inlineStr">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="Q157" t="inlineStr">
         <is>
-          <t>C105</t>
+          <t>C109</t>
         </is>
       </c>
       <c r="R157" t="inlineStr">
@@ -11668,7 +11668,7 @@
       </c>
       <c r="Q158" t="inlineStr">
         <is>
-          <t>C105</t>
+          <t>C109</t>
         </is>
       </c>
       <c r="R158" t="inlineStr">
@@ -11748,7 +11748,7 @@
       </c>
       <c r="Q159" t="inlineStr">
         <is>
-          <t>C105</t>
+          <t>C109</t>
         </is>
       </c>
       <c r="R159" t="inlineStr">
@@ -11828,7 +11828,7 @@
       </c>
       <c r="Q160" t="inlineStr">
         <is>
-          <t>C105</t>
+          <t>C109</t>
         </is>
       </c>
       <c r="R160" t="inlineStr">
@@ -11908,7 +11908,7 @@
       </c>
       <c r="Q161" t="inlineStr">
         <is>
-          <t>C105</t>
+          <t>C109</t>
         </is>
       </c>
       <c r="R161" t="inlineStr">
@@ -11988,7 +11988,7 @@
       </c>
       <c r="Q162" t="inlineStr">
         <is>
-          <t>C105</t>
+          <t>C109</t>
         </is>
       </c>
       <c r="R162" t="inlineStr">
@@ -12068,7 +12068,7 @@
       </c>
       <c r="Q163" t="inlineStr">
         <is>
-          <t>C105</t>
+          <t>C109</t>
         </is>
       </c>
       <c r="R163" t="inlineStr">
@@ -12148,7 +12148,7 @@
       </c>
       <c r="Q164" t="inlineStr">
         <is>
-          <t>C105</t>
+          <t>C109</t>
         </is>
       </c>
       <c r="R164" t="inlineStr">
@@ -12228,7 +12228,7 @@
       </c>
       <c r="Q165" t="inlineStr">
         <is>
-          <t>C105</t>
+          <t>C109</t>
         </is>
       </c>
       <c r="R165" t="inlineStr">
@@ -12308,7 +12308,7 @@
       </c>
       <c r="Q166" t="inlineStr">
         <is>
-          <t>C105</t>
+          <t>C109</t>
         </is>
       </c>
       <c r="R166" t="inlineStr">
@@ -12388,7 +12388,7 @@
       </c>
       <c r="Q167" t="inlineStr">
         <is>
-          <t>C105</t>
+          <t>C109</t>
         </is>
       </c>
       <c r="R167" t="inlineStr">
@@ -12468,7 +12468,7 @@
       </c>
       <c r="Q168" t="inlineStr">
         <is>
-          <t>C105</t>
+          <t>C109</t>
         </is>
       </c>
       <c r="R168" t="inlineStr">
@@ -12548,7 +12548,7 @@
       </c>
       <c r="Q169" t="inlineStr">
         <is>
-          <t>C105</t>
+          <t>C109</t>
         </is>
       </c>
       <c r="R169" t="inlineStr">
@@ -12612,7 +12612,7 @@
       </c>
       <c r="Q170" t="inlineStr">
         <is>
-          <t>C106</t>
+          <t>C110</t>
         </is>
       </c>
       <c r="R170" t="inlineStr">
@@ -12676,7 +12676,7 @@
       </c>
       <c r="Q171" t="inlineStr">
         <is>
-          <t>C106</t>
+          <t>C110</t>
         </is>
       </c>
       <c r="R171" t="inlineStr">
@@ -12740,7 +12740,7 @@
       </c>
       <c r="Q172" t="inlineStr">
         <is>
-          <t>C106</t>
+          <t>C110</t>
         </is>
       </c>
       <c r="R172" t="inlineStr">
@@ -12804,7 +12804,7 @@
       </c>
       <c r="Q173" t="inlineStr">
         <is>
-          <t>C106</t>
+          <t>C110</t>
         </is>
       </c>
       <c r="R173" t="inlineStr">
@@ -12868,7 +12868,7 @@
       </c>
       <c r="Q174" t="inlineStr">
         <is>
-          <t>C106</t>
+          <t>C110</t>
         </is>
       </c>
       <c r="R174" t="inlineStr">
@@ -12932,7 +12932,7 @@
       </c>
       <c r="Q175" t="inlineStr">
         <is>
-          <t>C106</t>
+          <t>C110</t>
         </is>
       </c>
       <c r="R175" t="inlineStr">
@@ -12996,7 +12996,7 @@
       </c>
       <c r="Q176" t="inlineStr">
         <is>
-          <t>C106</t>
+          <t>C110</t>
         </is>
       </c>
       <c r="R176" t="inlineStr">
@@ -13060,7 +13060,7 @@
       </c>
       <c r="Q177" t="inlineStr">
         <is>
-          <t>C106</t>
+          <t>C110</t>
         </is>
       </c>
       <c r="R177" t="inlineStr">
@@ -13124,7 +13124,7 @@
       </c>
       <c r="Q178" t="inlineStr">
         <is>
-          <t>C106</t>
+          <t>C110</t>
         </is>
       </c>
       <c r="R178" t="inlineStr">
@@ -13188,7 +13188,7 @@
       </c>
       <c r="Q179" t="inlineStr">
         <is>
-          <t>C106</t>
+          <t>C110</t>
         </is>
       </c>
       <c r="R179" t="inlineStr">
@@ -13252,7 +13252,7 @@
       </c>
       <c r="Q180" t="inlineStr">
         <is>
-          <t>C106</t>
+          <t>C110</t>
         </is>
       </c>
       <c r="R180" t="inlineStr">
@@ -13316,7 +13316,7 @@
       </c>
       <c r="Q181" t="inlineStr">
         <is>
-          <t>C106</t>
+          <t>C110</t>
         </is>
       </c>
       <c r="R181" t="inlineStr">
@@ -13380,7 +13380,7 @@
       </c>
       <c r="Q182" t="inlineStr">
         <is>
-          <t>C106</t>
+          <t>C110</t>
         </is>
       </c>
       <c r="R182" t="inlineStr">
@@ -13444,7 +13444,7 @@
       </c>
       <c r="Q183" t="inlineStr">
         <is>
-          <t>C106</t>
+          <t>C110</t>
         </is>
       </c>
       <c r="R183" t="inlineStr">
@@ -13508,7 +13508,7 @@
       </c>
       <c r="Q184" t="inlineStr">
         <is>
-          <t>C106</t>
+          <t>C110</t>
         </is>
       </c>
       <c r="R184" t="inlineStr">
@@ -13572,7 +13572,7 @@
       </c>
       <c r="Q185" t="inlineStr">
         <is>
-          <t>C106</t>
+          <t>C110</t>
         </is>
       </c>
       <c r="R185" t="inlineStr">
@@ -13636,7 +13636,7 @@
       </c>
       <c r="Q186" t="inlineStr">
         <is>
-          <t>C106</t>
+          <t>C110</t>
         </is>
       </c>
       <c r="R186" t="inlineStr">
@@ -13700,7 +13700,7 @@
       </c>
       <c r="Q187" t="inlineStr">
         <is>
-          <t>C106</t>
+          <t>C110</t>
         </is>
       </c>
       <c r="R187" t="inlineStr">
@@ -13764,7 +13764,7 @@
       </c>
       <c r="Q188" t="inlineStr">
         <is>
-          <t>C106</t>
+          <t>C110</t>
         </is>
       </c>
       <c r="R188" t="inlineStr">
@@ -13828,7 +13828,7 @@
       </c>
       <c r="Q189" t="inlineStr">
         <is>
-          <t>C106</t>
+          <t>C110</t>
         </is>
       </c>
       <c r="R189" t="inlineStr">
@@ -13892,7 +13892,7 @@
       </c>
       <c r="Q190" t="inlineStr">
         <is>
-          <t>C106</t>
+          <t>C110</t>
         </is>
       </c>
       <c r="R190" t="inlineStr">
@@ -13956,7 +13956,7 @@
       </c>
       <c r="Q191" t="inlineStr">
         <is>
-          <t>C106</t>
+          <t>C110</t>
         </is>
       </c>
       <c r="R191" t="inlineStr">
@@ -14020,7 +14020,7 @@
       </c>
       <c r="Q192" t="inlineStr">
         <is>
-          <t>C106</t>
+          <t>C110</t>
         </is>
       </c>
       <c r="R192" t="inlineStr">
@@ -14084,7 +14084,7 @@
       </c>
       <c r="Q193" t="inlineStr">
         <is>
-          <t>C106</t>
+          <t>C110</t>
         </is>
       </c>
       <c r="R193" t="inlineStr">
@@ -14148,7 +14148,7 @@
       </c>
       <c r="Q194" t="inlineStr">
         <is>
-          <t>C106</t>
+          <t>C110</t>
         </is>
       </c>
       <c r="R194" t="inlineStr">
@@ -14212,7 +14212,7 @@
       </c>
       <c r="Q195" t="inlineStr">
         <is>
-          <t>C106</t>
+          <t>C110</t>
         </is>
       </c>
       <c r="R195" t="inlineStr">
@@ -14276,7 +14276,7 @@
       </c>
       <c r="Q196" t="inlineStr">
         <is>
-          <t>C106</t>
+          <t>C110</t>
         </is>
       </c>
       <c r="R196" t="inlineStr">
@@ -14340,7 +14340,7 @@
       </c>
       <c r="Q197" t="inlineStr">
         <is>
-          <t>C106</t>
+          <t>C110</t>
         </is>
       </c>
       <c r="R197" t="inlineStr">
@@ -14404,7 +14404,7 @@
       </c>
       <c r="Q198" t="inlineStr">
         <is>
-          <t>C106</t>
+          <t>C110</t>
         </is>
       </c>
       <c r="R198" t="inlineStr">
@@ -14468,7 +14468,7 @@
       </c>
       <c r="Q199" t="inlineStr">
         <is>
-          <t>C106</t>
+          <t>C110</t>
         </is>
       </c>
       <c r="R199" t="inlineStr">
@@ -14532,7 +14532,7 @@
       </c>
       <c r="Q200" t="inlineStr">
         <is>
-          <t>C106</t>
+          <t>C110</t>
         </is>
       </c>
       <c r="R200" t="inlineStr">
@@ -14596,7 +14596,7 @@
       </c>
       <c r="Q201" t="inlineStr">
         <is>
-          <t>C106</t>
+          <t>C110</t>
         </is>
       </c>
       <c r="R201" t="inlineStr">
@@ -14660,7 +14660,7 @@
       </c>
       <c r="Q202" t="inlineStr">
         <is>
-          <t>C106</t>
+          <t>C110</t>
         </is>
       </c>
       <c r="R202" t="inlineStr">
@@ -14724,7 +14724,7 @@
       </c>
       <c r="Q203" t="inlineStr">
         <is>
-          <t>C106</t>
+          <t>C110</t>
         </is>
       </c>
       <c r="R203" t="inlineStr">
@@ -14788,7 +14788,7 @@
       </c>
       <c r="Q204" t="inlineStr">
         <is>
-          <t>C106</t>
+          <t>C110</t>
         </is>
       </c>
       <c r="R204" t="inlineStr">
@@ -14852,7 +14852,7 @@
       </c>
       <c r="Q205" t="inlineStr">
         <is>
-          <t>C106</t>
+          <t>C110</t>
         </is>
       </c>
       <c r="R205" t="inlineStr">
@@ -14916,7 +14916,7 @@
       </c>
       <c r="Q206" t="inlineStr">
         <is>
-          <t>C106</t>
+          <t>C110</t>
         </is>
       </c>
       <c r="R206" t="inlineStr">
@@ -14980,7 +14980,7 @@
       </c>
       <c r="Q207" t="inlineStr">
         <is>
-          <t>C106</t>
+          <t>C110</t>
         </is>
       </c>
       <c r="R207" t="inlineStr">
@@ -15044,7 +15044,7 @@
       </c>
       <c r="Q208" t="inlineStr">
         <is>
-          <t>C106</t>
+          <t>C110</t>
         </is>
       </c>
       <c r="R208" t="inlineStr">
@@ -15108,7 +15108,7 @@
       </c>
       <c r="Q209" t="inlineStr">
         <is>
-          <t>C106</t>
+          <t>C110</t>
         </is>
       </c>
       <c r="R209" t="inlineStr">
@@ -15172,7 +15172,7 @@
       </c>
       <c r="Q210" t="inlineStr">
         <is>
-          <t>C106</t>
+          <t>C110</t>
         </is>
       </c>
       <c r="R210" t="inlineStr">
@@ -15236,7 +15236,7 @@
       </c>
       <c r="Q211" t="inlineStr">
         <is>
-          <t>C106</t>
+          <t>C110</t>
         </is>
       </c>
       <c r="R211" t="inlineStr">
@@ -15300,7 +15300,7 @@
       </c>
       <c r="Q212" t="inlineStr">
         <is>
-          <t>C106</t>
+          <t>C110</t>
         </is>
       </c>
       <c r="R212" t="inlineStr">
@@ -15364,7 +15364,7 @@
       </c>
       <c r="Q213" t="inlineStr">
         <is>
-          <t>C106</t>
+          <t>C110</t>
         </is>
       </c>
       <c r="R213" t="inlineStr">
@@ -15428,7 +15428,7 @@
       </c>
       <c r="Q214" t="inlineStr">
         <is>
-          <t>C106</t>
+          <t>C110</t>
         </is>
       </c>
       <c r="R214" t="inlineStr">
@@ -15492,7 +15492,7 @@
       </c>
       <c r="Q215" t="inlineStr">
         <is>
-          <t>C106</t>
+          <t>C110</t>
         </is>
       </c>
       <c r="R215" t="inlineStr">
@@ -15556,7 +15556,7 @@
       </c>
       <c r="Q216" t="inlineStr">
         <is>
-          <t>C106</t>
+          <t>C110</t>
         </is>
       </c>
       <c r="R216" t="inlineStr">
@@ -15620,7 +15620,7 @@
       </c>
       <c r="Q217" t="inlineStr">
         <is>
-          <t>C106</t>
+          <t>C110</t>
         </is>
       </c>
       <c r="R217" t="inlineStr">
@@ -15684,7 +15684,7 @@
       </c>
       <c r="Q218" t="inlineStr">
         <is>
-          <t>C106</t>
+          <t>C110</t>
         </is>
       </c>
       <c r="R218" t="inlineStr">
@@ -15748,7 +15748,7 @@
       </c>
       <c r="Q219" t="inlineStr">
         <is>
-          <t>C106</t>
+          <t>C110</t>
         </is>
       </c>
       <c r="R219" t="inlineStr">
@@ -15812,7 +15812,7 @@
       </c>
       <c r="Q220" t="inlineStr">
         <is>
-          <t>C106</t>
+          <t>C110</t>
         </is>
       </c>
       <c r="R220" t="inlineStr">
@@ -15876,7 +15876,7 @@
       </c>
       <c r="Q221" t="inlineStr">
         <is>
-          <t>C106</t>
+          <t>C110</t>
         </is>
       </c>
       <c r="R221" t="inlineStr">
@@ -15940,7 +15940,7 @@
       </c>
       <c r="Q222" t="inlineStr">
         <is>
-          <t>C106</t>
+          <t>C110</t>
         </is>
       </c>
       <c r="R222" t="inlineStr">
@@ -16004,7 +16004,7 @@
       </c>
       <c r="Q223" t="inlineStr">
         <is>
-          <t>C106</t>
+          <t>C110</t>
         </is>
       </c>
       <c r="R223" t="inlineStr">
@@ -16068,7 +16068,7 @@
       </c>
       <c r="Q224" t="inlineStr">
         <is>
-          <t>C106</t>
+          <t>C110</t>
         </is>
       </c>
       <c r="R224" t="inlineStr">
@@ -16132,7 +16132,7 @@
       </c>
       <c r="Q225" t="inlineStr">
         <is>
-          <t>C106</t>
+          <t>C110</t>
         </is>
       </c>
       <c r="R225" t="inlineStr">
@@ -16196,7 +16196,7 @@
       </c>
       <c r="Q226" t="inlineStr">
         <is>
-          <t>C106</t>
+          <t>C110</t>
         </is>
       </c>
       <c r="R226" t="inlineStr">
@@ -16262,7 +16262,7 @@
       </c>
       <c r="Q227" t="inlineStr">
         <is>
-          <t>C119</t>
+          <t>C123</t>
         </is>
       </c>
       <c r="R227" t="inlineStr">
@@ -16328,7 +16328,7 @@
       </c>
       <c r="Q228" t="inlineStr">
         <is>
-          <t>C119</t>
+          <t>C123</t>
         </is>
       </c>
       <c r="R228" t="inlineStr">
@@ -16394,7 +16394,7 @@
       </c>
       <c r="Q229" t="inlineStr">
         <is>
-          <t>C119</t>
+          <t>C123</t>
         </is>
       </c>
       <c r="R229" t="inlineStr">
@@ -16460,7 +16460,7 @@
       </c>
       <c r="Q230" t="inlineStr">
         <is>
-          <t>C119</t>
+          <t>C123</t>
         </is>
       </c>
       <c r="R230" t="inlineStr">
@@ -16526,7 +16526,7 @@
       </c>
       <c r="Q231" t="inlineStr">
         <is>
-          <t>C119</t>
+          <t>C123</t>
         </is>
       </c>
       <c r="R231" t="inlineStr">
@@ -16592,7 +16592,7 @@
       </c>
       <c r="Q232" t="inlineStr">
         <is>
-          <t>C119</t>
+          <t>C123</t>
         </is>
       </c>
       <c r="R232" t="inlineStr">
@@ -16658,7 +16658,7 @@
       </c>
       <c r="Q233" t="inlineStr">
         <is>
-          <t>C119</t>
+          <t>C123</t>
         </is>
       </c>
       <c r="R233" t="inlineStr">
@@ -16724,7 +16724,7 @@
       </c>
       <c r="Q234" t="inlineStr">
         <is>
-          <t>C119</t>
+          <t>C123</t>
         </is>
       </c>
       <c r="R234" t="inlineStr">
@@ -16790,7 +16790,7 @@
       </c>
       <c r="Q235" t="inlineStr">
         <is>
-          <t>C119</t>
+          <t>C123</t>
         </is>
       </c>
       <c r="R235" t="inlineStr">
@@ -16856,7 +16856,7 @@
       </c>
       <c r="Q236" t="inlineStr">
         <is>
-          <t>C119</t>
+          <t>C123</t>
         </is>
       </c>
       <c r="R236" t="inlineStr">
@@ -16922,7 +16922,7 @@
       </c>
       <c r="Q237" t="inlineStr">
         <is>
-          <t>C119</t>
+          <t>C123</t>
         </is>
       </c>
       <c r="R237" t="inlineStr">
@@ -16988,7 +16988,7 @@
       </c>
       <c r="Q238" t="inlineStr">
         <is>
-          <t>C119</t>
+          <t>C123</t>
         </is>
       </c>
       <c r="R238" t="inlineStr">
@@ -17054,7 +17054,7 @@
       </c>
       <c r="Q239" t="inlineStr">
         <is>
-          <t>C119</t>
+          <t>C123</t>
         </is>
       </c>
       <c r="R239" t="inlineStr">
@@ -17120,7 +17120,7 @@
       </c>
       <c r="Q240" t="inlineStr">
         <is>
-          <t>C119</t>
+          <t>C123</t>
         </is>
       </c>
       <c r="R240" t="inlineStr">
@@ -17186,7 +17186,7 @@
       </c>
       <c r="Q241" t="inlineStr">
         <is>
-          <t>C119</t>
+          <t>C123</t>
         </is>
       </c>
       <c r="R241" t="inlineStr">
@@ -17252,7 +17252,7 @@
       </c>
       <c r="Q242" t="inlineStr">
         <is>
-          <t>C119</t>
+          <t>C123</t>
         </is>
       </c>
       <c r="R242" t="inlineStr">
@@ -17318,7 +17318,7 @@
       </c>
       <c r="Q243" t="inlineStr">
         <is>
-          <t>C119</t>
+          <t>C123</t>
         </is>
       </c>
       <c r="R243" t="inlineStr">
@@ -17384,7 +17384,7 @@
       </c>
       <c r="Q244" t="inlineStr">
         <is>
-          <t>C119</t>
+          <t>C123</t>
         </is>
       </c>
       <c r="R244" t="inlineStr">
@@ -17450,7 +17450,7 @@
       </c>
       <c r="Q245" t="inlineStr">
         <is>
-          <t>C119</t>
+          <t>C123</t>
         </is>
       </c>
       <c r="R245" t="inlineStr">
@@ -17516,7 +17516,7 @@
       </c>
       <c r="Q246" t="inlineStr">
         <is>
-          <t>C119</t>
+          <t>C123</t>
         </is>
       </c>
       <c r="R246" t="inlineStr">
@@ -17582,7 +17582,7 @@
       </c>
       <c r="Q247" t="inlineStr">
         <is>
-          <t>C119</t>
+          <t>C123</t>
         </is>
       </c>
       <c r="R247" t="inlineStr">
@@ -17648,7 +17648,7 @@
       </c>
       <c r="Q248" t="inlineStr">
         <is>
-          <t>C119</t>
+          <t>C123</t>
         </is>
       </c>
       <c r="R248" t="inlineStr">
@@ -17714,7 +17714,7 @@
       </c>
       <c r="Q249" t="inlineStr">
         <is>
-          <t>C119</t>
+          <t>C123</t>
         </is>
       </c>
       <c r="R249" t="inlineStr">
@@ -17780,7 +17780,7 @@
       </c>
       <c r="Q250" t="inlineStr">
         <is>
-          <t>C119</t>
+          <t>C123</t>
         </is>
       </c>
       <c r="R250" t="inlineStr">
@@ -17846,7 +17846,7 @@
       </c>
       <c r="Q251" t="inlineStr">
         <is>
-          <t>C119</t>
+          <t>C123</t>
         </is>
       </c>
       <c r="R251" t="inlineStr">
@@ -17912,7 +17912,7 @@
       </c>
       <c r="Q252" t="inlineStr">
         <is>
-          <t>C119</t>
+          <t>C123</t>
         </is>
       </c>
       <c r="R252" t="inlineStr">
@@ -17978,7 +17978,7 @@
       </c>
       <c r="Q253" t="inlineStr">
         <is>
-          <t>C119</t>
+          <t>C123</t>
         </is>
       </c>
       <c r="R253" t="inlineStr">
@@ -18044,7 +18044,7 @@
       </c>
       <c r="Q254" t="inlineStr">
         <is>
-          <t>C119</t>
+          <t>C123</t>
         </is>
       </c>
       <c r="R254" t="inlineStr">
@@ -18110,7 +18110,7 @@
       </c>
       <c r="Q255" t="inlineStr">
         <is>
-          <t>C119</t>
+          <t>C123</t>
         </is>
       </c>
       <c r="R255" t="inlineStr">
@@ -18176,7 +18176,7 @@
       </c>
       <c r="Q256" t="inlineStr">
         <is>
-          <t>C119</t>
+          <t>C123</t>
         </is>
       </c>
       <c r="R256" t="inlineStr">
@@ -18242,7 +18242,7 @@
       </c>
       <c r="Q257" t="inlineStr">
         <is>
-          <t>C119</t>
+          <t>C123</t>
         </is>
       </c>
       <c r="R257" t="inlineStr">
@@ -18308,7 +18308,7 @@
       </c>
       <c r="Q258" t="inlineStr">
         <is>
-          <t>C119</t>
+          <t>C123</t>
         </is>
       </c>
       <c r="R258" t="inlineStr">
@@ -18374,7 +18374,7 @@
       </c>
       <c r="Q259" t="inlineStr">
         <is>
-          <t>C119</t>
+          <t>C123</t>
         </is>
       </c>
       <c r="R259" t="inlineStr">
@@ -18440,7 +18440,7 @@
       </c>
       <c r="Q260" t="inlineStr">
         <is>
-          <t>C119</t>
+          <t>C123</t>
         </is>
       </c>
       <c r="R260" t="inlineStr">
@@ -18506,7 +18506,7 @@
       </c>
       <c r="Q261" t="inlineStr">
         <is>
-          <t>C119</t>
+          <t>C123</t>
         </is>
       </c>
       <c r="R261" t="inlineStr">
@@ -18572,7 +18572,7 @@
       </c>
       <c r="Q262" t="inlineStr">
         <is>
-          <t>C119</t>
+          <t>C123</t>
         </is>
       </c>
       <c r="R262" t="inlineStr">
@@ -18638,7 +18638,7 @@
       </c>
       <c r="Q263" t="inlineStr">
         <is>
-          <t>C119</t>
+          <t>C123</t>
         </is>
       </c>
       <c r="R263" t="inlineStr">
@@ -18704,7 +18704,7 @@
       </c>
       <c r="Q264" t="inlineStr">
         <is>
-          <t>C119</t>
+          <t>C123</t>
         </is>
       </c>
       <c r="R264" t="inlineStr">
@@ -18770,7 +18770,7 @@
       </c>
       <c r="Q265" t="inlineStr">
         <is>
-          <t>C119</t>
+          <t>C123</t>
         </is>
       </c>
       <c r="R265" t="inlineStr">
@@ -18836,7 +18836,7 @@
       </c>
       <c r="Q266" t="inlineStr">
         <is>
-          <t>C119</t>
+          <t>C123</t>
         </is>
       </c>
       <c r="R266" t="inlineStr">
@@ -18902,7 +18902,7 @@
       </c>
       <c r="Q267" t="inlineStr">
         <is>
-          <t>C119</t>
+          <t>C123</t>
         </is>
       </c>
       <c r="R267" t="inlineStr">
@@ -18968,7 +18968,7 @@
       </c>
       <c r="Q268" t="inlineStr">
         <is>
-          <t>C119</t>
+          <t>C123</t>
         </is>
       </c>
       <c r="R268" t="inlineStr">
@@ -19034,7 +19034,7 @@
       </c>
       <c r="Q269" t="inlineStr">
         <is>
-          <t>C119</t>
+          <t>C123</t>
         </is>
       </c>
       <c r="R269" t="inlineStr">
@@ -19100,7 +19100,7 @@
       </c>
       <c r="Q270" t="inlineStr">
         <is>
-          <t>C119</t>
+          <t>C123</t>
         </is>
       </c>
       <c r="R270" t="inlineStr">
@@ -19166,7 +19166,7 @@
       </c>
       <c r="Q271" t="inlineStr">
         <is>
-          <t>C119</t>
+          <t>C123</t>
         </is>
       </c>
       <c r="R271" t="inlineStr">
@@ -19232,7 +19232,7 @@
       </c>
       <c r="Q272" t="inlineStr">
         <is>
-          <t>C119</t>
+          <t>C123</t>
         </is>
       </c>
       <c r="R272" t="inlineStr">
@@ -19298,7 +19298,7 @@
       </c>
       <c r="Q273" t="inlineStr">
         <is>
-          <t>C119</t>
+          <t>C123</t>
         </is>
       </c>
       <c r="R273" t="inlineStr">
@@ -19364,7 +19364,7 @@
       </c>
       <c r="Q274" t="inlineStr">
         <is>
-          <t>C119</t>
+          <t>C123</t>
         </is>
       </c>
       <c r="R274" t="inlineStr">
@@ -19430,7 +19430,7 @@
       </c>
       <c r="Q275" t="inlineStr">
         <is>
-          <t>C119</t>
+          <t>C123</t>
         </is>
       </c>
       <c r="R275" t="inlineStr">
@@ -19496,7 +19496,7 @@
       </c>
       <c r="Q276" t="inlineStr">
         <is>
-          <t>C119</t>
+          <t>C123</t>
         </is>
       </c>
       <c r="R276" t="inlineStr">
@@ -19562,7 +19562,7 @@
       </c>
       <c r="Q277" t="inlineStr">
         <is>
-          <t>C119</t>
+          <t>C123</t>
         </is>
       </c>
       <c r="R277" t="inlineStr">
@@ -19628,7 +19628,7 @@
       </c>
       <c r="Q278" t="inlineStr">
         <is>
-          <t>C119</t>
+          <t>C123</t>
         </is>
       </c>
       <c r="R278" t="inlineStr">
@@ -19694,7 +19694,7 @@
       </c>
       <c r="Q279" t="inlineStr">
         <is>
-          <t>C119</t>
+          <t>C123</t>
         </is>
       </c>
       <c r="R279" t="inlineStr">
@@ -19760,7 +19760,7 @@
       </c>
       <c r="Q280" t="inlineStr">
         <is>
-          <t>C119</t>
+          <t>C123</t>
         </is>
       </c>
       <c r="R280" t="inlineStr">
@@ -19826,7 +19826,7 @@
       </c>
       <c r="Q281" t="inlineStr">
         <is>
-          <t>C119</t>
+          <t>C123</t>
         </is>
       </c>
       <c r="R281" t="inlineStr">
@@ -19892,7 +19892,7 @@
       </c>
       <c r="Q282" t="inlineStr">
         <is>
-          <t>C119</t>
+          <t>C123</t>
         </is>
       </c>
       <c r="R282" t="inlineStr">
@@ -19956,7 +19956,7 @@
       </c>
       <c r="Q283" t="inlineStr">
         <is>
-          <t>C120</t>
+          <t>C124</t>
         </is>
       </c>
       <c r="R283" t="inlineStr">
@@ -20020,7 +20020,7 @@
       </c>
       <c r="Q284" t="inlineStr">
         <is>
-          <t>C120</t>
+          <t>C124</t>
         </is>
       </c>
       <c r="R284" t="inlineStr">
@@ -20084,7 +20084,7 @@
       </c>
       <c r="Q285" t="inlineStr">
         <is>
-          <t>C120</t>
+          <t>C124</t>
         </is>
       </c>
       <c r="R285" t="inlineStr">
@@ -20148,7 +20148,7 @@
       </c>
       <c r="Q286" t="inlineStr">
         <is>
-          <t>C120</t>
+          <t>C124</t>
         </is>
       </c>
       <c r="R286" t="inlineStr">
@@ -20212,7 +20212,7 @@
       </c>
       <c r="Q287" t="inlineStr">
         <is>
-          <t>C120</t>
+          <t>C124</t>
         </is>
       </c>
       <c r="R287" t="inlineStr">
@@ -20276,7 +20276,7 @@
       </c>
       <c r="Q288" t="inlineStr">
         <is>
-          <t>C120</t>
+          <t>C124</t>
         </is>
       </c>
       <c r="R288" t="inlineStr">
@@ -20340,7 +20340,7 @@
       </c>
       <c r="Q289" t="inlineStr">
         <is>
-          <t>C120</t>
+          <t>C124</t>
         </is>
       </c>
       <c r="R289" t="inlineStr">
@@ -20404,7 +20404,7 @@
       </c>
       <c r="Q290" t="inlineStr">
         <is>
-          <t>C120</t>
+          <t>C124</t>
         </is>
       </c>
       <c r="R290" t="inlineStr">
@@ -20468,7 +20468,7 @@
       </c>
       <c r="Q291" t="inlineStr">
         <is>
-          <t>C120</t>
+          <t>C124</t>
         </is>
       </c>
       <c r="R291" t="inlineStr">
@@ -20532,7 +20532,7 @@
       </c>
       <c r="Q292" t="inlineStr">
         <is>
-          <t>C120</t>
+          <t>C124</t>
         </is>
       </c>
       <c r="R292" t="inlineStr">
@@ -20596,7 +20596,7 @@
       </c>
       <c r="Q293" t="inlineStr">
         <is>
-          <t>C120</t>
+          <t>C124</t>
         </is>
       </c>
       <c r="R293" t="inlineStr">
@@ -20660,7 +20660,7 @@
       </c>
       <c r="Q294" t="inlineStr">
         <is>
-          <t>C120</t>
+          <t>C124</t>
         </is>
       </c>
       <c r="R294" t="inlineStr">
@@ -20724,7 +20724,7 @@
       </c>
       <c r="Q295" t="inlineStr">
         <is>
-          <t>C120</t>
+          <t>C124</t>
         </is>
       </c>
       <c r="R295" t="inlineStr">
@@ -20788,7 +20788,7 @@
       </c>
       <c r="Q296" t="inlineStr">
         <is>
-          <t>C120</t>
+          <t>C124</t>
         </is>
       </c>
       <c r="R296" t="inlineStr">
@@ -20852,7 +20852,7 @@
       </c>
       <c r="Q297" t="inlineStr">
         <is>
-          <t>C120</t>
+          <t>C124</t>
         </is>
       </c>
       <c r="R297" t="inlineStr">
@@ -20916,7 +20916,7 @@
       </c>
       <c r="Q298" t="inlineStr">
         <is>
-          <t>C120</t>
+          <t>C124</t>
         </is>
       </c>
       <c r="R298" t="inlineStr">
@@ -20980,7 +20980,7 @@
       </c>
       <c r="Q299" t="inlineStr">
         <is>
-          <t>C120</t>
+          <t>C124</t>
         </is>
       </c>
       <c r="R299" t="inlineStr">
@@ -21044,7 +21044,7 @@
       </c>
       <c r="Q300" t="inlineStr">
         <is>
-          <t>C120</t>
+          <t>C124</t>
         </is>
       </c>
       <c r="R300" t="inlineStr">
@@ -21108,7 +21108,7 @@
       </c>
       <c r="Q301" t="inlineStr">
         <is>
-          <t>C120</t>
+          <t>C124</t>
         </is>
       </c>
       <c r="R301" t="inlineStr">
@@ -21172,7 +21172,7 @@
       </c>
       <c r="Q302" t="inlineStr">
         <is>
-          <t>C120</t>
+          <t>C124</t>
         </is>
       </c>
       <c r="R302" t="inlineStr">
@@ -21236,7 +21236,7 @@
       </c>
       <c r="Q303" t="inlineStr">
         <is>
-          <t>C120</t>
+          <t>C124</t>
         </is>
       </c>
       <c r="R303" t="inlineStr">
@@ -21300,7 +21300,7 @@
       </c>
       <c r="Q304" t="inlineStr">
         <is>
-          <t>C120</t>
+          <t>C124</t>
         </is>
       </c>
       <c r="R304" t="inlineStr">
@@ -21364,7 +21364,7 @@
       </c>
       <c r="Q305" t="inlineStr">
         <is>
-          <t>C120</t>
+          <t>C124</t>
         </is>
       </c>
       <c r="R305" t="inlineStr">
@@ -21428,7 +21428,7 @@
       </c>
       <c r="Q306" t="inlineStr">
         <is>
-          <t>C120</t>
+          <t>C124</t>
         </is>
       </c>
       <c r="R306" t="inlineStr">
@@ -21492,7 +21492,7 @@
       </c>
       <c r="Q307" t="inlineStr">
         <is>
-          <t>C120</t>
+          <t>C124</t>
         </is>
       </c>
       <c r="R307" t="inlineStr">
@@ -21556,7 +21556,7 @@
       </c>
       <c r="Q308" t="inlineStr">
         <is>
-          <t>C120</t>
+          <t>C124</t>
         </is>
       </c>
       <c r="R308" t="inlineStr">
@@ -21620,7 +21620,7 @@
       </c>
       <c r="Q309" t="inlineStr">
         <is>
-          <t>C120</t>
+          <t>C124</t>
         </is>
       </c>
       <c r="R309" t="inlineStr">
@@ -21684,7 +21684,7 @@
       </c>
       <c r="Q310" t="inlineStr">
         <is>
-          <t>C120</t>
+          <t>C124</t>
         </is>
       </c>
       <c r="R310" t="inlineStr">
@@ -21748,7 +21748,7 @@
       </c>
       <c r="Q311" t="inlineStr">
         <is>
-          <t>C120</t>
+          <t>C124</t>
         </is>
       </c>
       <c r="R311" t="inlineStr">
@@ -21812,7 +21812,7 @@
       </c>
       <c r="Q312" t="inlineStr">
         <is>
-          <t>C120</t>
+          <t>C124</t>
         </is>
       </c>
       <c r="R312" t="inlineStr">
@@ -21876,7 +21876,7 @@
       </c>
       <c r="Q313" t="inlineStr">
         <is>
-          <t>C120</t>
+          <t>C124</t>
         </is>
       </c>
       <c r="R313" t="inlineStr">
@@ -21940,7 +21940,7 @@
       </c>
       <c r="Q314" t="inlineStr">
         <is>
-          <t>C120</t>
+          <t>C124</t>
         </is>
       </c>
       <c r="R314" t="inlineStr">
@@ -22004,7 +22004,7 @@
       </c>
       <c r="Q315" t="inlineStr">
         <is>
-          <t>C120</t>
+          <t>C124</t>
         </is>
       </c>
       <c r="R315" t="inlineStr">
@@ -22068,7 +22068,7 @@
       </c>
       <c r="Q316" t="inlineStr">
         <is>
-          <t>C120</t>
+          <t>C124</t>
         </is>
       </c>
       <c r="R316" t="inlineStr">
@@ -22132,7 +22132,7 @@
       </c>
       <c r="Q317" t="inlineStr">
         <is>
-          <t>C120</t>
+          <t>C124</t>
         </is>
       </c>
       <c r="R317" t="inlineStr">
@@ -22196,7 +22196,7 @@
       </c>
       <c r="Q318" t="inlineStr">
         <is>
-          <t>C120</t>
+          <t>C124</t>
         </is>
       </c>
       <c r="R318" t="inlineStr">
@@ -22260,7 +22260,7 @@
       </c>
       <c r="Q319" t="inlineStr">
         <is>
-          <t>C120</t>
+          <t>C124</t>
         </is>
       </c>
       <c r="R319" t="inlineStr">
@@ -22324,7 +22324,7 @@
       </c>
       <c r="Q320" t="inlineStr">
         <is>
-          <t>C120</t>
+          <t>C124</t>
         </is>
       </c>
       <c r="R320" t="inlineStr">
@@ -22388,7 +22388,7 @@
       </c>
       <c r="Q321" t="inlineStr">
         <is>
-          <t>C120</t>
+          <t>C124</t>
         </is>
       </c>
       <c r="R321" t="inlineStr">
@@ -22452,7 +22452,7 @@
       </c>
       <c r="Q322" t="inlineStr">
         <is>
-          <t>C120</t>
+          <t>C124</t>
         </is>
       </c>
       <c r="R322" t="inlineStr">
@@ -22516,7 +22516,7 @@
       </c>
       <c r="Q323" t="inlineStr">
         <is>
-          <t>C120</t>
+          <t>C124</t>
         </is>
       </c>
       <c r="R323" t="inlineStr">
@@ -22580,7 +22580,7 @@
       </c>
       <c r="Q324" t="inlineStr">
         <is>
-          <t>C120</t>
+          <t>C124</t>
         </is>
       </c>
       <c r="R324" t="inlineStr">
@@ -22644,7 +22644,7 @@
       </c>
       <c r="Q325" t="inlineStr">
         <is>
-          <t>C120</t>
+          <t>C124</t>
         </is>
       </c>
       <c r="R325" t="inlineStr">
@@ -22708,7 +22708,7 @@
       </c>
       <c r="Q326" t="inlineStr">
         <is>
-          <t>C120</t>
+          <t>C124</t>
         </is>
       </c>
       <c r="R326" t="inlineStr">
@@ -22772,7 +22772,7 @@
       </c>
       <c r="Q327" t="inlineStr">
         <is>
-          <t>C120</t>
+          <t>C124</t>
         </is>
       </c>
       <c r="R327" t="inlineStr">
@@ -22836,7 +22836,7 @@
       </c>
       <c r="Q328" t="inlineStr">
         <is>
-          <t>C120</t>
+          <t>C124</t>
         </is>
       </c>
       <c r="R328" t="inlineStr">
@@ -22900,7 +22900,7 @@
       </c>
       <c r="Q329" t="inlineStr">
         <is>
-          <t>C120</t>
+          <t>C124</t>
         </is>
       </c>
       <c r="R329" t="inlineStr">
@@ -22964,7 +22964,7 @@
       </c>
       <c r="Q330" t="inlineStr">
         <is>
-          <t>C120</t>
+          <t>C124</t>
         </is>
       </c>
       <c r="R330" t="inlineStr">
@@ -23028,7 +23028,7 @@
       </c>
       <c r="Q331" t="inlineStr">
         <is>
-          <t>C120</t>
+          <t>C124</t>
         </is>
       </c>
       <c r="R331" t="inlineStr">
@@ -23092,7 +23092,7 @@
       </c>
       <c r="Q332" t="inlineStr">
         <is>
-          <t>C120</t>
+          <t>C124</t>
         </is>
       </c>
       <c r="R332" t="inlineStr">
@@ -23156,7 +23156,7 @@
       </c>
       <c r="Q333" t="inlineStr">
         <is>
-          <t>C120</t>
+          <t>C124</t>
         </is>
       </c>
       <c r="R333" t="inlineStr">
@@ -23220,7 +23220,7 @@
       </c>
       <c r="Q334" t="inlineStr">
         <is>
-          <t>C120</t>
+          <t>C124</t>
         </is>
       </c>
       <c r="R334" t="inlineStr">
@@ -23284,7 +23284,7 @@
       </c>
       <c r="Q335" t="inlineStr">
         <is>
-          <t>C120</t>
+          <t>C124</t>
         </is>
       </c>
       <c r="R335" t="inlineStr">
@@ -23348,7 +23348,7 @@
       </c>
       <c r="Q336" t="inlineStr">
         <is>
-          <t>C120</t>
+          <t>C124</t>
         </is>
       </c>
       <c r="R336" t="inlineStr">
@@ -23412,7 +23412,7 @@
       </c>
       <c r="Q337" t="inlineStr">
         <is>
-          <t>C120</t>
+          <t>C124</t>
         </is>
       </c>
       <c r="R337" t="inlineStr">
@@ -23476,7 +23476,7 @@
       </c>
       <c r="Q338" t="inlineStr">
         <is>
-          <t>C120</t>
+          <t>C124</t>
         </is>
       </c>
       <c r="R338" t="inlineStr">
@@ -34693,12 +34693,12 @@
       <c r="O504" t="inlineStr"/>
       <c r="P504" t="inlineStr">
         <is>
-          <t>concentration-response series per chemical (Table S3, not extracted); positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
+          <t>not reported by the paper; stocks serially diluted to unstated working concentrations, and Table S3 gives the stock concentration and solvent only; positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
         </is>
       </c>
       <c r="Q504" t="inlineStr">
         <is>
-          <t>C149</t>
+          <t>C096</t>
         </is>
       </c>
       <c r="R504" t="inlineStr">
@@ -34761,12 +34761,12 @@
       <c r="O505" t="inlineStr"/>
       <c r="P505" t="inlineStr">
         <is>
-          <t>concentration-response series per chemical (Table S3, not extracted); positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
+          <t>not reported by the paper; stocks serially diluted to unstated working concentrations, and Table S3 gives the stock concentration and solvent only; positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
         </is>
       </c>
       <c r="Q505" t="inlineStr">
         <is>
-          <t>C149</t>
+          <t>C096</t>
         </is>
       </c>
       <c r="R505" t="inlineStr">
@@ -34827,12 +34827,12 @@
       <c r="O506" t="inlineStr"/>
       <c r="P506" t="inlineStr">
         <is>
-          <t>concentration-response series per chemical (Table S3, not extracted); positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
+          <t>not reported by the paper; stocks serially diluted to unstated working concentrations, and Table S3 gives the stock concentration and solvent only; positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
         </is>
       </c>
       <c r="Q506" t="inlineStr">
         <is>
-          <t>C149</t>
+          <t>C096</t>
         </is>
       </c>
       <c r="R506" t="inlineStr">
@@ -34895,12 +34895,12 @@
       <c r="O507" t="inlineStr"/>
       <c r="P507" t="inlineStr">
         <is>
-          <t>concentration-response series per chemical (Table S3, not extracted); positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
+          <t>not reported by the paper; stocks serially diluted to unstated working concentrations, and Table S3 gives the stock concentration and solvent only; positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
         </is>
       </c>
       <c r="Q507" t="inlineStr">
         <is>
-          <t>C149</t>
+          <t>C096</t>
         </is>
       </c>
       <c r="R507" t="inlineStr">
@@ -34961,12 +34961,12 @@
       <c r="O508" t="inlineStr"/>
       <c r="P508" t="inlineStr">
         <is>
-          <t>concentration-response series per chemical (Table S3, not extracted); positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
+          <t>not reported by the paper; stocks serially diluted to unstated working concentrations, and Table S3 gives the stock concentration and solvent only; positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
         </is>
       </c>
       <c r="Q508" t="inlineStr">
         <is>
-          <t>C149</t>
+          <t>C096</t>
         </is>
       </c>
       <c r="R508" t="inlineStr">
@@ -35029,12 +35029,12 @@
       <c r="O509" t="inlineStr"/>
       <c r="P509" t="inlineStr">
         <is>
-          <t>concentration-response series per chemical (Table S3, not extracted); positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
+          <t>not reported by the paper; stocks serially diluted to unstated working concentrations, and Table S3 gives the stock concentration and solvent only; positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
         </is>
       </c>
       <c r="Q509" t="inlineStr">
         <is>
-          <t>C149</t>
+          <t>C096</t>
         </is>
       </c>
       <c r="R509" t="inlineStr">
@@ -35097,12 +35097,12 @@
       <c r="O510" t="inlineStr"/>
       <c r="P510" t="inlineStr">
         <is>
-          <t>concentration-response series per chemical (Table S3, not extracted); positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
+          <t>not reported by the paper; stocks serially diluted to unstated working concentrations, and Table S3 gives the stock concentration and solvent only; positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
         </is>
       </c>
       <c r="Q510" t="inlineStr">
         <is>
-          <t>C149</t>
+          <t>C097</t>
         </is>
       </c>
       <c r="R510" t="inlineStr">
@@ -35163,12 +35163,12 @@
       <c r="O511" t="inlineStr"/>
       <c r="P511" t="inlineStr">
         <is>
-          <t>concentration-response series per chemical (Table S3, not extracted); positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
+          <t>not reported by the paper; stocks serially diluted to unstated working concentrations, and Table S3 gives the stock concentration and solvent only; positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
         </is>
       </c>
       <c r="Q511" t="inlineStr">
         <is>
-          <t>C149</t>
+          <t>C096</t>
         </is>
       </c>
       <c r="R511" t="inlineStr">
@@ -35231,12 +35231,12 @@
       <c r="O512" t="inlineStr"/>
       <c r="P512" t="inlineStr">
         <is>
-          <t>concentration-response series per chemical (Table S3, not extracted); positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
+          <t>not reported by the paper; stocks serially diluted to unstated working concentrations, and Table S3 gives the stock concentration and solvent only; positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
         </is>
       </c>
       <c r="Q512" t="inlineStr">
         <is>
-          <t>C149</t>
+          <t>C096</t>
         </is>
       </c>
       <c r="R512" t="inlineStr">
@@ -35299,12 +35299,12 @@
       <c r="O513" t="inlineStr"/>
       <c r="P513" t="inlineStr">
         <is>
-          <t>concentration-response series per chemical (Table S3, not extracted); positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
+          <t>not reported by the paper; stocks serially diluted to unstated working concentrations, and Table S3 gives the stock concentration and solvent only; positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
         </is>
       </c>
       <c r="Q513" t="inlineStr">
         <is>
-          <t>C149</t>
+          <t>C096</t>
         </is>
       </c>
       <c r="R513" t="inlineStr">
@@ -35367,12 +35367,12 @@
       <c r="O514" t="inlineStr"/>
       <c r="P514" t="inlineStr">
         <is>
-          <t>concentration-response series per chemical (Table S3, not extracted); positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
+          <t>not reported by the paper; stocks serially diluted to unstated working concentrations, and Table S3 gives the stock concentration and solvent only; positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
         </is>
       </c>
       <c r="Q514" t="inlineStr">
         <is>
-          <t>C149</t>
+          <t>C096</t>
         </is>
       </c>
       <c r="R514" t="inlineStr">
@@ -35435,12 +35435,12 @@
       <c r="O515" t="inlineStr"/>
       <c r="P515" t="inlineStr">
         <is>
-          <t>concentration-response series per chemical (Table S3, not extracted); positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
+          <t>not reported by the paper; stocks serially diluted to unstated working concentrations, and Table S3 gives the stock concentration and solvent only; positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
         </is>
       </c>
       <c r="Q515" t="inlineStr">
         <is>
-          <t>C149</t>
+          <t>C096</t>
         </is>
       </c>
       <c r="R515" t="inlineStr">
@@ -35503,12 +35503,12 @@
       <c r="O516" t="inlineStr"/>
       <c r="P516" t="inlineStr">
         <is>
-          <t>concentration-response series per chemical (Table S3, not extracted); positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
+          <t>not reported by the paper; stocks serially diluted to unstated working concentrations, and Table S3 gives the stock concentration and solvent only; positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
         </is>
       </c>
       <c r="Q516" t="inlineStr">
         <is>
-          <t>C149</t>
+          <t>C096</t>
         </is>
       </c>
       <c r="R516" t="inlineStr">
@@ -35571,12 +35571,12 @@
       <c r="O517" t="inlineStr"/>
       <c r="P517" t="inlineStr">
         <is>
-          <t>concentration-response series per chemical (Table S3, not extracted); positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
+          <t>not reported by the paper; stocks serially diluted to unstated working concentrations, and Table S3 gives the stock concentration and solvent only; positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
         </is>
       </c>
       <c r="Q517" t="inlineStr">
         <is>
-          <t>C149</t>
+          <t>C096</t>
         </is>
       </c>
       <c r="R517" t="inlineStr">
@@ -35639,12 +35639,12 @@
       <c r="O518" t="inlineStr"/>
       <c r="P518" t="inlineStr">
         <is>
-          <t>concentration-response series per chemical (Table S3, not extracted); positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
+          <t>not reported by the paper; stocks serially diluted to unstated working concentrations, and Table S3 gives the stock concentration and solvent only; positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
         </is>
       </c>
       <c r="Q518" t="inlineStr">
         <is>
-          <t>C149</t>
+          <t>C096</t>
         </is>
       </c>
       <c r="R518" t="inlineStr">
@@ -35707,12 +35707,12 @@
       <c r="O519" t="inlineStr"/>
       <c r="P519" t="inlineStr">
         <is>
-          <t>concentration-response series per chemical (Table S3, not extracted); positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
+          <t>not reported by the paper; stocks serially diluted to unstated working concentrations, and Table S3 gives the stock concentration and solvent only; positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
         </is>
       </c>
       <c r="Q519" t="inlineStr">
         <is>
-          <t>C149</t>
+          <t>C096</t>
         </is>
       </c>
       <c r="R519" t="inlineStr">
@@ -35775,12 +35775,12 @@
       <c r="O520" t="inlineStr"/>
       <c r="P520" t="inlineStr">
         <is>
-          <t>concentration-response series per chemical (Table S3, not extracted); positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
+          <t>not reported by the paper; stocks serially diluted to unstated working concentrations, and Table S3 gives the stock concentration and solvent only; positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
         </is>
       </c>
       <c r="Q520" t="inlineStr">
         <is>
-          <t>C149</t>
+          <t>C096</t>
         </is>
       </c>
       <c r="R520" t="inlineStr">
@@ -35843,12 +35843,12 @@
       <c r="O521" t="inlineStr"/>
       <c r="P521" t="inlineStr">
         <is>
-          <t>concentration-response series per chemical (Table S3, not extracted); positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
+          <t>not reported by the paper; stocks serially diluted to unstated working concentrations, and Table S3 gives the stock concentration and solvent only; positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
         </is>
       </c>
       <c r="Q521" t="inlineStr">
         <is>
-          <t>C149</t>
+          <t>C096</t>
         </is>
       </c>
       <c r="R521" t="inlineStr">
@@ -35911,12 +35911,12 @@
       <c r="O522" t="inlineStr"/>
       <c r="P522" t="inlineStr">
         <is>
-          <t>concentration-response series per chemical (Table S3, not extracted); positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
+          <t>not reported by the paper; stocks serially diluted to unstated working concentrations, and Table S3 gives the stock concentration and solvent only; positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
         </is>
       </c>
       <c r="Q522" t="inlineStr">
         <is>
-          <t>C149</t>
+          <t>C096</t>
         </is>
       </c>
       <c r="R522" t="inlineStr">
@@ -35979,12 +35979,12 @@
       <c r="O523" t="inlineStr"/>
       <c r="P523" t="inlineStr">
         <is>
-          <t>concentration-response series per chemical (Table S3, not extracted); positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
+          <t>not reported by the paper; stocks serially diluted to unstated working concentrations, and Table S3 gives the stock concentration and solvent only; positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
         </is>
       </c>
       <c r="Q523" t="inlineStr">
         <is>
-          <t>C149</t>
+          <t>C096</t>
         </is>
       </c>
       <c r="R523" t="inlineStr">
@@ -36047,12 +36047,12 @@
       <c r="O524" t="inlineStr"/>
       <c r="P524" t="inlineStr">
         <is>
-          <t>concentration-response series per chemical (Table S3, not extracted); positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
+          <t>not reported by the paper; stocks serially diluted to unstated working concentrations, and Table S3 gives the stock concentration and solvent only; positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
         </is>
       </c>
       <c r="Q524" t="inlineStr">
         <is>
-          <t>C149</t>
+          <t>C096</t>
         </is>
       </c>
       <c r="R524" t="inlineStr">
@@ -36115,12 +36115,12 @@
       <c r="O525" t="inlineStr"/>
       <c r="P525" t="inlineStr">
         <is>
-          <t>concentration-response series per chemical (Table S3, not extracted); positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
+          <t>not reported by the paper; stocks serially diluted to unstated working concentrations, and Table S3 gives the stock concentration and solvent only; positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
         </is>
       </c>
       <c r="Q525" t="inlineStr">
         <is>
-          <t>C149</t>
+          <t>C096</t>
         </is>
       </c>
       <c r="R525" t="inlineStr">
@@ -36183,12 +36183,12 @@
       <c r="O526" t="inlineStr"/>
       <c r="P526" t="inlineStr">
         <is>
-          <t>concentration-response series per chemical (Table S3, not extracted); positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
+          <t>not reported by the paper; stocks serially diluted to unstated working concentrations, and Table S3 gives the stock concentration and solvent only; positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
         </is>
       </c>
       <c r="Q526" t="inlineStr">
         <is>
-          <t>C149</t>
+          <t>C096</t>
         </is>
       </c>
       <c r="R526" t="inlineStr">
@@ -36251,12 +36251,12 @@
       <c r="O527" t="inlineStr"/>
       <c r="P527" t="inlineStr">
         <is>
-          <t>concentration-response series per chemical (Table S3, not extracted); positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
+          <t>not reported by the paper; stocks serially diluted to unstated working concentrations, and Table S3 gives the stock concentration and solvent only; positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
         </is>
       </c>
       <c r="Q527" t="inlineStr">
         <is>
-          <t>C149</t>
+          <t>C096</t>
         </is>
       </c>
       <c r="R527" t="inlineStr">
@@ -36319,12 +36319,12 @@
       <c r="O528" t="inlineStr"/>
       <c r="P528" t="inlineStr">
         <is>
-          <t>concentration-response series per chemical (Table S3, not extracted); positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
+          <t>not reported by the paper; stocks serially diluted to unstated working concentrations, and Table S3 gives the stock concentration and solvent only; positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
         </is>
       </c>
       <c r="Q528" t="inlineStr">
         <is>
-          <t>C149</t>
+          <t>C096</t>
         </is>
       </c>
       <c r="R528" t="inlineStr">
@@ -36387,12 +36387,12 @@
       <c r="O529" t="inlineStr"/>
       <c r="P529" t="inlineStr">
         <is>
-          <t>concentration-response series per chemical (Table S3, not extracted); positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
+          <t>not reported by the paper; stocks serially diluted to unstated working concentrations, and Table S3 gives the stock concentration and solvent only; positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
         </is>
       </c>
       <c r="Q529" t="inlineStr">
         <is>
-          <t>C149</t>
+          <t>C096</t>
         </is>
       </c>
       <c r="R529" t="inlineStr">
@@ -36455,12 +36455,12 @@
       <c r="O530" t="inlineStr"/>
       <c r="P530" t="inlineStr">
         <is>
-          <t>concentration-response series per chemical (Table S3, not extracted); positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
+          <t>not reported by the paper; stocks serially diluted to unstated working concentrations, and Table S3 gives the stock concentration and solvent only; positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
         </is>
       </c>
       <c r="Q530" t="inlineStr">
         <is>
-          <t>C149</t>
+          <t>C096</t>
         </is>
       </c>
       <c r="R530" t="inlineStr">
@@ -36523,12 +36523,12 @@
       <c r="O531" t="inlineStr"/>
       <c r="P531" t="inlineStr">
         <is>
-          <t>concentration-response series per chemical (Table S3, not extracted); positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
+          <t>not reported by the paper; stocks serially diluted to unstated working concentrations, and Table S3 gives the stock concentration and solvent only; positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
         </is>
       </c>
       <c r="Q531" t="inlineStr">
         <is>
-          <t>C149</t>
+          <t>C096</t>
         </is>
       </c>
       <c r="R531" t="inlineStr">
@@ -38274,7 +38274,7 @@
       </c>
       <c r="Q556" t="inlineStr">
         <is>
-          <t>C103</t>
+          <t>C107</t>
         </is>
       </c>
       <c r="R556" t="inlineStr">
@@ -38340,7 +38340,7 @@
       </c>
       <c r="Q557" t="inlineStr">
         <is>
-          <t>C103</t>
+          <t>C107</t>
         </is>
       </c>
       <c r="R557" t="inlineStr">
@@ -38406,7 +38406,7 @@
       </c>
       <c r="Q558" t="inlineStr">
         <is>
-          <t>C103</t>
+          <t>C107</t>
         </is>
       </c>
       <c r="R558" t="inlineStr">
@@ -38472,7 +38472,7 @@
       </c>
       <c r="Q559" t="inlineStr">
         <is>
-          <t>C103</t>
+          <t>C107</t>
         </is>
       </c>
       <c r="R559" t="inlineStr">
@@ -38538,7 +38538,7 @@
       </c>
       <c r="Q560" t="inlineStr">
         <is>
-          <t>C104</t>
+          <t>C108</t>
         </is>
       </c>
       <c r="R560" t="inlineStr">
@@ -38604,7 +38604,7 @@
       </c>
       <c r="Q561" t="inlineStr">
         <is>
-          <t>C104</t>
+          <t>C108</t>
         </is>
       </c>
       <c r="R561" t="inlineStr">
@@ -38670,7 +38670,7 @@
       </c>
       <c r="Q562" t="inlineStr">
         <is>
-          <t>C104</t>
+          <t>C108</t>
         </is>
       </c>
       <c r="R562" t="inlineStr">
@@ -38736,7 +38736,7 @@
       </c>
       <c r="Q563" t="inlineStr">
         <is>
-          <t>C104</t>
+          <t>C108</t>
         </is>
       </c>
       <c r="R563" t="inlineStr">
@@ -38802,7 +38802,7 @@
       </c>
       <c r="Q564" t="inlineStr">
         <is>
-          <t>C104</t>
+          <t>C108</t>
         </is>
       </c>
       <c r="R564" t="inlineStr">
@@ -38868,7 +38868,7 @@
       </c>
       <c r="Q565" t="inlineStr">
         <is>
-          <t>C104</t>
+          <t>C108</t>
         </is>
       </c>
       <c r="R565" t="inlineStr">
@@ -38934,7 +38934,7 @@
       </c>
       <c r="Q566" t="inlineStr">
         <is>
-          <t>C104</t>
+          <t>C108</t>
         </is>
       </c>
       <c r="R566" t="inlineStr">
@@ -39000,7 +39000,7 @@
       </c>
       <c r="Q567" t="inlineStr">
         <is>
-          <t>C104</t>
+          <t>C108</t>
         </is>
       </c>
       <c r="R567" t="inlineStr">
@@ -39066,7 +39066,7 @@
       </c>
       <c r="Q568" t="inlineStr">
         <is>
-          <t>C104</t>
+          <t>C108</t>
         </is>
       </c>
       <c r="R568" t="inlineStr">
@@ -39879,7 +39879,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R53"/>
+  <dimension ref="A1:R54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -43213,12 +43213,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>C103</t>
+          <t>C096</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Jia 2022</t>
+          <t>Starnes 2025</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -43233,19 +43233,21 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>microscale thermophoresis (MST), Monolith NT.115, 25 C</t>
+          <t>differential scanning fluorimetry (DSF), GloMelt dye with ROX reference; Ka from the concentration-response of dTm by nonlinear regression</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>MST titration series</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr"/>
+          <t>not reported by the paper; stocks serially diluted to unstated working concentrations, and Table S3 gives the stock concentration and solvent only; positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
+        <v>130</v>
+      </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>see Text S7</t>
+          <t>0.13 mM</t>
         </is>
       </c>
       <c r="J47" t="inlineStr"/>
@@ -43254,39 +43256,39 @@
           <t>neither both concentrations nor a stated ratio</t>
         </is>
       </c>
-      <c r="L47" t="n">
-        <v>25</v>
-      </c>
+      <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
+          <t>thermal ramp - Ka is an apparent affinity at the melting transition, not a 37 C equilibrium constant</t>
+        </is>
+      </c>
+      <c r="N47" t="n">
+        <v>140</v>
+      </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Tris-HCl</t>
+          <t>HEPES-buffered saline: 140 mM NaCl, 50 mM HEPES, 0.38 mM Na2HPO4, pH 7.4</t>
         </is>
       </c>
       <c r="P47" t="n">
-        <v>5</v>
+        <v>62</v>
       </c>
       <c r="Q47" t="n">
-        <v>5</v>
+        <v>62</v>
       </c>
       <c r="R47" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>C104</t>
+          <t>C097</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Jia 2022</t>
+          <t>Starnes 2025</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -43296,24 +43298,26 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>liver fatty acid-binding protein (hL-FABP)</t>
+          <t>human serum albumin (HSA)</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>microscale thermophoresis (MST), Monolith NT.115; Kd over 21-40 C fitted by the van't Hoff equation, the value here being 25 C</t>
+          <t>differential scanning fluorimetry (DSF), GloMelt dye with ROX reference; Ka from the concentration-response of dTm by nonlinear regression</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>MST titration series</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr"/>
+          <t>not reported by the paper; stocks serially diluted to unstated working concentrations, and Table S3 gives the stock concentration and solvent only; positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
+        </is>
+      </c>
+      <c r="H48" t="n">
+        <v>130</v>
+      </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>see Text S7</t>
+          <t>0.13 mM</t>
         </is>
       </c>
       <c r="J48" t="inlineStr"/>
@@ -43322,39 +43326,39 @@
           <t>neither both concentrations nor a stated ratio</t>
         </is>
       </c>
-      <c r="L48" t="n">
-        <v>25</v>
-      </c>
+      <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
+          <t>thermal ramp - Ka is an apparent affinity at the melting transition, not a 37 C equilibrium constant</t>
+        </is>
+      </c>
+      <c r="N48" t="n">
+        <v>140</v>
+      </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>Tris-HCl</t>
+          <t>HEPES-buffered saline: 140 mM NaCl, 50 mM HEPES, 0.38 mM Na2HPO4, pH 7.4; plus 50% DMSO as co-solvent, required to dissolve this chemical (Table S3)</t>
         </is>
       </c>
       <c r="P48" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="Q48" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="R48" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>C105</t>
+          <t>C107</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Chen 2025</t>
+          <t>Jia 2022</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -43369,91 +43373,87 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>equilibrium dialysis, Slide-A-Lyzer 10 kDa MWCO, 48 h at 50 rpm; single-site Langmuir fit to the specific binding curve; LC-MS/MS</t>
-        </is>
-      </c>
-      <c r="F49" t="n">
-        <v>2</v>
-      </c>
+          <t>microscale thermophoresis (MST), Monolith NT.115, 25 C</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>0.0625-2 uM (0.0625, 0.125, 0.25, 0.5, 1, 2)</t>
-        </is>
-      </c>
-      <c r="H49" t="n">
-        <v>1</v>
-      </c>
+          <t>MST titration series</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
-          <t>1.0 uM</t>
-        </is>
-      </c>
-      <c r="J49" t="n">
-        <v>2</v>
-      </c>
+          <t>see Text S7</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
-          <t>computed from the two concentrations</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr"/>
+          <t>neither both concentrations nor a stated ratio</t>
+        </is>
+      </c>
+      <c r="L49" t="n">
+        <v>25</v>
+      </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>room temperature (not stated more precisely)</t>
+          <t>25</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr">
         <is>
-          <t>10 mM ammonium acetate, pH 7.4</t>
+          <t>Tris-HCl</t>
         </is>
       </c>
       <c r="P49" t="n">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="Q49" t="n">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="R49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>C106</t>
+          <t>C108</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Chen 2025</t>
+          <t>Jia 2022</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>not applicable (synthetic phosphatidylcholine)</t>
+          <t>human</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>phospholipid bilayer membrane (solid-supported, SSLM)</t>
+          <t>liver fatty acid-binding protein (hL-FABP)</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>solid-supported lipid membrane (SSLM; TRANSIL Membrane Affinity Kit, phosphatidylcholine beads), 4 h at 50 rpm; aqueous phase by LC-MS/MS and membrane concentration by difference</t>
+          <t>microscale thermophoresis (MST), Monolith NT.115; Kd over 21-40 C fitted by the van't Hoff equation, the value here being 25 C</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>one spike level per PFAS group</t>
+          <t>MST titration series</t>
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
-          <t>0.067-2.166 uL lipid per vial (6-point series)</t>
+          <t>see Text S7</t>
         </is>
       </c>
       <c r="J50" t="inlineStr"/>
@@ -43462,37 +43462,39 @@
           <t>neither both concentrations nor a stated ratio</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr"/>
+      <c r="L50" t="n">
+        <v>25</v>
+      </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>room temperature (not stated more precisely)</t>
+          <t>25</t>
         </is>
       </c>
       <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr">
         <is>
-          <t>10 mM ammonium acetate, pH 7.0</t>
+          <t>Tris-HCl</t>
         </is>
       </c>
       <c r="P50" t="n">
-        <v>60</v>
+        <v>11</v>
       </c>
       <c r="Q50" t="n">
-        <v>60</v>
+        <v>11</v>
       </c>
       <c r="R50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>C119</t>
+          <t>C109</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Muensterman 2026</t>
+          <t>Chen 2025</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -43502,51 +43504,55 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>human serum albumin (HSA), immobilised stationary phase</t>
+          <t>human serum albumin (HSA)</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>biomimetic chromatography, rapid-gradient; retention on a protein- or phospholipid-coated column calibrated against pharmaceuticals of known partition coefficient (SURROGATE, not an equilibrium measurement)</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr"/>
+          <t>equilibrium dialysis, Slide-A-Lyzer 10 kDa MWCO, 48 h at 50 rpm; single-site Langmuir fit to the specific binding curve; LC-MS/MS</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>2</v>
+      </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>10 uL injection of a standard</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr"/>
+          <t>0.0625-2 uM (0.0625, 0.125, 0.25, 0.5, 1, 2)</t>
+        </is>
+      </c>
+      <c r="H51" t="n">
+        <v>1</v>
+      </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>immobilised stationary phase</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr"/>
+          <t>1.0 uM</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>2</v>
+      </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>neither both concentrations nor a stated ratio</t>
-        </is>
-      </c>
-      <c r="L51" t="n">
-        <v>25</v>
-      </c>
+          <t>computed from the two concentrations</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>room temperature (not stated more precisely)</t>
         </is>
       </c>
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr">
         <is>
-          <t>pH 7.4 mobile phase; isopropanol gradient 0-30%</t>
+          <t>10 mM ammonium acetate, pH 7.4</t>
         </is>
       </c>
       <c r="P51" t="n">
-        <v>82</v>
+        <v>60</v>
       </c>
       <c r="Q51" t="n">
-        <v>82</v>
+        <v>60</v>
       </c>
       <c r="R51" t="n">
         <v>2</v>
@@ -43555,39 +43561,39 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>C120</t>
+          <t>C110</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Muensterman 2026</t>
+          <t>Chen 2025</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>not applicable (synthetic phospholipid)</t>
+          <t>not applicable (synthetic phosphatidylcholine)</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>immobilised artificial membrane (IAM, phospholipid stationary phase)</t>
+          <t>phospholipid bilayer membrane (solid-supported, SSLM)</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>biomimetic chromatography, rapid-gradient; retention on a protein- or phospholipid-coated column calibrated against pharmaceuticals of known partition coefficient (SURROGATE, not an equilibrium measurement)</t>
+          <t>solid-supported lipid membrane (SSLM; TRANSIL Membrane Affinity Kit, phosphatidylcholine beads), 4 h at 50 rpm; aqueous phase by LC-MS/MS and membrane concentration by difference</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>10 uL injection of a standard</t>
+          <t>one spike level per PFAS group</t>
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
-          <t>immobilised stationary phase</t>
+          <t>0.067-2.166 uL lipid per vial (6-point series)</t>
         </is>
       </c>
       <c r="J52" t="inlineStr"/>
@@ -43596,25 +43602,23 @@
           <t>neither both concentrations nor a stated ratio</t>
         </is>
       </c>
-      <c r="L52" t="n">
-        <v>25</v>
-      </c>
+      <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>room temperature (not stated more precisely)</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr">
         <is>
-          <t>pH 7.4 mobile phase; isopropanol gradient 0-30%</t>
+          <t>10 mM ammonium acetate, pH 7.0</t>
         </is>
       </c>
       <c r="P52" t="n">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="Q52" t="n">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="R52" t="n">
         <v>2</v>
@@ -43623,12 +43627,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>C149</t>
+          <t>C123</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Starnes 2025</t>
+          <t>Muensterman 2026</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -43638,26 +43642,24 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>human serum albumin (HSA)</t>
+          <t>human serum albumin (HSA), immobilised stationary phase</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>differential scanning fluorimetry (DSF), GloMelt dye with ROX reference; Ka from the concentration-response of dTm by nonlinear regression</t>
+          <t>biomimetic chromatography, rapid-gradient; retention on a protein- or phospholipid-coated column calibrated against pharmaceuticals of known partition coefficient (SURROGATE, not an equilibrium measurement)</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>concentration-response series per chemical (Table S3, not extracted); positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
-        </is>
-      </c>
-      <c r="H53" t="n">
-        <v>130</v>
-      </c>
+          <t>10 uL injection of a standard</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
-          <t>0.13 mM</t>
+          <t>immobilised stationary phase</t>
         </is>
       </c>
       <c r="J53" t="inlineStr"/>
@@ -43666,32 +43668,100 @@
           <t>neither both concentrations nor a stated ratio</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr"/>
+      <c r="L53" t="n">
+        <v>25</v>
+      </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>thermal ramp - Ka is an apparent affinity at the melting transition, not a 37 C equilibrium constant</t>
-        </is>
-      </c>
-      <c r="N53" t="n">
-        <v>140</v>
-      </c>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr">
         <is>
-          <t>HEPES-buffered saline: 140 mM NaCl, 50 mM HEPES, 0.38 mM Na2HPO4, pH 7.4</t>
+          <t>pH 7.4 mobile phase; isopropanol gradient 0-30%</t>
         </is>
       </c>
       <c r="P53" t="n">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="Q53" t="n">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="R53" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>C124</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Muensterman 2026</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>not applicable (synthetic phospholipid)</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>immobilised artificial membrane (IAM, phospholipid stationary phase)</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>biomimetic chromatography, rapid-gradient; retention on a protein- or phospholipid-coated column calibrated against pharmaceuticals of known partition coefficient (SURROGATE, not an equilibrium measurement)</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>10 uL injection of a standard</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>immobilised stationary phase</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>neither both concentrations nor a stated ratio</t>
+        </is>
+      </c>
+      <c r="L54" t="n">
+        <v>25</v>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>pH 7.4 mobile phase; isopropanol gradient 0-30%</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>83</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>83</v>
+      </c>
+      <c r="R54" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R53"/>
+  <autoFilter ref="A1:R54"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -43725,7 +43795,7 @@
     <col width="19" customWidth="1" min="18" max="18"/>
     <col width="19" customWidth="1" min="19" max="19"/>
     <col width="23" customWidth="1" min="20" max="20"/>
-    <col width="19" customWidth="1" min="21" max="21"/>
+    <col width="24" customWidth="1" min="21" max="21"/>
     <col width="44" customWidth="1" min="22" max="22"/>
     <col width="17" customWidth="1" min="23" max="23"/>
     <col width="24" customWidth="1" min="24" max="24"/>
@@ -65994,7 +66064,7 @@
       <c r="T213" t="inlineStr"/>
       <c r="U213" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>unknown (not reported)</t>
         </is>
       </c>
       <c r="V213" t="inlineStr">
@@ -66013,7 +66083,7 @@
       <c r="Y213" t="inlineStr"/>
       <c r="Z213" t="inlineStr">
         <is>
-          <t>concentration-response series per chemical (Table S3, not extracted); positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
+          <t>not reported by the paper; stocks serially diluted to unstated working concentrations, and Table S3 gives the stock concentration and solvent only; positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
         </is>
       </c>
       <c r="AA213" t="inlineStr"/>
@@ -66090,7 +66160,7 @@
       <c r="T214" t="inlineStr"/>
       <c r="U214" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>unknown (not reported)</t>
         </is>
       </c>
       <c r="V214" t="inlineStr">
@@ -66109,7 +66179,7 @@
       <c r="Y214" t="inlineStr"/>
       <c r="Z214" t="inlineStr">
         <is>
-          <t>concentration-response series per chemical (Table S3, not extracted); positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
+          <t>not reported by the paper; stocks serially diluted to unstated working concentrations, and Table S3 gives the stock concentration and solvent only; positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
         </is>
       </c>
       <c r="AA214" t="inlineStr"/>
@@ -66186,7 +66256,7 @@
       <c r="T215" t="inlineStr"/>
       <c r="U215" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>unknown (not reported)</t>
         </is>
       </c>
       <c r="V215" t="inlineStr">
@@ -66205,7 +66275,7 @@
       <c r="Y215" t="inlineStr"/>
       <c r="Z215" t="inlineStr">
         <is>
-          <t>concentration-response series per chemical (Table S3, not extracted); positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
+          <t>not reported by the paper; stocks serially diluted to unstated working concentrations, and Table S3 gives the stock concentration and solvent only; positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
         </is>
       </c>
       <c r="AA215" t="inlineStr"/>
@@ -66282,7 +66352,7 @@
       <c r="T216" t="inlineStr"/>
       <c r="U216" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>unknown (not reported)</t>
         </is>
       </c>
       <c r="V216" t="inlineStr">
@@ -66301,7 +66371,7 @@
       <c r="Y216" t="inlineStr"/>
       <c r="Z216" t="inlineStr">
         <is>
-          <t>concentration-response series per chemical (Table S3, not extracted); positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
+          <t>not reported by the paper; stocks serially diluted to unstated working concentrations, and Table S3 gives the stock concentration and solvent only; positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
         </is>
       </c>
       <c r="AA216" t="inlineStr"/>
@@ -66378,7 +66448,7 @@
       <c r="T217" t="inlineStr"/>
       <c r="U217" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>unknown (not reported)</t>
         </is>
       </c>
       <c r="V217" t="inlineStr">
@@ -66397,7 +66467,7 @@
       <c r="Y217" t="inlineStr"/>
       <c r="Z217" t="inlineStr">
         <is>
-          <t>concentration-response series per chemical (Table S3, not extracted); positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
+          <t>not reported by the paper; stocks serially diluted to unstated working concentrations, and Table S3 gives the stock concentration and solvent only; positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
         </is>
       </c>
       <c r="AA217" t="inlineStr"/>
@@ -66474,7 +66544,7 @@
       <c r="T218" t="inlineStr"/>
       <c r="U218" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>unknown (not reported)</t>
         </is>
       </c>
       <c r="V218" t="inlineStr">
@@ -66493,7 +66563,7 @@
       <c r="Y218" t="inlineStr"/>
       <c r="Z218" t="inlineStr">
         <is>
-          <t>concentration-response series per chemical (Table S3, not extracted); positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
+          <t>not reported by the paper; stocks serially diluted to unstated working concentrations, and Table S3 gives the stock concentration and solvent only; positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
         </is>
       </c>
       <c r="AA218" t="inlineStr"/>
@@ -66570,7 +66640,7 @@
       <c r="T219" t="inlineStr"/>
       <c r="U219" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>unknown (not reported)</t>
         </is>
       </c>
       <c r="V219" t="inlineStr">
@@ -66589,7 +66659,7 @@
       <c r="Y219" t="inlineStr"/>
       <c r="Z219" t="inlineStr">
         <is>
-          <t>concentration-response series per chemical (Table S3, not extracted); positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
+          <t>not reported by the paper; stocks serially diluted to unstated working concentrations, and Table S3 gives the stock concentration and solvent only; positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
         </is>
       </c>
       <c r="AA219" t="inlineStr"/>
@@ -66666,7 +66736,7 @@
       <c r="T220" t="inlineStr"/>
       <c r="U220" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>unknown (not reported)</t>
         </is>
       </c>
       <c r="V220" t="inlineStr">
@@ -66685,7 +66755,7 @@
       <c r="Y220" t="inlineStr"/>
       <c r="Z220" t="inlineStr">
         <is>
-          <t>concentration-response series per chemical (Table S3, not extracted); positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
+          <t>not reported by the paper; stocks serially diluted to unstated working concentrations, and Table S3 gives the stock concentration and solvent only; positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
         </is>
       </c>
       <c r="AA220" t="inlineStr"/>
@@ -66762,7 +66832,7 @@
       <c r="T221" t="inlineStr"/>
       <c r="U221" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>unknown (not reported)</t>
         </is>
       </c>
       <c r="V221" t="inlineStr">
@@ -66781,7 +66851,7 @@
       <c r="Y221" t="inlineStr"/>
       <c r="Z221" t="inlineStr">
         <is>
-          <t>concentration-response series per chemical (Table S3, not extracted); positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
+          <t>not reported by the paper; stocks serially diluted to unstated working concentrations, and Table S3 gives the stock concentration and solvent only; positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
         </is>
       </c>
       <c r="AA221" t="inlineStr"/>
@@ -66858,7 +66928,7 @@
       <c r="T222" t="inlineStr"/>
       <c r="U222" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>unknown (not reported)</t>
         </is>
       </c>
       <c r="V222" t="inlineStr">
@@ -66877,7 +66947,7 @@
       <c r="Y222" t="inlineStr"/>
       <c r="Z222" t="inlineStr">
         <is>
-          <t>concentration-response series per chemical (Table S3, not extracted); positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
+          <t>not reported by the paper; stocks serially diluted to unstated working concentrations, and Table S3 gives the stock concentration and solvent only; positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
         </is>
       </c>
       <c r="AA222" t="inlineStr"/>
@@ -66954,7 +67024,7 @@
       <c r="T223" t="inlineStr"/>
       <c r="U223" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>unknown (not reported)</t>
         </is>
       </c>
       <c r="V223" t="inlineStr">
@@ -66973,7 +67043,7 @@
       <c r="Y223" t="inlineStr"/>
       <c r="Z223" t="inlineStr">
         <is>
-          <t>concentration-response series per chemical (Table S3, not extracted); positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
+          <t>not reported by the paper; stocks serially diluted to unstated working concentrations, and Table S3 gives the stock concentration and solvent only; positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
         </is>
       </c>
       <c r="AA223" t="inlineStr"/>
@@ -67050,7 +67120,7 @@
       <c r="T224" t="inlineStr"/>
       <c r="U224" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>unknown (not reported)</t>
         </is>
       </c>
       <c r="V224" t="inlineStr">
@@ -67069,7 +67139,7 @@
       <c r="Y224" t="inlineStr"/>
       <c r="Z224" t="inlineStr">
         <is>
-          <t>concentration-response series per chemical (Table S3, not extracted); positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
+          <t>not reported by the paper; stocks serially diluted to unstated working concentrations, and Table S3 gives the stock concentration and solvent only; positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
         </is>
       </c>
       <c r="AA224" t="inlineStr"/>
@@ -67146,7 +67216,7 @@
       <c r="T225" t="inlineStr"/>
       <c r="U225" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>unknown (not reported)</t>
         </is>
       </c>
       <c r="V225" t="inlineStr">
@@ -67165,7 +67235,7 @@
       <c r="Y225" t="inlineStr"/>
       <c r="Z225" t="inlineStr">
         <is>
-          <t>concentration-response series per chemical (Table S3, not extracted); positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
+          <t>not reported by the paper; stocks serially diluted to unstated working concentrations, and Table S3 gives the stock concentration and solvent only; positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
         </is>
       </c>
       <c r="AA225" t="inlineStr"/>
@@ -67242,7 +67312,7 @@
       <c r="T226" t="inlineStr"/>
       <c r="U226" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>unknown (not reported)</t>
         </is>
       </c>
       <c r="V226" t="inlineStr">
@@ -67261,7 +67331,7 @@
       <c r="Y226" t="inlineStr"/>
       <c r="Z226" t="inlineStr">
         <is>
-          <t>concentration-response series per chemical (Table S3, not extracted); positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
+          <t>not reported by the paper; stocks serially diluted to unstated working concentrations, and Table S3 gives the stock concentration and solvent only; positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
         </is>
       </c>
       <c r="AA226" t="inlineStr"/>
@@ -67338,7 +67408,7 @@
       <c r="T227" t="inlineStr"/>
       <c r="U227" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>unknown (not reported)</t>
         </is>
       </c>
       <c r="V227" t="inlineStr">
@@ -67357,7 +67427,7 @@
       <c r="Y227" t="inlineStr"/>
       <c r="Z227" t="inlineStr">
         <is>
-          <t>concentration-response series per chemical (Table S3, not extracted); positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
+          <t>not reported by the paper; stocks serially diluted to unstated working concentrations, and Table S3 gives the stock concentration and solvent only; positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
         </is>
       </c>
       <c r="AA227" t="inlineStr"/>
@@ -67434,7 +67504,7 @@
       <c r="T228" t="inlineStr"/>
       <c r="U228" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>unknown (not reported)</t>
         </is>
       </c>
       <c r="V228" t="inlineStr">
@@ -67453,7 +67523,7 @@
       <c r="Y228" t="inlineStr"/>
       <c r="Z228" t="inlineStr">
         <is>
-          <t>concentration-response series per chemical (Table S3, not extracted); positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
+          <t>not reported by the paper; stocks serially diluted to unstated working concentrations, and Table S3 gives the stock concentration and solvent only; positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
         </is>
       </c>
       <c r="AA228" t="inlineStr"/>
@@ -67530,7 +67600,7 @@
       <c r="T229" t="inlineStr"/>
       <c r="U229" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>unknown (not reported)</t>
         </is>
       </c>
       <c r="V229" t="inlineStr">
@@ -67549,7 +67619,7 @@
       <c r="Y229" t="inlineStr"/>
       <c r="Z229" t="inlineStr">
         <is>
-          <t>concentration-response series per chemical (Table S3, not extracted); positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
+          <t>not reported by the paper; stocks serially diluted to unstated working concentrations, and Table S3 gives the stock concentration and solvent only; positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
         </is>
       </c>
       <c r="AA229" t="inlineStr"/>
@@ -67626,7 +67696,7 @@
       <c r="T230" t="inlineStr"/>
       <c r="U230" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>unknown (not reported)</t>
         </is>
       </c>
       <c r="V230" t="inlineStr">
@@ -67645,7 +67715,7 @@
       <c r="Y230" t="inlineStr"/>
       <c r="Z230" t="inlineStr">
         <is>
-          <t>concentration-response series per chemical (Table S3, not extracted); positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
+          <t>not reported by the paper; stocks serially diluted to unstated working concentrations, and Table S3 gives the stock concentration and solvent only; positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
         </is>
       </c>
       <c r="AA230" t="inlineStr"/>
@@ -67722,7 +67792,7 @@
       <c r="T231" t="inlineStr"/>
       <c r="U231" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>unknown (not reported)</t>
         </is>
       </c>
       <c r="V231" t="inlineStr">
@@ -67741,7 +67811,7 @@
       <c r="Y231" t="inlineStr"/>
       <c r="Z231" t="inlineStr">
         <is>
-          <t>concentration-response series per chemical (Table S3, not extracted); positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
+          <t>not reported by the paper; stocks serially diluted to unstated working concentrations, and Table S3 gives the stock concentration and solvent only; positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
         </is>
       </c>
       <c r="AA231" t="inlineStr"/>
@@ -67818,7 +67888,7 @@
       <c r="T232" t="inlineStr"/>
       <c r="U232" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>unknown (not reported)</t>
         </is>
       </c>
       <c r="V232" t="inlineStr">
@@ -67837,7 +67907,7 @@
       <c r="Y232" t="inlineStr"/>
       <c r="Z232" t="inlineStr">
         <is>
-          <t>concentration-response series per chemical (Table S3, not extracted); positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
+          <t>not reported by the paper; stocks serially diluted to unstated working concentrations, and Table S3 gives the stock concentration and solvent only; positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
         </is>
       </c>
       <c r="AA232" t="inlineStr"/>
@@ -67914,7 +67984,7 @@
       <c r="T233" t="inlineStr"/>
       <c r="U233" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>unknown (not reported)</t>
         </is>
       </c>
       <c r="V233" t="inlineStr">
@@ -67933,7 +68003,7 @@
       <c r="Y233" t="inlineStr"/>
       <c r="Z233" t="inlineStr">
         <is>
-          <t>concentration-response series per chemical (Table S3, not extracted); positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
+          <t>not reported by the paper; stocks serially diluted to unstated working concentrations, and Table S3 gives the stock concentration and solvent only; positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
         </is>
       </c>
       <c r="AA233" t="inlineStr"/>
@@ -68010,7 +68080,7 @@
       <c r="T234" t="inlineStr"/>
       <c r="U234" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>unknown (not reported)</t>
         </is>
       </c>
       <c r="V234" t="inlineStr">
@@ -68029,7 +68099,7 @@
       <c r="Y234" t="inlineStr"/>
       <c r="Z234" t="inlineStr">
         <is>
-          <t>concentration-response series per chemical (Table S3, not extracted); positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
+          <t>not reported by the paper; stocks serially diluted to unstated working concentrations, and Table S3 gives the stock concentration and solvent only; positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
         </is>
       </c>
       <c r="AA234" t="inlineStr"/>
@@ -68106,7 +68176,7 @@
       <c r="T235" t="inlineStr"/>
       <c r="U235" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>unknown (not reported)</t>
         </is>
       </c>
       <c r="V235" t="inlineStr">
@@ -68125,7 +68195,7 @@
       <c r="Y235" t="inlineStr"/>
       <c r="Z235" t="inlineStr">
         <is>
-          <t>concentration-response series per chemical (Table S3, not extracted); positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
+          <t>not reported by the paper; stocks serially diluted to unstated working concentrations, and Table S3 gives the stock concentration and solvent only; positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
         </is>
       </c>
       <c r="AA235" t="inlineStr"/>
@@ -68202,7 +68272,7 @@
       <c r="T236" t="inlineStr"/>
       <c r="U236" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>unknown (not reported)</t>
         </is>
       </c>
       <c r="V236" t="inlineStr">
@@ -68221,7 +68291,7 @@
       <c r="Y236" t="inlineStr"/>
       <c r="Z236" t="inlineStr">
         <is>
-          <t>concentration-response series per chemical (Table S3, not extracted); positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
+          <t>not reported by the paper; stocks serially diluted to unstated working concentrations, and Table S3 gives the stock concentration and solvent only; positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
         </is>
       </c>
       <c r="AA236" t="inlineStr"/>
@@ -68298,7 +68368,7 @@
       <c r="T237" t="inlineStr"/>
       <c r="U237" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>unknown (not reported)</t>
         </is>
       </c>
       <c r="V237" t="inlineStr">
@@ -68317,7 +68387,7 @@
       <c r="Y237" t="inlineStr"/>
       <c r="Z237" t="inlineStr">
         <is>
-          <t>concentration-response series per chemical (Table S3, not extracted); positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
+          <t>not reported by the paper; stocks serially diluted to unstated working concentrations, and Table S3 gives the stock concentration and solvent only; positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
         </is>
       </c>
       <c r="AA237" t="inlineStr"/>
@@ -68394,7 +68464,7 @@
       <c r="T238" t="inlineStr"/>
       <c r="U238" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>unknown (not reported)</t>
         </is>
       </c>
       <c r="V238" t="inlineStr">
@@ -68413,7 +68483,7 @@
       <c r="Y238" t="inlineStr"/>
       <c r="Z238" t="inlineStr">
         <is>
-          <t>concentration-response series per chemical (Table S3, not extracted); positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
+          <t>not reported by the paper; stocks serially diluted to unstated working concentrations, and Table S3 gives the stock concentration and solvent only; positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
         </is>
       </c>
       <c r="AA238" t="inlineStr"/>
@@ -68490,7 +68560,7 @@
       <c r="T239" t="inlineStr"/>
       <c r="U239" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>unknown (not reported)</t>
         </is>
       </c>
       <c r="V239" t="inlineStr">
@@ -68509,7 +68579,7 @@
       <c r="Y239" t="inlineStr"/>
       <c r="Z239" t="inlineStr">
         <is>
-          <t>concentration-response series per chemical (Table S3, not extracted); positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
+          <t>not reported by the paper; stocks serially diluted to unstated working concentrations, and Table S3 gives the stock concentration and solvent only; positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
         </is>
       </c>
       <c r="AA239" t="inlineStr"/>
@@ -68586,7 +68656,7 @@
       <c r="T240" t="inlineStr"/>
       <c r="U240" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>unknown (not reported)</t>
         </is>
       </c>
       <c r="V240" t="inlineStr">
@@ -68605,7 +68675,7 @@
       <c r="Y240" t="inlineStr"/>
       <c r="Z240" t="inlineStr">
         <is>
-          <t>concentration-response series per chemical (Table S3, not extracted); positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
+          <t>not reported by the paper; stocks serially diluted to unstated working concentrations, and Table S3 gives the stock concentration and solvent only; positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
         </is>
       </c>
       <c r="AA240" t="inlineStr"/>
@@ -68682,7 +68752,7 @@
       <c r="T241" t="inlineStr"/>
       <c r="U241" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>unknown (not reported)</t>
         </is>
       </c>
       <c r="V241" t="inlineStr">
@@ -68701,7 +68771,7 @@
       <c r="Y241" t="inlineStr"/>
       <c r="Z241" t="inlineStr">
         <is>
-          <t>concentration-response series per chemical (Table S3, not extracted); positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
+          <t>not reported by the paper; stocks serially diluted to unstated working concentrations, and Table S3 gives the stock concentration and solvent only; positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
         </is>
       </c>
       <c r="AA241" t="inlineStr"/>
@@ -68778,7 +68848,7 @@
       <c r="T242" t="inlineStr"/>
       <c r="U242" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>unknown (not reported)</t>
         </is>
       </c>
       <c r="V242" t="inlineStr">
@@ -68797,7 +68867,7 @@
       <c r="Y242" t="inlineStr"/>
       <c r="Z242" t="inlineStr">
         <is>
-          <t>concentration-response series per chemical (Table S3, not extracted); positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
+          <t>not reported by the paper; stocks serially diluted to unstated working concentrations, and Table S3 gives the stock concentration and solvent only; positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
         </is>
       </c>
       <c r="AA242" t="inlineStr"/>
@@ -68874,7 +68944,7 @@
       <c r="T243" t="inlineStr"/>
       <c r="U243" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>unknown (not reported)</t>
         </is>
       </c>
       <c r="V243" t="inlineStr">
@@ -68893,7 +68963,7 @@
       <c r="Y243" t="inlineStr"/>
       <c r="Z243" t="inlineStr">
         <is>
-          <t>concentration-response series per chemical (Table S3, not extracted); positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
+          <t>not reported by the paper; stocks serially diluted to unstated working concentrations, and Table S3 gives the stock concentration and solvent only; positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
         </is>
       </c>
       <c r="AA243" t="inlineStr"/>
@@ -68970,7 +69040,7 @@
       <c r="T244" t="inlineStr"/>
       <c r="U244" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>unknown (not reported)</t>
         </is>
       </c>
       <c r="V244" t="inlineStr">
@@ -68989,7 +69059,7 @@
       <c r="Y244" t="inlineStr"/>
       <c r="Z244" t="inlineStr">
         <is>
-          <t>concentration-response series per chemical (Table S3, not extracted); positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
+          <t>not reported by the paper; stocks serially diluted to unstated working concentrations, and Table S3 gives the stock concentration and solvent only; positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
         </is>
       </c>
       <c r="AA244" t="inlineStr"/>
@@ -69066,7 +69136,7 @@
       <c r="T245" t="inlineStr"/>
       <c r="U245" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>unknown (not reported)</t>
         </is>
       </c>
       <c r="V245" t="inlineStr">
@@ -69085,7 +69155,7 @@
       <c r="Y245" t="inlineStr"/>
       <c r="Z245" t="inlineStr">
         <is>
-          <t>concentration-response series per chemical (Table S3, not extracted); positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
+          <t>not reported by the paper; stocks serially diluted to unstated working concentrations, and Table S3 gives the stock concentration and solvent only; positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
         </is>
       </c>
       <c r="AA245" t="inlineStr"/>
@@ -69162,7 +69232,7 @@
       <c r="T246" t="inlineStr"/>
       <c r="U246" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>unknown (not reported)</t>
         </is>
       </c>
       <c r="V246" t="inlineStr">
@@ -69181,7 +69251,7 @@
       <c r="Y246" t="inlineStr"/>
       <c r="Z246" t="inlineStr">
         <is>
-          <t>concentration-response series per chemical (Table S3, not extracted); positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
+          <t>not reported by the paper; stocks serially diluted to unstated working concentrations, and Table S3 gives the stock concentration and solvent only; positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
         </is>
       </c>
       <c r="AA246" t="inlineStr"/>
@@ -69258,7 +69328,7 @@
       <c r="T247" t="inlineStr"/>
       <c r="U247" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>unknown (not reported)</t>
         </is>
       </c>
       <c r="V247" t="inlineStr">
@@ -69277,7 +69347,7 @@
       <c r="Y247" t="inlineStr"/>
       <c r="Z247" t="inlineStr">
         <is>
-          <t>concentration-response series per chemical (Table S3, not extracted); positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
+          <t>not reported by the paper; stocks serially diluted to unstated working concentrations, and Table S3 gives the stock concentration and solvent only; positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
         </is>
       </c>
       <c r="AA247" t="inlineStr"/>
@@ -69354,7 +69424,7 @@
       <c r="T248" t="inlineStr"/>
       <c r="U248" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>unknown (not reported)</t>
         </is>
       </c>
       <c r="V248" t="inlineStr">
@@ -69373,7 +69443,7 @@
       <c r="Y248" t="inlineStr"/>
       <c r="Z248" t="inlineStr">
         <is>
-          <t>concentration-response series per chemical (Table S3, not extracted); positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
+          <t>not reported by the paper; stocks serially diluted to unstated working concentrations, and Table S3 gives the stock concentration and solvent only; positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
         </is>
       </c>
       <c r="AA248" t="inlineStr"/>
@@ -69450,7 +69520,7 @@
       <c r="T249" t="inlineStr"/>
       <c r="U249" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>unknown (not reported)</t>
         </is>
       </c>
       <c r="V249" t="inlineStr">
@@ -69469,7 +69539,7 @@
       <c r="Y249" t="inlineStr"/>
       <c r="Z249" t="inlineStr">
         <is>
-          <t>concentration-response series per chemical (Table S3, not extracted); positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
+          <t>not reported by the paper; stocks serially diluted to unstated working concentrations, and Table S3 gives the stock concentration and solvent only; positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
         </is>
       </c>
       <c r="AA249" t="inlineStr"/>
@@ -69546,7 +69616,7 @@
       <c r="T250" t="inlineStr"/>
       <c r="U250" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>unknown (not reported)</t>
         </is>
       </c>
       <c r="V250" t="inlineStr">
@@ -69565,7 +69635,7 @@
       <c r="Y250" t="inlineStr"/>
       <c r="Z250" t="inlineStr">
         <is>
-          <t>concentration-response series per chemical (Table S3, not extracted); positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
+          <t>not reported by the paper; stocks serially diluted to unstated working concentrations, and Table S3 gives the stock concentration and solvent only; positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
         </is>
       </c>
       <c r="AA250" t="inlineStr"/>
@@ -69642,7 +69712,7 @@
       <c r="T251" t="inlineStr"/>
       <c r="U251" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>unknown (not reported)</t>
         </is>
       </c>
       <c r="V251" t="inlineStr">
@@ -69661,7 +69731,7 @@
       <c r="Y251" t="inlineStr"/>
       <c r="Z251" t="inlineStr">
         <is>
-          <t>concentration-response series per chemical (Table S3, not extracted); positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
+          <t>not reported by the paper; stocks serially diluted to unstated working concentrations, and Table S3 gives the stock concentration and solvent only; positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
         </is>
       </c>
       <c r="AA251" t="inlineStr"/>
@@ -69738,7 +69808,7 @@
       <c r="T252" t="inlineStr"/>
       <c r="U252" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>unknown (not reported)</t>
         </is>
       </c>
       <c r="V252" t="inlineStr">
@@ -69757,7 +69827,7 @@
       <c r="Y252" t="inlineStr"/>
       <c r="Z252" t="inlineStr">
         <is>
-          <t>concentration-response series per chemical (Table S3, not extracted); positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
+          <t>not reported by the paper; stocks serially diluted to unstated working concentrations, and Table S3 gives the stock concentration and solvent only; positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
         </is>
       </c>
       <c r="AA252" t="inlineStr"/>
@@ -69834,7 +69904,7 @@
       <c r="T253" t="inlineStr"/>
       <c r="U253" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>unknown (not reported)</t>
         </is>
       </c>
       <c r="V253" t="inlineStr">
@@ -69853,7 +69923,7 @@
       <c r="Y253" t="inlineStr"/>
       <c r="Z253" t="inlineStr">
         <is>
-          <t>concentration-response series per chemical (Table S3, not extracted); positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
+          <t>not reported by the paper; stocks serially diluted to unstated working concentrations, and Table S3 gives the stock concentration and solvent only; positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
         </is>
       </c>
       <c r="AA253" t="inlineStr"/>
@@ -69930,7 +70000,7 @@
       <c r="T254" t="inlineStr"/>
       <c r="U254" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>unknown (not reported)</t>
         </is>
       </c>
       <c r="V254" t="inlineStr">
@@ -69949,7 +70019,7 @@
       <c r="Y254" t="inlineStr"/>
       <c r="Z254" t="inlineStr">
         <is>
-          <t>concentration-response series per chemical (Table S3, not extracted); positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
+          <t>not reported by the paper; stocks serially diluted to unstated working concentrations, and Table S3 gives the stock concentration and solvent only; positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
         </is>
       </c>
       <c r="AA254" t="inlineStr"/>
@@ -70026,7 +70096,7 @@
       <c r="T255" t="inlineStr"/>
       <c r="U255" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>unknown (not reported)</t>
         </is>
       </c>
       <c r="V255" t="inlineStr">
@@ -70045,7 +70115,7 @@
       <c r="Y255" t="inlineStr"/>
       <c r="Z255" t="inlineStr">
         <is>
-          <t>concentration-response series per chemical (Table S3, not extracted); positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
+          <t>not reported by the paper; stocks serially diluted to unstated working concentrations, and Table S3 gives the stock concentration and solvent only; positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
         </is>
       </c>
       <c r="AA255" t="inlineStr"/>
@@ -70122,7 +70192,7 @@
       <c r="T256" t="inlineStr"/>
       <c r="U256" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>unknown (not reported)</t>
         </is>
       </c>
       <c r="V256" t="inlineStr">
@@ -70141,7 +70211,7 @@
       <c r="Y256" t="inlineStr"/>
       <c r="Z256" t="inlineStr">
         <is>
-          <t>concentration-response series per chemical (Table S3, not extracted); positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
+          <t>not reported by the paper; stocks serially diluted to unstated working concentrations, and Table S3 gives the stock concentration and solvent only; positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
         </is>
       </c>
       <c r="AA256" t="inlineStr"/>
@@ -70218,7 +70288,7 @@
       <c r="T257" t="inlineStr"/>
       <c r="U257" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>unknown (not reported)</t>
         </is>
       </c>
       <c r="V257" t="inlineStr">
@@ -70237,7 +70307,7 @@
       <c r="Y257" t="inlineStr"/>
       <c r="Z257" t="inlineStr">
         <is>
-          <t>concentration-response series per chemical (Table S3, not extracted); positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
+          <t>not reported by the paper; stocks serially diluted to unstated working concentrations, and Table S3 gives the stock concentration and solvent only; positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
         </is>
       </c>
       <c r="AA257" t="inlineStr"/>
@@ -70314,7 +70384,7 @@
       <c r="T258" t="inlineStr"/>
       <c r="U258" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>unknown (not reported)</t>
         </is>
       </c>
       <c r="V258" t="inlineStr">
@@ -70333,7 +70403,7 @@
       <c r="Y258" t="inlineStr"/>
       <c r="Z258" t="inlineStr">
         <is>
-          <t>concentration-response series per chemical (Table S3, not extracted); positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
+          <t>not reported by the paper; stocks serially diluted to unstated working concentrations, and Table S3 gives the stock concentration and solvent only; positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
         </is>
       </c>
       <c r="AA258" t="inlineStr"/>
@@ -70410,7 +70480,7 @@
       <c r="T259" t="inlineStr"/>
       <c r="U259" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>unknown (not reported)</t>
         </is>
       </c>
       <c r="V259" t="inlineStr">
@@ -70429,7 +70499,7 @@
       <c r="Y259" t="inlineStr"/>
       <c r="Z259" t="inlineStr">
         <is>
-          <t>concentration-response series per chemical (Table S3, not extracted); positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
+          <t>not reported by the paper; stocks serially diluted to unstated working concentrations, and Table S3 gives the stock concentration and solvent only; positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
         </is>
       </c>
       <c r="AA259" t="inlineStr"/>
@@ -70506,7 +70576,7 @@
       <c r="T260" t="inlineStr"/>
       <c r="U260" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>unknown (not reported)</t>
         </is>
       </c>
       <c r="V260" t="inlineStr">
@@ -70525,7 +70595,7 @@
       <c r="Y260" t="inlineStr"/>
       <c r="Z260" t="inlineStr">
         <is>
-          <t>concentration-response series per chemical (Table S3, not extracted); positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
+          <t>not reported by the paper; stocks serially diluted to unstated working concentrations, and Table S3 gives the stock concentration and solvent only; positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
         </is>
       </c>
       <c r="AA260" t="inlineStr"/>
@@ -70602,7 +70672,7 @@
       <c r="T261" t="inlineStr"/>
       <c r="U261" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>unknown (not reported)</t>
         </is>
       </c>
       <c r="V261" t="inlineStr">
@@ -70621,7 +70691,7 @@
       <c r="Y261" t="inlineStr"/>
       <c r="Z261" t="inlineStr">
         <is>
-          <t>concentration-response series per chemical (Table S3, not extracted); positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
+          <t>not reported by the paper; stocks serially diluted to unstated working concentrations, and Table S3 gives the stock concentration and solvent only; positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
         </is>
       </c>
       <c r="AA261" t="inlineStr"/>
@@ -73094,7 +73164,7 @@
       <c r="T285" t="inlineStr"/>
       <c r="U285" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>unknown (not reported)</t>
         </is>
       </c>
       <c r="V285" t="inlineStr">
@@ -73113,7 +73183,7 @@
       <c r="Y285" t="inlineStr"/>
       <c r="Z285" t="inlineStr">
         <is>
-          <t>concentration-response series per chemical (Table S3, not extracted); positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
+          <t>not reported by the paper; stocks serially diluted to unstated working concentrations, and Table S3 gives the stock concentration and solvent only; positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
         </is>
       </c>
       <c r="AA285" t="inlineStr"/>
@@ -73186,7 +73256,7 @@
       <c r="T286" t="inlineStr"/>
       <c r="U286" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>unknown (not reported)</t>
         </is>
       </c>
       <c r="V286" t="inlineStr">
@@ -73205,7 +73275,7 @@
       <c r="Y286" t="inlineStr"/>
       <c r="Z286" t="inlineStr">
         <is>
-          <t>concentration-response series per chemical (Table S3, not extracted); positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
+          <t>not reported by the paper; stocks serially diluted to unstated working concentrations, and Table S3 gives the stock concentration and solvent only; positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
         </is>
       </c>
       <c r="AA286" t="inlineStr"/>
@@ -73278,7 +73348,7 @@
       <c r="T287" t="inlineStr"/>
       <c r="U287" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>unknown (not reported)</t>
         </is>
       </c>
       <c r="V287" t="inlineStr">
@@ -73297,7 +73367,7 @@
       <c r="Y287" t="inlineStr"/>
       <c r="Z287" t="inlineStr">
         <is>
-          <t>concentration-response series per chemical (Table S3, not extracted); positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
+          <t>not reported by the paper; stocks serially diluted to unstated working concentrations, and Table S3 gives the stock concentration and solvent only; positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
         </is>
       </c>
       <c r="AA287" t="inlineStr"/>
@@ -73370,7 +73440,7 @@
       <c r="T288" t="inlineStr"/>
       <c r="U288" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>unknown (not reported)</t>
         </is>
       </c>
       <c r="V288" t="inlineStr">
@@ -73389,7 +73459,7 @@
       <c r="Y288" t="inlineStr"/>
       <c r="Z288" t="inlineStr">
         <is>
-          <t>concentration-response series per chemical (Table S3, not extracted); positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
+          <t>not reported by the paper; stocks serially diluted to unstated working concentrations, and Table S3 gives the stock concentration and solvent only; positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
         </is>
       </c>
       <c r="AA288" t="inlineStr"/>
@@ -73462,7 +73532,7 @@
       <c r="T289" t="inlineStr"/>
       <c r="U289" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>unknown (not reported)</t>
         </is>
       </c>
       <c r="V289" t="inlineStr">
@@ -73481,7 +73551,7 @@
       <c r="Y289" t="inlineStr"/>
       <c r="Z289" t="inlineStr">
         <is>
-          <t>concentration-response series per chemical (Table S3, not extracted); positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
+          <t>not reported by the paper; stocks serially diluted to unstated working concentrations, and Table S3 gives the stock concentration and solvent only; positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
         </is>
       </c>
       <c r="AA289" t="inlineStr"/>
@@ -73554,7 +73624,7 @@
       <c r="T290" t="inlineStr"/>
       <c r="U290" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>unknown (not reported)</t>
         </is>
       </c>
       <c r="V290" t="inlineStr">
@@ -73573,7 +73643,7 @@
       <c r="Y290" t="inlineStr"/>
       <c r="Z290" t="inlineStr">
         <is>
-          <t>concentration-response series per chemical (Table S3, not extracted); positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
+          <t>not reported by the paper; stocks serially diluted to unstated working concentrations, and Table S3 gives the stock concentration and solvent only; positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
         </is>
       </c>
       <c r="AA290" t="inlineStr"/>
@@ -73646,7 +73716,7 @@
       <c r="T291" t="inlineStr"/>
       <c r="U291" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>unknown (not reported)</t>
         </is>
       </c>
       <c r="V291" t="inlineStr">
@@ -73665,7 +73735,7 @@
       <c r="Y291" t="inlineStr"/>
       <c r="Z291" t="inlineStr">
         <is>
-          <t>concentration-response series per chemical (Table S3, not extracted); positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
+          <t>not reported by the paper; stocks serially diluted to unstated working concentrations, and Table S3 gives the stock concentration and solvent only; positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
         </is>
       </c>
       <c r="AA291" t="inlineStr"/>
@@ -73738,7 +73808,7 @@
       <c r="T292" t="inlineStr"/>
       <c r="U292" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>unknown (not reported)</t>
         </is>
       </c>
       <c r="V292" t="inlineStr">
@@ -73757,7 +73827,7 @@
       <c r="Y292" t="inlineStr"/>
       <c r="Z292" t="inlineStr">
         <is>
-          <t>concentration-response series per chemical (Table S3, not extracted); positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
+          <t>not reported by the paper; stocks serially diluted to unstated working concentrations, and Table S3 gives the stock concentration and solvent only; positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
         </is>
       </c>
       <c r="AA292" t="inlineStr"/>
@@ -73830,7 +73900,7 @@
       <c r="T293" t="inlineStr"/>
       <c r="U293" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>unknown (not reported)</t>
         </is>
       </c>
       <c r="V293" t="inlineStr">
@@ -73849,7 +73919,7 @@
       <c r="Y293" t="inlineStr"/>
       <c r="Z293" t="inlineStr">
         <is>
-          <t>concentration-response series per chemical (Table S3, not extracted); positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
+          <t>not reported by the paper; stocks serially diluted to unstated working concentrations, and Table S3 gives the stock concentration and solvent only; positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
         </is>
       </c>
       <c r="AA293" t="inlineStr"/>
@@ -73922,7 +73992,7 @@
       <c r="T294" t="inlineStr"/>
       <c r="U294" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>unknown (not reported)</t>
         </is>
       </c>
       <c r="V294" t="inlineStr">
@@ -73941,7 +74011,7 @@
       <c r="Y294" t="inlineStr"/>
       <c r="Z294" t="inlineStr">
         <is>
-          <t>concentration-response series per chemical (Table S3, not extracted); positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
+          <t>not reported by the paper; stocks serially diluted to unstated working concentrations, and Table S3 gives the stock concentration and solvent only; positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
         </is>
       </c>
       <c r="AA294" t="inlineStr"/>
@@ -74014,7 +74084,7 @@
       <c r="T295" t="inlineStr"/>
       <c r="U295" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>unknown (not reported)</t>
         </is>
       </c>
       <c r="V295" t="inlineStr">
@@ -74033,7 +74103,7 @@
       <c r="Y295" t="inlineStr"/>
       <c r="Z295" t="inlineStr">
         <is>
-          <t>concentration-response series per chemical (Table S3, not extracted); positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
+          <t>not reported by the paper; stocks serially diluted to unstated working concentrations, and Table S3 gives the stock concentration and solvent only; positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
         </is>
       </c>
       <c r="AA295" t="inlineStr"/>
@@ -74106,7 +74176,7 @@
       <c r="T296" t="inlineStr"/>
       <c r="U296" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>unknown (not reported)</t>
         </is>
       </c>
       <c r="V296" t="inlineStr">
@@ -74125,7 +74195,7 @@
       <c r="Y296" t="inlineStr"/>
       <c r="Z296" t="inlineStr">
         <is>
-          <t>concentration-response series per chemical (Table S3, not extracted); positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
+          <t>not reported by the paper; stocks serially diluted to unstated working concentrations, and Table S3 gives the stock concentration and solvent only; positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
         </is>
       </c>
       <c r="AA296" t="inlineStr"/>
@@ -74198,7 +74268,7 @@
       <c r="T297" t="inlineStr"/>
       <c r="U297" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>unknown (not reported)</t>
         </is>
       </c>
       <c r="V297" t="inlineStr">
@@ -74217,7 +74287,7 @@
       <c r="Y297" t="inlineStr"/>
       <c r="Z297" t="inlineStr">
         <is>
-          <t>concentration-response series per chemical (Table S3, not extracted); positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
+          <t>not reported by the paper; stocks serially diluted to unstated working concentrations, and Table S3 gives the stock concentration and solvent only; positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
         </is>
       </c>
       <c r="AA297" t="inlineStr"/>
@@ -74290,7 +74360,7 @@
       <c r="T298" t="inlineStr"/>
       <c r="U298" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>unknown (not reported)</t>
         </is>
       </c>
       <c r="V298" t="inlineStr">
@@ -74309,7 +74379,7 @@
       <c r="Y298" t="inlineStr"/>
       <c r="Z298" t="inlineStr">
         <is>
-          <t>concentration-response series per chemical (Table S3, not extracted); positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
+          <t>not reported by the paper; stocks serially diluted to unstated working concentrations, and Table S3 gives the stock concentration and solvent only; positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
         </is>
       </c>
       <c r="AA298" t="inlineStr"/>
@@ -74382,7 +74452,7 @@
       <c r="T299" t="inlineStr"/>
       <c r="U299" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>unknown (not reported)</t>
         </is>
       </c>
       <c r="V299" t="inlineStr">
@@ -74401,7 +74471,7 @@
       <c r="Y299" t="inlineStr"/>
       <c r="Z299" t="inlineStr">
         <is>
-          <t>concentration-response series per chemical (Table S3, not extracted); positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
+          <t>not reported by the paper; stocks serially diluted to unstated working concentrations, and Table S3 gives the stock concentration and solvent only; positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
         </is>
       </c>
       <c r="AA299" t="inlineStr"/>
@@ -74474,7 +74544,7 @@
       <c r="T300" t="inlineStr"/>
       <c r="U300" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>unknown (not reported)</t>
         </is>
       </c>
       <c r="V300" t="inlineStr">
@@ -74493,7 +74563,7 @@
       <c r="Y300" t="inlineStr"/>
       <c r="Z300" t="inlineStr">
         <is>
-          <t>concentration-response series per chemical (Table S3, not extracted); positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
+          <t>not reported by the paper; stocks serially diluted to unstated working concentrations, and Table S3 gives the stock concentration and solvent only; positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
         </is>
       </c>
       <c r="AA300" t="inlineStr"/>
@@ -74566,7 +74636,7 @@
       <c r="T301" t="inlineStr"/>
       <c r="U301" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>unknown (not reported)</t>
         </is>
       </c>
       <c r="V301" t="inlineStr">
@@ -74585,7 +74655,7 @@
       <c r="Y301" t="inlineStr"/>
       <c r="Z301" t="inlineStr">
         <is>
-          <t>concentration-response series per chemical (Table S3, not extracted); positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
+          <t>not reported by the paper; stocks serially diluted to unstated working concentrations, and Table S3 gives the stock concentration and solvent only; positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
         </is>
       </c>
       <c r="AA301" t="inlineStr"/>
@@ -74658,7 +74728,7 @@
       <c r="T302" t="inlineStr"/>
       <c r="U302" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>unknown (not reported)</t>
         </is>
       </c>
       <c r="V302" t="inlineStr">
@@ -74677,7 +74747,7 @@
       <c r="Y302" t="inlineStr"/>
       <c r="Z302" t="inlineStr">
         <is>
-          <t>concentration-response series per chemical (Table S3, not extracted); positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
+          <t>not reported by the paper; stocks serially diluted to unstated working concentrations, and Table S3 gives the stock concentration and solvent only; positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
         </is>
       </c>
       <c r="AA302" t="inlineStr"/>
@@ -74750,7 +74820,7 @@
       <c r="T303" t="inlineStr"/>
       <c r="U303" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>unknown (not reported)</t>
         </is>
       </c>
       <c r="V303" t="inlineStr">
@@ -74769,7 +74839,7 @@
       <c r="Y303" t="inlineStr"/>
       <c r="Z303" t="inlineStr">
         <is>
-          <t>concentration-response series per chemical (Table S3, not extracted); positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
+          <t>not reported by the paper; stocks serially diluted to unstated working concentrations, and Table S3 gives the stock concentration and solvent only; positive controls octanoic acid 1-3 mM and PFHxA 0.3-3 mM mM</t>
         </is>
       </c>
       <c r="AA303" t="inlineStr"/>
